--- a/final_score_table/delta_zscores_wide.xlsx
+++ b/final_score_table/delta_zscores_wide.xlsx
@@ -414,7 +414,7 @@
         <v>2024</v>
       </c>
       <c r="C2">
-        <v>0.7333424902596104</v>
+        <v>-0.7333424902596104</v>
       </c>
       <c r="D2">
         <v>0.0388945578516545</v>
@@ -446,7 +446,7 @@
         <v>2025</v>
       </c>
       <c r="C3">
-        <v>1.88924726678259</v>
+        <v>-1.88924726678259</v>
       </c>
       <c r="D3">
         <v>-0.05747712912017636</v>
@@ -478,7 +478,7 @@
         <v>2026</v>
       </c>
       <c r="C4">
-        <v>1.271939646823576</v>
+        <v>-1.271939646823576</v>
       </c>
       <c r="D4">
         <v>0.009125824712799871</v>
@@ -510,7 +510,7 @@
         <v>2027</v>
       </c>
       <c r="C5">
-        <v>1.993716583153642</v>
+        <v>-1.993716583153642</v>
       </c>
       <c r="D5">
         <v>0.02333876716993255</v>
@@ -542,7 +542,7 @@
         <v>2028</v>
       </c>
       <c r="C6">
-        <v>1.805126174581776</v>
+        <v>-1.805126174581776</v>
       </c>
       <c r="D6">
         <v>0.1038885181666004</v>
@@ -574,7 +574,7 @@
         <v>2024</v>
       </c>
       <c r="C7">
-        <v>0.5644980352802362</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0.8555369664685768</v>
@@ -606,7 +606,7 @@
         <v>2025</v>
       </c>
       <c r="C8">
-        <v>2.190546647885756</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0.912576104814224</v>
@@ -638,7 +638,7 @@
         <v>2026</v>
       </c>
       <c r="C9">
-        <v>1.396906995264833</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0.7281006971687246</v>
@@ -670,7 +670,7 @@
         <v>2027</v>
       </c>
       <c r="C10">
-        <v>2.18401000421736</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0.5130714837948983</v>
@@ -702,7 +702,7 @@
         <v>2028</v>
       </c>
       <c r="C11">
-        <v>2.01315778917803</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0.4162864453688061</v>
@@ -734,7 +734,7 @@
         <v>2024</v>
       </c>
       <c r="C12">
-        <v>0.6372249226646891</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0.7634053091493125</v>
@@ -766,7 +766,7 @@
         <v>2025</v>
       </c>
       <c r="C13">
-        <v>1.860498867875477</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>-0.4042925758364972</v>
@@ -798,7 +798,7 @@
         <v>2026</v>
       </c>
       <c r="C14">
-        <v>1.183256040829993</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0.9671295371895102</v>
@@ -830,7 +830,7 @@
         <v>2027</v>
       </c>
       <c r="C15">
-        <v>1.925542033341688</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>-0.07880851110079377</v>
@@ -862,7 +862,7 @@
         <v>2028</v>
       </c>
       <c r="C16">
-        <v>1.716993300425063</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0.7224510251812458</v>
@@ -894,7 +894,7 @@
         <v>2024</v>
       </c>
       <c r="C17">
-        <v>0.2068595376074132</v>
+        <v>-0.2068595376074132</v>
       </c>
       <c r="D17">
         <v>0.07421888120402384</v>
@@ -926,7 +926,7 @@
         <v>2025</v>
       </c>
       <c r="C18">
-        <v>0.7979875427818706</v>
+        <v>-0.7979875427818706</v>
       </c>
       <c r="D18">
         <v>-0.07475319541823656</v>
@@ -947,7 +947,7 @@
         <v>-0.4413156876577949</v>
       </c>
       <c r="J18">
-        <v>4.278576788150736</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -958,7 +958,7 @@
         <v>2026</v>
       </c>
       <c r="C19">
-        <v>0.4344645595460037</v>
+        <v>-0.4344645595460037</v>
       </c>
       <c r="D19">
         <v>0.009470635505051591</v>
@@ -979,7 +979,7 @@
         <v>-0.5025042532569713</v>
       </c>
       <c r="J19">
-        <v>4.003372325538229</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -990,7 +990,7 @@
         <v>2027</v>
       </c>
       <c r="C20">
-        <v>0.9042172161812426</v>
+        <v>-0.9042172161812426</v>
       </c>
       <c r="D20">
         <v>0.01977210586881845</v>
@@ -1022,7 +1022,7 @@
         <v>2028</v>
       </c>
       <c r="C21">
-        <v>0.6498867836195503</v>
+        <v>-0.6498867836195503</v>
       </c>
       <c r="D21">
         <v>0.1014527020470225</v>
@@ -1054,7 +1054,7 @@
         <v>2024</v>
       </c>
       <c r="C22">
-        <v>0.04456394685349729</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0.04005843105719911</v>
@@ -1086,7 +1086,7 @@
         <v>2025</v>
       </c>
       <c r="C23">
-        <v>0.3095822877291646</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>-0.1273395141268176</v>
@@ -1118,7 +1118,7 @@
         <v>2026</v>
       </c>
       <c r="C24">
-        <v>0.02667111440582718</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>-0.05362332310319957</v>
@@ -1150,7 +1150,7 @@
         <v>2027</v>
       </c>
       <c r="C25">
-        <v>0.395459670202239</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>-0.03984148883137382</v>
@@ -1182,7 +1182,7 @@
         <v>2028</v>
       </c>
       <c r="C26">
-        <v>0.1131404404814016</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0.04753196623476768</v>
@@ -1214,7 +1214,7 @@
         <v>2024</v>
       </c>
       <c r="C27">
-        <v>0.04456319064562979</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>-0.184684324533064</v>
@@ -1243,7 +1243,7 @@
         <v>2025</v>
       </c>
       <c r="C28">
-        <v>0.3095836729646668</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>-0.5835874883774302</v>
@@ -1272,7 +1272,7 @@
         <v>2026</v>
       </c>
       <c r="C29">
-        <v>0.02667043027554011</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>-0.5710862909395592</v>
@@ -1301,7 +1301,7 @@
         <v>2027</v>
       </c>
       <c r="C30">
-        <v>0.3954605052860894</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>-0.5639890758524272</v>
@@ -1330,7 +1330,7 @@
         <v>2028</v>
       </c>
       <c r="C31">
-        <v>0.1131404527566059</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>-0.4414595572392396</v>
@@ -1359,7 +1359,7 @@
         <v>2024</v>
       </c>
       <c r="C32">
-        <v>0.5060845631620389</v>
+        <v>-1.012169126324078</v>
       </c>
       <c r="D32">
         <v>0.04468987508871133</v>
@@ -1385,7 +1385,7 @@
         <v>2025</v>
       </c>
       <c r="C33">
-        <v>2.754696840608452</v>
+        <v>-4</v>
       </c>
       <c r="D33">
         <v>-0.07994539659314813</v>
@@ -1411,7 +1411,7 @@
         <v>2026</v>
       </c>
       <c r="C34">
-        <v>1.908471699090079</v>
+        <v>-3.816943398180157</v>
       </c>
       <c r="D34">
         <v>-0.00496665922969358</v>
@@ -1437,7 +1437,7 @@
         <v>2027</v>
       </c>
       <c r="C35">
-        <v>2.704385971414861</v>
+        <v>-4</v>
       </c>
       <c r="D35">
         <v>0.0075498732107112</v>
@@ -1463,7 +1463,7 @@
         <v>2028</v>
       </c>
       <c r="C36">
-        <v>2.637319261459818</v>
+        <v>-4</v>
       </c>
       <c r="D36">
         <v>0.09016935655276478</v>
@@ -1489,7 +1489,7 @@
         <v>2024</v>
       </c>
       <c r="C37">
-        <v>0.5054771403799232</v>
+        <v>-1.010954280759846</v>
       </c>
       <c r="D37">
         <v>0.1505038029587149</v>
@@ -1512,7 +1512,7 @@
         <v>2025</v>
       </c>
       <c r="C38">
-        <v>2.754215885164013</v>
+        <v>-4</v>
       </c>
       <c r="D38">
         <v>0.3108220599349051</v>
@@ -1535,7 +1535,7 @@
         <v>2026</v>
       </c>
       <c r="C39">
-        <v>1.907782252189578</v>
+        <v>-3.815564504379158</v>
       </c>
       <c r="D39">
         <v>0.2328536180541697</v>
@@ -1558,7 +1558,7 @@
         <v>2027</v>
       </c>
       <c r="C40">
-        <v>2.703746210589863</v>
+        <v>-4</v>
       </c>
       <c r="D40">
         <v>0.3563029762278507</v>
@@ -1581,7 +1581,7 @@
         <v>2028</v>
       </c>
       <c r="C41">
-        <v>2.636540054369118</v>
+        <v>-4</v>
       </c>
       <c r="D41">
         <v>0.3147078135646905</v>
@@ -1604,7 +1604,7 @@
         <v>2024</v>
       </c>
       <c r="C42">
-        <v>0.7333435721383892</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>-0.3541881231534463</v>
@@ -1636,7 +1636,7 @@
         <v>2025</v>
       </c>
       <c r="C43">
-        <v>1.889246320200981</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>-0.4508379103602681</v>
@@ -1668,7 +1668,7 @@
         <v>2026</v>
       </c>
       <c r="C44">
-        <v>1.271939772419336</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>-0.7668265813558827</v>
@@ -1700,7 +1700,7 @@
         <v>2027</v>
       </c>
       <c r="C45">
-        <v>1.993716278857253</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>-0.4635987296299755</v>
@@ -1732,7 +1732,7 @@
         <v>2028</v>
       </c>
       <c r="C46">
-        <v>1.8051259571195</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>-0.5768224634709042</v>
@@ -1764,7 +1764,7 @@
         <v>2024</v>
       </c>
       <c r="C47">
-        <v>0.5851036360972335</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>-0.2154272155270247</v>
@@ -1796,7 +1796,7 @@
         <v>2025</v>
       </c>
       <c r="C48">
-        <v>2.153840350634543</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>-0.572877093598449</v>
@@ -1828,7 +1828,7 @@
         <v>2026</v>
       </c>
       <c r="C49">
-        <v>1.377778754139848</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>-0.5437819228342443</v>
@@ -1860,7 +1860,7 @@
         <v>2027</v>
       </c>
       <c r="C50">
-        <v>2.15934062634398</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>-0.5324643034086465</v>
@@ -1892,7 +1892,7 @@
         <v>2028</v>
       </c>
       <c r="C51">
-        <v>1.984995296499867</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>-0.410567605606744</v>
@@ -1924,7 +1924,7 @@
         <v>2024</v>
       </c>
       <c r="C52">
-        <v>0.7120624019204042</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>0.2240051466377108</v>
@@ -1956,7 +1956,7 @@
         <v>2025</v>
       </c>
       <c r="C53">
-        <v>1.883080985128882</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>-0.09813578137556436</v>
@@ -1988,7 +1988,7 @@
         <v>2026</v>
       </c>
       <c r="C54">
-        <v>1.252329754201254</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0.2497606591936364</v>
@@ -2020,7 +2020,7 @@
         <v>2027</v>
       </c>
       <c r="C55">
-        <v>1.978762073831538</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0.04561182186391226</v>
@@ -2052,7 +2052,7 @@
         <v>2028</v>
       </c>
       <c r="C56">
-        <v>1.785726607864191</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0.2683205104275726</v>
@@ -2416,7 +2416,7 @@
         <v>0.1750596569033806</v>
       </c>
       <c r="G67">
-        <v>-12.97390441953681</v>
+        <v>-4</v>
       </c>
       <c r="H67">
         <v>0.4405152380751655</v>
@@ -2564,7 +2564,7 @@
         <v>2024</v>
       </c>
       <c r="C72">
-        <v>0.04456326972796434</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>-1.044139624156992</v>
@@ -2596,7 +2596,7 @@
         <v>2025</v>
       </c>
       <c r="C73">
-        <v>0.3095835292179706</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>1.369989560327411</v>
@@ -2628,7 +2628,7 @@
         <v>2026</v>
       </c>
       <c r="C74">
-        <v>0.02667050202998473</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>-0.7102174956014559</v>
@@ -2660,7 +2660,7 @@
         <v>2027</v>
       </c>
       <c r="C75">
-        <v>0.3954604189180965</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>0.5336467121233255</v>
@@ -2692,7 +2692,7 @@
         <v>2028</v>
       </c>
       <c r="C76">
-        <v>0.1131404521127849</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>-0.07960586510850433</v>
@@ -2724,7 +2724,7 @@
         <v>2024</v>
       </c>
       <c r="C77">
-        <v>0.0445636275249828</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>-0.2639734947220446</v>
@@ -2753,7 +2753,7 @@
         <v>2025</v>
       </c>
       <c r="C78">
-        <v>0.3095828665707552</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>-0.7313571839977996</v>
@@ -2782,7 +2782,7 @@
         <v>2026</v>
       </c>
       <c r="C79">
-        <v>0.02667082436639979</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>-0.731442923507483</v>
@@ -2811,7 +2811,7 @@
         <v>2027</v>
       </c>
       <c r="C80">
-        <v>0.3954600175743202</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>-0.7298216059491696</v>
@@ -2840,7 +2840,7 @@
         <v>2028</v>
       </c>
       <c r="C81">
-        <v>0.113140442166535</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>-0.6021163487127894</v>
@@ -3014,7 +3014,7 @@
         <v>2024</v>
       </c>
       <c r="C87">
-        <v>0.04456144010686853</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0.1592059636378345</v>
@@ -3043,7 +3043,7 @@
         <v>2025</v>
       </c>
       <c r="C88">
-        <v>0.3095868928486417</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>0.07919860060209098</v>
@@ -3072,7 +3072,7 @@
         <v>2026</v>
       </c>
       <c r="C89">
-        <v>0.02666884907713513</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>0.1668465403504979</v>
@@ -3101,7 +3101,7 @@
         <v>2027</v>
       </c>
       <c r="C90">
-        <v>0.3954624497962806</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0.1718307284935156</v>
@@ -3130,7 +3130,7 @@
         <v>2028</v>
       </c>
       <c r="C91">
-        <v>0.1131404887446153</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0.2361894143801802</v>
@@ -3159,7 +3159,7 @@
         <v>2024</v>
       </c>
       <c r="C92">
-        <v>-0.09699579980866252</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>0.09040897689643476</v>
@@ -3188,7 +3188,7 @@
         <v>2025</v>
       </c>
       <c r="C93">
-        <v>1.526525861994069</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>0.00521353076518799</v>
@@ -3217,7 +3217,7 @@
         <v>2026</v>
       </c>
       <c r="C94">
-        <v>0.4596314936275101</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>0.08193061162916616</v>
@@ -3246,7 +3246,7 @@
         <v>2027</v>
       </c>
       <c r="C95">
-        <v>1.319105059298282</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0.0920728157294169</v>
@@ -3275,7 +3275,7 @@
         <v>2028</v>
       </c>
       <c r="C96">
-        <v>0.9575844713612932</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>0.1654576909254313</v>
@@ -3304,7 +3304,7 @@
         <v>2024</v>
       </c>
       <c r="C97">
-        <v>-0.09699292335125027</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>-0.2300677768949428</v>
@@ -3333,7 +3333,7 @@
         <v>2025</v>
       </c>
       <c r="C98">
-        <v>1.526523809105733</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>-0.799285669063304</v>
@@ -3362,7 +3362,7 @@
         <v>2026</v>
       </c>
       <c r="C99">
-        <v>0.4596312496908682</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>-0.8462424832795863</v>
@@ -3391,7 +3391,7 @@
         <v>2027</v>
       </c>
       <c r="C100">
-        <v>1.319104311545344</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>-0.8603809791796868</v>
@@ -3420,7 +3420,7 @@
         <v>2028</v>
       </c>
       <c r="C101">
-        <v>0.9575836920044346</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>-0.7329711588860481</v>
@@ -3449,7 +3449,7 @@
         <v>2024</v>
       </c>
       <c r="C102">
-        <v>-0.09698902213368542</v>
+        <v>0.09698902213368542</v>
       </c>
       <c r="D102">
         <v>0.1288449353980621</v>
@@ -3478,7 +3478,7 @@
         <v>2025</v>
       </c>
       <c r="C103">
-        <v>1.52652102490612</v>
+        <v>-1.52652102490612</v>
       </c>
       <c r="D103">
         <v>0.05904609062546863</v>
@@ -3507,7 +3507,7 @@
         <v>2026</v>
       </c>
       <c r="C104">
-        <v>0.4596309189092965</v>
+        <v>-0.4596309189092965</v>
       </c>
       <c r="D104">
         <v>0.140930839594242</v>
@@ -3536,7 +3536,7 @@
         <v>2027</v>
       </c>
       <c r="C105">
-        <v>1.3191032974511</v>
+        <v>-1.3191032974511</v>
       </c>
       <c r="D105">
         <v>0.1477935709791404</v>
@@ -3565,7 +3565,7 @@
         <v>2028</v>
       </c>
       <c r="C106">
-        <v>0.9575826350603468</v>
+        <v>-0.9575826350603468</v>
       </c>
       <c r="D106">
         <v>0.214942823724008</v>
@@ -3594,7 +3594,7 @@
         <v>2024</v>
       </c>
       <c r="C107">
-        <v>-0.09699687965080096</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0.4322627895604731</v>
@@ -3623,7 +3623,7 @@
         <v>2025</v>
       </c>
       <c r="C108">
-        <v>1.526526634804145</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>0.3309552975882219</v>
@@ -3652,7 +3652,7 @@
         <v>2026</v>
       </c>
       <c r="C109">
-        <v>0.4596315871034076</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>0.4470346609226996</v>
@@ -3681,7 +3681,7 @@
         <v>2027</v>
       </c>
       <c r="C110">
-        <v>1.319105341982369</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>0.4312796725052867</v>
@@ -3710,7 +3710,7 @@
         <v>2028</v>
       </c>
       <c r="C111">
-        <v>0.9575847662891094</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0.4611815984181286</v>
@@ -3739,7 +3739,7 @@
         <v>2024</v>
       </c>
       <c r="C112">
-        <v>-0.09699319799076792</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>0.1694746369623975</v>
@@ -3765,7 +3765,7 @@
         <v>2025</v>
       </c>
       <c r="C113">
-        <v>1.526524007823796</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>-0.2466173839627325</v>
@@ -3791,7 +3791,7 @@
         <v>2026</v>
       </c>
       <c r="C114">
-        <v>0.4596312753834484</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>-0.03814211400214935</v>
@@ -3817,7 +3817,7 @@
         <v>2027</v>
       </c>
       <c r="C115">
-        <v>1.319104385435009</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>-0.07459976266651888</v>
@@ -3843,7 +3843,7 @@
         <v>2028</v>
       </c>
       <c r="C116">
-        <v>0.9575837693906784</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>0.03204201468127618</v>
@@ -3869,7 +3869,7 @@
         <v>2024</v>
       </c>
       <c r="C117">
-        <v>0.43349129415464</v>
+        <v>-0.43349129415464</v>
       </c>
       <c r="D117">
         <v>-0.04721288730806083</v>
@@ -3901,7 +3901,7 @@
         <v>2025</v>
       </c>
       <c r="C118">
-        <v>-0.3274321260035988</v>
+        <v>0.3274321260035988</v>
       </c>
       <c r="D118">
         <v>-0.3281362800066198</v>
@@ -3933,7 +3933,7 @@
         <v>2026</v>
       </c>
       <c r="C119">
-        <v>-0.1440609049849968</v>
+        <v>0.1440609049849968</v>
       </c>
       <c r="D119">
         <v>-0.2581349370645015</v>
@@ -3965,7 +3965,7 @@
         <v>2027</v>
       </c>
       <c r="C120">
-        <v>-0.04461052866115887</v>
+        <v>0.04461052866115887</v>
       </c>
       <c r="D120">
         <v>-0.2441328745207646</v>
@@ -3997,7 +3997,7 @@
         <v>2028</v>
       </c>
       <c r="C121">
-        <v>-0.2735598689425195</v>
+        <v>0.2735598689425195</v>
       </c>
       <c r="D121">
         <v>-0.1387181989024345</v>
@@ -4029,7 +4029,7 @@
         <v>2024</v>
       </c>
       <c r="C122">
-        <v>7.112859071929436</v>
+        <v>4</v>
       </c>
       <c r="D122">
         <v>0.9468455274879264</v>
@@ -4174,7 +4174,7 @@
         <v>2024</v>
       </c>
       <c r="C127">
-        <v>0.433473850620741</v>
+        <v>-0.433473850620741</v>
       </c>
       <c r="D127">
         <v>0.1208833894824362</v>
@@ -4206,7 +4206,7 @@
         <v>2025</v>
       </c>
       <c r="C128">
-        <v>-0.327464107143183</v>
+        <v>0.327464107143183</v>
       </c>
       <c r="D128">
         <v>-0.4097027192029862</v>
@@ -4238,7 +4238,7 @@
         <v>2026</v>
       </c>
       <c r="C129">
-        <v>-0.1440878580264681</v>
+        <v>0.1440878580264681</v>
       </c>
       <c r="D129">
         <v>-0.04433709120410097</v>
@@ -4270,7 +4270,7 @@
         <v>2027</v>
       </c>
       <c r="C130">
-        <v>-0.04464646188531514</v>
+        <v>0.04464646188531514</v>
       </c>
       <c r="D130">
         <v>-0.2274401810401871</v>
@@ -4302,7 +4302,7 @@
         <v>2028</v>
       </c>
       <c r="C131">
-        <v>-0.273595606298329</v>
+        <v>0.273595606298329</v>
       </c>
       <c r="D131">
         <v>-0.0094449070790235</v>
@@ -4334,7 +4334,7 @@
         <v>2024</v>
       </c>
       <c r="C132">
-        <v>0.4335003464177231</v>
+        <v>-0.4335003464177231</v>
       </c>
       <c r="D132">
         <v>-0.7159262826625644</v>
@@ -4363,7 +4363,7 @@
         <v>2025</v>
       </c>
       <c r="C133">
-        <v>-0.327447602410342</v>
+        <v>0.327447602410342</v>
       </c>
       <c r="D133">
         <v>-0.2139222402325734</v>
@@ -4392,7 +4392,7 @@
         <v>2026</v>
       </c>
       <c r="C134">
-        <v>-0.1440526977656661</v>
+        <v>0.1440526977656661</v>
       </c>
       <c r="D134">
         <v>-1.614677620948121</v>
@@ -4421,7 +4421,7 @@
         <v>2027</v>
       </c>
       <c r="C135">
-        <v>-0.04462006125025361</v>
+        <v>0.04462006125025361</v>
       </c>
       <c r="D135">
         <v>-0.1765535321567982</v>
@@ -4450,7 +4450,7 @@
         <v>2028</v>
       </c>
       <c r="C136">
-        <v>-0.2735596963325852</v>
+        <v>0.2735596963325852</v>
       </c>
       <c r="D136">
         <v>-1.450249109694733</v>
@@ -4479,7 +4479,7 @@
         <v>2024</v>
       </c>
       <c r="C137">
-        <v>0.4335028919017059</v>
+        <v>-0.4335028919017059</v>
       </c>
       <c r="D137">
         <v>-0.2796408532058017</v>
@@ -4508,7 +4508,7 @@
         <v>2025</v>
       </c>
       <c r="C138">
-        <v>-0.3274519709118439</v>
+        <v>0.3274519709118439</v>
       </c>
       <c r="D138">
         <v>-0.110460053589302</v>
@@ -4537,7 +4537,7 @@
         <v>2026</v>
       </c>
       <c r="C139">
-        <v>-0.1440503928607431</v>
+        <v>0.1440503928607431</v>
       </c>
       <c r="D139">
         <v>-0.4331664320758579</v>
@@ -4566,7 +4566,7 @@
         <v>2027</v>
       </c>
       <c r="C140">
-        <v>-0.0446227563592366</v>
+        <v>0.0446227563592366</v>
       </c>
       <c r="D140">
         <v>-0.1700047745043274</v>
@@ -4595,7 +4595,7 @@
         <v>2028</v>
       </c>
       <c r="C141">
-        <v>-0.2735596572532438</v>
+        <v>0.2735596572532438</v>
       </c>
       <c r="D141">
         <v>-0.2130834453417925</v>
@@ -4624,7 +4624,7 @@
         <v>2024</v>
       </c>
       <c r="C142">
-        <v>0.4334865445479064</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>0.1981747961294711</v>
@@ -4656,7 +4656,7 @@
         <v>2025</v>
       </c>
       <c r="C143">
-        <v>-0.3274240160322323</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>0.2416717689888746</v>
@@ -4688,7 +4688,7 @@
         <v>2026</v>
       </c>
       <c r="C144">
-        <v>-0.1440652129983456</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>0.3310685586206317</v>
@@ -4720,7 +4720,7 @@
         <v>2027</v>
       </c>
       <c r="C145">
-        <v>-0.04460553610783189</v>
+        <v>0</v>
       </c>
       <c r="D145">
         <v>0.3270730386809056</v>
@@ -4752,7 +4752,7 @@
         <v>2028</v>
       </c>
       <c r="C146">
-        <v>-0.2735599653513306</v>
+        <v>0</v>
       </c>
       <c r="D146">
         <v>0.3714474316352843</v>
@@ -4784,7 +4784,7 @@
         <v>2024</v>
       </c>
       <c r="C147">
-        <v>0.4334608039010074</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>-0.417885233551836</v>
@@ -4816,7 +4816,7 @@
         <v>2025</v>
       </c>
       <c r="C148">
-        <v>-0.3274416555582014</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>0.2534922358967237</v>
@@ -4848,7 +4848,7 @@
         <v>2026</v>
       </c>
       <c r="C149">
-        <v>-0.1440996604337057</v>
+        <v>0</v>
       </c>
       <c r="D149">
         <v>-0.5713147322857181</v>
@@ -4880,7 +4880,7 @@
         <v>2027</v>
       </c>
       <c r="C150">
-        <v>-0.04463259467640611</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>0.09202679711526759</v>
@@ -4912,7 +4912,7 @@
         <v>2028</v>
       </c>
       <c r="C151">
-        <v>-0.2735957713947618</v>
+        <v>0</v>
       </c>
       <c r="D151">
         <v>-0.2502992070013809</v>
@@ -4944,7 +4944,7 @@
         <v>2024</v>
       </c>
       <c r="C152">
-        <v>0.4334886309804972</v>
+        <v>0</v>
       </c>
       <c r="D152">
         <v>-0.01363690853678012</v>
@@ -4976,7 +4976,7 @@
         <v>2025</v>
       </c>
       <c r="C153">
-        <v>-0.3274275814383307</v>
+        <v>0</v>
       </c>
       <c r="D153">
         <v>-0.1723867288709821</v>
@@ -5008,7 +5008,7 @@
         <v>2026</v>
       </c>
       <c r="C154">
-        <v>-0.1440633210640917</v>
+        <v>0</v>
       </c>
       <c r="D154">
         <v>-0.1039186292329294</v>
@@ -5040,7 +5040,7 @@
         <v>2027</v>
       </c>
       <c r="C155">
-        <v>-0.04460773173431726</v>
+        <v>0</v>
       </c>
       <c r="D155">
         <v>-0.0889626502383191</v>
@@ -5072,7 +5072,7 @@
         <v>2028</v>
       </c>
       <c r="C156">
-        <v>-0.2735599246176985</v>
+        <v>0</v>
       </c>
       <c r="D156">
         <v>0.00307428525516856</v>
@@ -5104,7 +5104,7 @@
         <v>2024</v>
       </c>
       <c r="C157">
-        <v>0.4334383923010208</v>
+        <v>-0.4334383923010208</v>
       </c>
       <c r="D157">
         <v>-0.00766177714569753</v>
@@ -5136,7 +5136,7 @@
         <v>2025</v>
       </c>
       <c r="C158">
-        <v>-0.3267789755021803</v>
+        <v>0.3267789755021803</v>
       </c>
       <c r="D158">
         <v>0.1454959715624441</v>
@@ -5168,7 +5168,7 @@
         <v>2026</v>
       </c>
       <c r="C159">
-        <v>-0.143879577409506</v>
+        <v>0.143879577409506</v>
       </c>
       <c r="D159">
         <v>0.08126324238452826</v>
@@ -5200,7 +5200,7 @@
         <v>2027</v>
       </c>
       <c r="C160">
-        <v>-0.04404539161702108</v>
+        <v>0.04404539161702108</v>
       </c>
       <c r="D160">
         <v>0.1530429028388627</v>
@@ -5232,7 +5232,7 @@
         <v>2028</v>
       </c>
       <c r="C161">
-        <v>-0.2731385781874539</v>
+        <v>0.2731385781874539</v>
       </c>
       <c r="D161">
         <v>0.1955344700184099</v>
@@ -5264,7 +5264,7 @@
         <v>2024</v>
       </c>
       <c r="C162">
-        <v>0.05096743232020245</v>
+        <v>-0.1019348646404049</v>
       </c>
       <c r="D162">
         <v>-0.1624049302626747</v>
@@ -5285,7 +5285,7 @@
         <v>-1.152098193670531</v>
       </c>
       <c r="J162">
-        <v>-7.031023995814655</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="163">
@@ -5296,7 +5296,7 @@
         <v>2025</v>
       </c>
       <c r="C163">
-        <v>1.246411314946629</v>
+        <v>-2.492822629893258</v>
       </c>
       <c r="D163">
         <v>0.22468011476787</v>
@@ -5328,7 +5328,7 @@
         <v>2026</v>
       </c>
       <c r="C164">
-        <v>0.3208824449749464</v>
+        <v>-0.6417648899498929</v>
       </c>
       <c r="D164">
         <v>-0.3620761852999293</v>
@@ -5360,7 +5360,7 @@
         <v>2027</v>
       </c>
       <c r="C165">
-        <v>1.1308892398202</v>
+        <v>-2.261778479640399</v>
       </c>
       <c r="D165">
         <v>0.272874270162784</v>
@@ -5392,7 +5392,7 @@
         <v>2028</v>
       </c>
       <c r="C166">
-        <v>0.7463420652809052</v>
+        <v>-1.49268413056181</v>
       </c>
       <c r="D166">
         <v>-0.1830128606558517</v>
@@ -5424,7 +5424,7 @@
         <v>2024</v>
       </c>
       <c r="C167">
-        <v>-0.09699637926670134</v>
+        <v>0</v>
       </c>
       <c r="D167">
         <v>-0.5865787244628338</v>
@@ -5453,7 +5453,7 @@
         <v>2025</v>
       </c>
       <c r="C168">
-        <v>1.526526277874541</v>
+        <v>0</v>
       </c>
       <c r="D168">
         <v>-1.145362617754787</v>
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="C169">
-        <v>0.4596315448331869</v>
+        <v>0</v>
       </c>
       <c r="D169">
         <v>-1.060044706957616</v>
@@ -5511,7 +5511,7 @@
         <v>2027</v>
       </c>
       <c r="C170">
-        <v>1.319105212076389</v>
+        <v>0</v>
       </c>
       <c r="D170">
         <v>-0.9660008007075908</v>
@@ -5540,7 +5540,7 @@
         <v>2028</v>
       </c>
       <c r="C171">
-        <v>0.9575846309180496</v>
+        <v>0</v>
       </c>
       <c r="D171">
         <v>-0.7545152283033375</v>
@@ -5569,7 +5569,7 @@
         <v>2024</v>
       </c>
       <c r="C172">
-        <v>-0.0969952450624106</v>
+        <v>0</v>
       </c>
       <c r="D172">
         <v>-0.2241537681541397</v>
@@ -5598,7 +5598,7 @@
         <v>2025</v>
       </c>
       <c r="C173">
-        <v>1.526525465318258</v>
+        <v>0</v>
       </c>
       <c r="D173">
         <v>-0.4682095074867714</v>
@@ -5627,7 +5627,7 @@
         <v>2026</v>
       </c>
       <c r="C174">
-        <v>0.4596314459073939</v>
+        <v>0</v>
       </c>
       <c r="D174">
         <v>-0.4118954840326277</v>
@@ -5656,7 +5656,7 @@
         <v>2027</v>
       </c>
       <c r="C175">
-        <v>1.319104914387737</v>
+        <v>0</v>
       </c>
       <c r="D175">
         <v>-0.3954431881656312</v>
@@ -5685,7 +5685,7 @@
         <v>2028</v>
       </c>
       <c r="C176">
-        <v>0.9575843202209414</v>
+        <v>0</v>
       </c>
       <c r="D176">
         <v>-0.2802119702370798</v>
@@ -5735,7 +5735,7 @@
         <v>-1.151727065515722</v>
       </c>
       <c r="J177">
-        <v>-7.749234498851919</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="178">
@@ -5895,7 +5895,7 @@
         <v>-0.3763484792844571</v>
       </c>
       <c r="J182">
-        <v>-4.837003156598143</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="183">
@@ -5982,7 +5982,7 @@
         <v>0.7386454099206915</v>
       </c>
       <c r="G185">
-        <v>4.074596258935308</v>
+        <v>4</v>
       </c>
       <c r="H185">
         <v>-0.01860581406713301</v>
@@ -6354,7 +6354,7 @@
         <v>2024</v>
       </c>
       <c r="C197">
-        <v>0.01271279210913685</v>
+        <v>-0.01271279210913685</v>
       </c>
       <c r="D197">
         <v>-0.1042758023090792</v>
@@ -6383,7 +6383,7 @@
         <v>2025</v>
       </c>
       <c r="C198">
-        <v>-0.1189445995548905</v>
+        <v>0.1189445995548905</v>
       </c>
       <c r="D198">
         <v>-0.3104934847106516</v>
@@ -6412,7 +6412,7 @@
         <v>2026</v>
       </c>
       <c r="C199">
-        <v>-0.3531442306075899</v>
+        <v>0.3531442306075899</v>
       </c>
       <c r="D199">
         <v>-0.264644285610209</v>
@@ -6441,7 +6441,7 @@
         <v>2027</v>
       </c>
       <c r="C200">
-        <v>-0.02282784997576937</v>
+        <v>0.02282784997576937</v>
       </c>
       <c r="D200">
         <v>-0.2457221703144132</v>
@@ -6470,7 +6470,7 @@
         <v>2028</v>
       </c>
       <c r="C201">
-        <v>-0.3687750864595797</v>
+        <v>0.3687750864595797</v>
       </c>
       <c r="D201">
         <v>-0.141064600680126</v>
@@ -6499,7 +6499,7 @@
         <v>2024</v>
       </c>
       <c r="C202">
-        <v>0.4334617942870069</v>
+        <v>-0.4334617942870069</v>
       </c>
       <c r="D202">
         <v>-0.2469194134806739</v>
@@ -6528,7 +6528,7 @@
         <v>2025</v>
       </c>
       <c r="C203">
-        <v>-0.3274413521298175</v>
+        <v>0.3274413521298175</v>
       </c>
       <c r="D203">
         <v>-0.05929667292398229</v>
@@ -6557,7 +6557,7 @@
         <v>2026</v>
       </c>
       <c r="C204">
-        <v>-0.1440984026791458</v>
+        <v>0.1440984026791458</v>
       </c>
       <c r="D204">
         <v>-0.3464090769185706</v>
@@ -6586,7 +6586,7 @@
         <v>2027</v>
       </c>
       <c r="C205">
-        <v>-0.04463188329584098</v>
+        <v>0.04463188329584098</v>
       </c>
       <c r="D205">
         <v>-0.1167541366303538</v>
@@ -6615,7 +6615,7 @@
         <v>2028</v>
       </c>
       <c r="C206">
-        <v>-0.2735946087107534</v>
+        <v>0.2735946087107534</v>
       </c>
       <c r="D206">
         <v>-0.1369606721098951</v>
@@ -6644,7 +6644,7 @@
         <v>2024</v>
       </c>
       <c r="C207">
-        <v>0.4334841461592859</v>
+        <v>0</v>
       </c>
       <c r="D207">
         <v>0.6736105435595352</v>
@@ -6673,7 +6673,7 @@
         <v>2025</v>
       </c>
       <c r="C208">
-        <v>-0.3274199164354618</v>
+        <v>0</v>
       </c>
       <c r="D208">
         <v>0.1761428304405133</v>
@@ -6705,7 +6705,7 @@
         <v>2026</v>
       </c>
       <c r="C209">
-        <v>-0.1440673875981564</v>
+        <v>0</v>
       </c>
       <c r="D209">
         <v>-1.093494107430287</v>
@@ -6737,7 +6737,7 @@
         <v>2027</v>
       </c>
       <c r="C210">
-        <v>-0.04460301123311016</v>
+        <v>0</v>
       </c>
       <c r="D210">
         <v>0.3603832602199697</v>
@@ -6769,7 +6769,7 @@
         <v>2028</v>
       </c>
       <c r="C211">
-        <v>-0.2735600115333892</v>
+        <v>0</v>
       </c>
       <c r="D211">
         <v>1.06415258775628</v>
@@ -6801,7 +6801,7 @@
         <v>2024</v>
       </c>
       <c r="C212">
-        <v>-0.4966218799453314</v>
+        <v>0</v>
       </c>
       <c r="D212">
         <v>-0.07282932928160631</v>
@@ -6833,7 +6833,7 @@
         <v>2025</v>
       </c>
       <c r="C213">
-        <v>-0.04847798981778094</v>
+        <v>0</v>
       </c>
       <c r="D213">
         <v>-0.4748039465783236</v>
@@ -6865,7 +6865,7 @@
         <v>2026</v>
       </c>
       <c r="C214">
-        <v>-0.8560055742709681</v>
+        <v>0</v>
       </c>
       <c r="D214">
         <v>-0.3835581252932834</v>
@@ -6897,7 +6897,7 @@
         <v>2027</v>
       </c>
       <c r="C215">
-        <v>-0.1992575380670373</v>
+        <v>0</v>
       </c>
       <c r="D215">
         <v>-0.3816293523479133</v>
@@ -6929,7 +6929,7 @@
         <v>2028</v>
       </c>
       <c r="C216">
-        <v>-0.7578778210944417</v>
+        <v>0</v>
       </c>
       <c r="D216">
         <v>-0.2639952583782884</v>
@@ -6961,7 +6961,7 @@
         <v>2024</v>
       </c>
       <c r="C217">
-        <v>-0.08975523675472458</v>
+        <v>0.08975523675472458</v>
       </c>
       <c r="D217">
         <v>-0.07446920279863971</v>
@@ -6993,7 +6993,7 @@
         <v>2025</v>
       </c>
       <c r="C218">
-        <v>-0.1736964123709177</v>
+        <v>0.1736964123709177</v>
       </c>
       <c r="D218">
         <v>0.03467580228787425</v>
@@ -7014,7 +7014,7 @@
         <v>-0.9244145364070604</v>
       </c>
       <c r="J218">
-        <v>4.32506538574634</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219">
@@ -7025,7 +7025,7 @@
         <v>2026</v>
       </c>
       <c r="C219">
-        <v>-0.5722184106855156</v>
+        <v>0.5722184106855156</v>
       </c>
       <c r="D219">
         <v>-0.07076847576854316</v>
@@ -7046,7 +7046,7 @@
         <v>-1.010716257432811</v>
       </c>
       <c r="J219">
-        <v>4.2019479584807</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220">
@@ -7057,7 +7057,7 @@
         <v>2027</v>
       </c>
       <c r="C220">
-        <v>-0.1321517621780673</v>
+        <v>0.1321517621780673</v>
       </c>
       <c r="D220">
         <v>0.03740378728813665</v>
@@ -7078,7 +7078,7 @@
         <v>-1.032420909587716</v>
       </c>
       <c r="J220">
-        <v>4.189457998369152</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221">
@@ -7089,7 +7089,7 @@
         <v>2028</v>
       </c>
       <c r="C221">
-        <v>-0.5679918995558172</v>
+        <v>0.5679918995558172</v>
       </c>
       <c r="D221">
         <v>0.07335187513968565</v>
@@ -7110,7 +7110,7 @@
         <v>-1.038388847562996</v>
       </c>
       <c r="J221">
-        <v>4.135651513726279</v>
+        <v>4</v>
       </c>
     </row>
     <row r="222">
@@ -7121,7 +7121,7 @@
         <v>2024</v>
       </c>
       <c r="C222">
-        <v>-0.5267705041834986</v>
+        <v>0.5267705041834986</v>
       </c>
       <c r="D222">
         <v>-0.05984512381284691</v>
@@ -7153,7 +7153,7 @@
         <v>2025</v>
       </c>
       <c r="C223">
-        <v>0.1198517830513214</v>
+        <v>-0.1198517830513214</v>
       </c>
       <c r="D223">
         <v>-0.2623766630419378</v>
@@ -7185,7 +7185,7 @@
         <v>2026</v>
       </c>
       <c r="C224">
-        <v>-0.6320797494409316</v>
+        <v>0.6320797494409316</v>
       </c>
       <c r="D224">
         <v>-0.2018547194460387</v>
@@ -7217,7 +7217,7 @@
         <v>2027</v>
       </c>
       <c r="C225">
-        <v>-0.03025991685245883</v>
+        <v>0.03025991685245883</v>
       </c>
       <c r="D225">
         <v>-0.1855236876984437</v>
@@ -7249,7 +7249,7 @@
         <v>2028</v>
       </c>
       <c r="C226">
-        <v>-0.5151231114682597</v>
+        <v>0.5151231114682597</v>
       </c>
       <c r="D226">
         <v>-0.0850974187785173</v>
@@ -7281,7 +7281,7 @@
         <v>2024</v>
       </c>
       <c r="C227">
-        <v>-1.429697845242699</v>
+        <v>1.429697845242699</v>
       </c>
       <c r="D227">
         <v>-0.02545812132992876</v>
@@ -7313,7 +7313,7 @@
         <v>2025</v>
       </c>
       <c r="C228">
-        <v>0.5261654242901999</v>
+        <v>-0.5261654242901999</v>
       </c>
       <c r="D228">
         <v>-0.148806757752939</v>
@@ -7345,7 +7345,7 @@
         <v>2026</v>
       </c>
       <c r="C229">
-        <v>-1.027344781651582</v>
+        <v>1.027344781651582</v>
       </c>
       <c r="D229">
         <v>-0.1029826779723506</v>
@@ -7377,7 +7377,7 @@
         <v>2027</v>
       </c>
       <c r="C230">
-        <v>-0.04820641804395792</v>
+        <v>0.04820641804395792</v>
       </c>
       <c r="D230">
         <v>-0.07961539635857037</v>
@@ -7409,7 +7409,7 @@
         <v>2028</v>
       </c>
       <c r="C231">
-        <v>-0.7110073876263546</v>
+        <v>0.7110073876263546</v>
       </c>
       <c r="D231">
         <v>0.00891054432550214</v>
@@ -7441,7 +7441,7 @@
         <v>2024</v>
       </c>
       <c r="C232">
-        <v>-1.431867990396503</v>
+        <v>0</v>
       </c>
       <c r="D232">
         <v>0.3184541992049212</v>
@@ -7473,7 +7473,7 @@
         <v>2025</v>
       </c>
       <c r="C233">
-        <v>0.5286290933823482</v>
+        <v>0</v>
       </c>
       <c r="D233">
         <v>-0.1407945333309404</v>
@@ -7505,7 +7505,7 @@
         <v>2026</v>
       </c>
       <c r="C234">
-        <v>-1.026721868670543</v>
+        <v>0</v>
       </c>
       <c r="D234">
         <v>0.3248198735871252</v>
@@ -7537,7 +7537,7 @@
         <v>2027</v>
       </c>
       <c r="C235">
-        <v>-0.0468171224902798</v>
+        <v>0</v>
       </c>
       <c r="D235">
         <v>0.06090645602211637</v>
@@ -7569,7 +7569,7 @@
         <v>2028</v>
       </c>
       <c r="C236">
-        <v>-0.7096486334990734</v>
+        <v>0</v>
       </c>
       <c r="D236">
         <v>0.2993615648345365</v>
@@ -7601,7 +7601,7 @@
         <v>2024</v>
       </c>
       <c r="C237">
-        <v>-1.152164122035431</v>
+        <v>1.152164122035431</v>
       </c>
       <c r="D237">
         <v>0.4707318900325879</v>
@@ -7633,7 +7633,7 @@
         <v>2025</v>
       </c>
       <c r="C238">
-        <v>0.1585786259582232</v>
+        <v>-0.1585786259582232</v>
       </c>
       <c r="D238">
         <v>0.444373640825601</v>
@@ -7665,7 +7665,7 @@
         <v>2026</v>
       </c>
       <c r="C239">
-        <v>-1.271593184220991</v>
+        <v>1.271593184220991</v>
       </c>
       <c r="D239">
         <v>0.4882800486159031</v>
@@ -7697,7 +7697,7 @@
         <v>2027</v>
       </c>
       <c r="C240">
-        <v>-0.325534483365681</v>
+        <v>0.325534483365681</v>
       </c>
       <c r="D240">
         <v>0.4637325673286133</v>
@@ -7729,7 +7729,7 @@
         <v>2028</v>
       </c>
       <c r="C241">
-        <v>-1.035309147269162</v>
+        <v>1.035309147269162</v>
       </c>
       <c r="D241">
         <v>0.4870358695095186</v>
@@ -7761,7 +7761,7 @@
         <v>2024</v>
       </c>
       <c r="C242">
-        <v>-1.152154724000378</v>
+        <v>1.152154724000378</v>
       </c>
       <c r="D242">
         <v>0.4822207328391058</v>
@@ -7790,7 +7790,7 @@
         <v>2025</v>
       </c>
       <c r="C243">
-        <v>0.1585870506495886</v>
+        <v>-0.1585870506495886</v>
       </c>
       <c r="D243">
         <v>-0.1085030883037783</v>
@@ -7819,7 +7819,7 @@
         <v>2026</v>
       </c>
       <c r="C244">
-        <v>-1.271579988056088</v>
+        <v>1.271579988056088</v>
       </c>
       <c r="D244">
         <v>0.237222868842244</v>
@@ -7848,7 +7848,7 @@
         <v>2027</v>
       </c>
       <c r="C245">
-        <v>-0.3255227454759341</v>
+        <v>0.3255227454759341</v>
       </c>
       <c r="D245">
         <v>0.1528286417794209</v>
@@ -7877,7 +7877,7 @@
         <v>2028</v>
       </c>
       <c r="C246">
-        <v>-1.035294648697244</v>
+        <v>1.035294648697244</v>
       </c>
       <c r="D246">
         <v>0.2447653291186256</v>
@@ -7906,7 +7906,7 @@
         <v>2024</v>
       </c>
       <c r="C247">
-        <v>-1.152164011075168</v>
+        <v>1.152164011075168</v>
       </c>
       <c r="D247">
         <v>0.09110526759126553</v>
@@ -7938,7 +7938,7 @@
         <v>2025</v>
       </c>
       <c r="C248">
-        <v>0.1585784589738213</v>
+        <v>-0.1585784589738213</v>
       </c>
       <c r="D248">
         <v>-0.04804355429191721</v>
@@ -7970,7 +7970,7 @@
         <v>2026</v>
       </c>
       <c r="C249">
-        <v>-1.271593217444132</v>
+        <v>1.271593217444132</v>
       </c>
       <c r="D249">
         <v>0.008055397518450851</v>
@@ -8002,7 +8002,7 @@
         <v>2027</v>
       </c>
       <c r="C250">
-        <v>-0.3255345711216214</v>
+        <v>0.3255345711216214</v>
       </c>
       <c r="D250">
         <v>0.01123551315814546</v>
@@ -8034,7 +8034,7 @@
         <v>2028</v>
       </c>
       <c r="C251">
-        <v>-1.035309233587003</v>
+        <v>1.035309233587003</v>
       </c>
       <c r="D251">
         <v>0.08991979652304458</v>
@@ -8066,7 +8066,7 @@
         <v>2024</v>
       </c>
       <c r="C252">
-        <v>-1.152165018603741</v>
+        <v>0</v>
       </c>
       <c r="D252">
         <v>0.4036078685033545</v>
@@ -8098,7 +8098,7 @@
         <v>2025</v>
       </c>
       <c r="C253">
-        <v>0.1585800148646939</v>
+        <v>0</v>
       </c>
       <c r="D253">
         <v>0.4486881125773106</v>
@@ -8130,7 +8130,7 @@
         <v>2026</v>
       </c>
       <c r="C254">
-        <v>-1.271592887638318</v>
+        <v>0</v>
       </c>
       <c r="D254">
         <v>0.5520659425573216</v>
@@ -8162,7 +8162,7 @@
         <v>2027</v>
       </c>
       <c r="C255">
-        <v>-0.3255337406011934</v>
+        <v>0</v>
       </c>
       <c r="D255">
         <v>0.5273521163938438</v>
@@ -8194,7 +8194,7 @@
         <v>2028</v>
       </c>
       <c r="C256">
-        <v>-1.035308411486484</v>
+        <v>0</v>
       </c>
       <c r="D256">
         <v>0.5428561851305856</v>
@@ -8226,7 +8226,7 @@
         <v>2024</v>
       </c>
       <c r="C257">
-        <v>-1.152163730450144</v>
+        <v>0</v>
       </c>
       <c r="E257">
         <v>1.146477353031271</v>
@@ -8255,7 +8255,7 @@
         <v>2025</v>
       </c>
       <c r="C258">
-        <v>0.1585780348993849</v>
+        <v>0</v>
       </c>
       <c r="E258">
         <v>0.08740133035770066</v>
@@ -8284,7 +8284,7 @@
         <v>2026</v>
       </c>
       <c r="C259">
-        <v>-1.271593302716489</v>
+        <v>0</v>
       </c>
       <c r="E259">
         <v>0.1140246068019335</v>
@@ -8313,7 +8313,7 @@
         <v>2027</v>
       </c>
       <c r="C260">
-        <v>-0.3255347945574253</v>
+        <v>0</v>
       </c>
       <c r="E260">
         <v>0.1357279685831456</v>
@@ -8342,7 +8342,7 @@
         <v>2028</v>
       </c>
       <c r="C261">
-        <v>-1.035309453591524</v>
+        <v>0</v>
       </c>
       <c r="E261">
         <v>0.198899129365429</v>
@@ -8406,7 +8406,7 @@
         <v>-0.7792648674812075</v>
       </c>
       <c r="H263">
-        <v>4.364206288370003</v>
+        <v>4</v>
       </c>
       <c r="I263">
         <v>0.2938871844034385</v>
@@ -8501,7 +8501,7 @@
         <v>2024</v>
       </c>
       <c r="C267">
-        <v>-1.146955847998403</v>
+        <v>0</v>
       </c>
       <c r="D267">
         <v>-0.2460788454442369</v>
@@ -8530,7 +8530,7 @@
         <v>2025</v>
       </c>
       <c r="C268">
-        <v>0.1580415209931619</v>
+        <v>0</v>
       </c>
       <c r="D268">
         <v>-0.2852317998279109</v>
@@ -8559,7 +8559,7 @@
         <v>2026</v>
       </c>
       <c r="C269">
-        <v>-1.26826755162176</v>
+        <v>0</v>
       </c>
       <c r="D269">
         <v>-0.5549351713803861</v>
@@ -8588,7 +8588,7 @@
         <v>2027</v>
       </c>
       <c r="C270">
-        <v>-0.3236060296024513</v>
+        <v>0</v>
       </c>
       <c r="D270">
         <v>-0.2541685029929733</v>
@@ -8617,7 +8617,7 @@
         <v>2028</v>
       </c>
       <c r="C271">
-        <v>-1.032542007741758</v>
+        <v>0</v>
       </c>
       <c r="D271">
         <v>-0.37975699100371</v>
@@ -8806,7 +8806,7 @@
         <v>2024</v>
       </c>
       <c r="C277">
-        <v>-0.3546775601134055</v>
+        <v>0</v>
       </c>
       <c r="D277">
         <v>-0.2632979273962857</v>
@@ -8832,7 +8832,7 @@
         <v>2025</v>
       </c>
       <c r="C278">
-        <v>0.9599052073191606</v>
+        <v>0</v>
       </c>
       <c r="D278">
         <v>-0.6532510246550726</v>
@@ -8858,7 +8858,7 @@
         <v>2026</v>
       </c>
       <c r="C279">
-        <v>-0.1920997232493371</v>
+        <v>0</v>
       </c>
       <c r="D279">
         <v>-0.6358271221281638</v>
@@ -8884,7 +8884,7 @@
         <v>2027</v>
       </c>
       <c r="C280">
-        <v>0.6886986454965232</v>
+        <v>0</v>
       </c>
       <c r="D280">
         <v>-0.6283263002972828</v>
@@ -8910,7 +8910,7 @@
         <v>2028</v>
       </c>
       <c r="C281">
-        <v>0.1958226225804214</v>
+        <v>0</v>
       </c>
       <c r="D281">
         <v>-0.5029886608419036</v>
@@ -8936,7 +8936,7 @@
         <v>2024</v>
       </c>
       <c r="C282">
-        <v>-0.3546848221899044</v>
+        <v>0</v>
       </c>
       <c r="D282">
         <v>-0.05479659985263602</v>
@@ -8965,7 +8965,7 @@
         <v>2025</v>
       </c>
       <c r="C283">
-        <v>0.9599123439184676</v>
+        <v>0</v>
       </c>
       <c r="D283">
         <v>-0.3920945473934559</v>
@@ -8994,7 +8994,7 @@
         <v>2026</v>
       </c>
       <c r="C284">
-        <v>-0.1920984196295002</v>
+        <v>0</v>
       </c>
       <c r="D284">
         <v>-0.3332440812918698</v>
@@ -9023,7 +9023,7 @@
         <v>2027</v>
       </c>
       <c r="C285">
-        <v>0.6887018658812636</v>
+        <v>0</v>
       </c>
       <c r="D285">
         <v>-0.3177808678052742</v>
@@ -9052,7 +9052,7 @@
         <v>2028</v>
       </c>
       <c r="C286">
-        <v>0.1958259544993768</v>
+        <v>0</v>
       </c>
       <c r="D286">
         <v>-0.2074956207228518</v>
@@ -9226,7 +9226,7 @@
         <v>2024</v>
       </c>
       <c r="C292">
-        <v>-0.3546886352946686</v>
+        <v>0.3546886352946686</v>
       </c>
       <c r="D292">
         <v>0.1309980045402227</v>
@@ -9249,7 +9249,7 @@
         <v>2025</v>
       </c>
       <c r="C293">
-        <v>0.9599160896162612</v>
+        <v>-0.9599160896162612</v>
       </c>
       <c r="D293">
         <v>-0.1088940169117601</v>
@@ -9272,7 +9272,7 @@
         <v>2026</v>
       </c>
       <c r="C294">
-        <v>-0.1920977363485533</v>
+        <v>0.1920977363485533</v>
       </c>
       <c r="D294">
         <v>-0.1235038420638694</v>
@@ -9295,7 +9295,7 @@
         <v>2027</v>
       </c>
       <c r="C295">
-        <v>0.688703555469933</v>
+        <v>-0.688703555469933</v>
       </c>
       <c r="D295">
         <v>-0.1486079299826974</v>
@@ -9318,7 +9318,7 @@
         <v>2028</v>
       </c>
       <c r="C296">
-        <v>0.195827702424417</v>
+        <v>-0.195827702424417</v>
       </c>
       <c r="D296">
         <v>-0.06844672514524121</v>
@@ -9341,7 +9341,7 @@
         <v>2024</v>
       </c>
       <c r="C297">
-        <v>-0.3546873503964699</v>
+        <v>0.3546873503964699</v>
       </c>
       <c r="D297">
         <v>-0.1555019774090491</v>
@@ -9364,7 +9364,7 @@
         <v>2025</v>
       </c>
       <c r="C298">
-        <v>0.9599148264498172</v>
+        <v>-0.9599148264498172</v>
       </c>
       <c r="D298">
         <v>-0.3102849875039994</v>
@@ -9390,7 +9390,7 @@
         <v>2026</v>
       </c>
       <c r="C299">
-        <v>-0.1920979674019116</v>
+        <v>0.1920979674019116</v>
       </c>
       <c r="D299">
         <v>-0.1908865939935614</v>
@@ -9416,13 +9416,13 @@
         <v>2027</v>
       </c>
       <c r="C300">
-        <v>0.6887029852544044</v>
+        <v>-0.6887029852544044</v>
       </c>
       <c r="D300">
         <v>-0.1519896748104674</v>
       </c>
       <c r="E300">
-        <v>4.42305721840521</v>
+        <v>4</v>
       </c>
       <c r="F300">
         <v>-0.7634134801311431</v>
@@ -9442,13 +9442,13 @@
         <v>2028</v>
       </c>
       <c r="C301">
-        <v>0.1958271123961098</v>
+        <v>-0.1958271123961098</v>
       </c>
       <c r="D301">
         <v>-0.04653657703629086</v>
       </c>
       <c r="E301">
-        <v>4.885404973962261</v>
+        <v>4</v>
       </c>
       <c r="F301">
         <v>-0.7292025366037196</v>
@@ -9468,7 +9468,7 @@
         <v>2024</v>
       </c>
       <c r="C302">
-        <v>-0.3546882181659249</v>
+        <v>0</v>
       </c>
       <c r="D302">
         <v>0.00701674700249772</v>
@@ -9497,7 +9497,7 @@
         <v>2025</v>
       </c>
       <c r="C303">
-        <v>0.9599156841088958</v>
+        <v>0</v>
       </c>
       <c r="D303">
         <v>-0.204801039018747</v>
@@ -9526,7 +9526,7 @@
         <v>2026</v>
       </c>
       <c r="C304">
-        <v>-0.1920978076113195</v>
+        <v>0</v>
       </c>
       <c r="D304">
         <v>-0.130843738836234</v>
@@ -9555,7 +9555,7 @@
         <v>2027</v>
       </c>
       <c r="C305">
-        <v>0.6887033744242382</v>
+        <v>0</v>
       </c>
       <c r="D305">
         <v>-0.1164274055284571</v>
@@ -9584,7 +9584,7 @@
         <v>2028</v>
       </c>
       <c r="C306">
-        <v>0.195827515663842</v>
+        <v>0</v>
       </c>
       <c r="D306">
         <v>-0.02177240362511975</v>
@@ -9613,7 +9613,7 @@
         <v>2024</v>
       </c>
       <c r="C307">
-        <v>-0.06189145586890574</v>
+        <v>0.06189145586890574</v>
       </c>
       <c r="D307">
         <v>-0.132812436470571</v>
@@ -9642,7 +9642,7 @@
         <v>2025</v>
       </c>
       <c r="C308">
-        <v>0.7472018047410383</v>
+        <v>-0.7472018047410383</v>
       </c>
       <c r="D308">
         <v>-0.4265713565815958</v>
@@ -9671,7 +9671,7 @@
         <v>2026</v>
       </c>
       <c r="C309">
-        <v>0.01528893977183678</v>
+        <v>-0.01528893977183678</v>
       </c>
       <c r="D309">
         <v>-0.3794977943124221</v>
@@ -9700,7 +9700,7 @@
         <v>2027</v>
       </c>
       <c r="C310">
-        <v>0.6989817208256859</v>
+        <v>-0.6989817208256859</v>
       </c>
       <c r="D310">
         <v>-0.3640528609748131</v>
@@ -9729,7 +9729,7 @@
         <v>2028</v>
       </c>
       <c r="C311">
-        <v>0.2887619339783684</v>
+        <v>-0.2887619339783684</v>
       </c>
       <c r="D311">
         <v>-0.2508376519291859</v>
@@ -9758,7 +9758,7 @@
         <v>2024</v>
       </c>
       <c r="C312">
-        <v>-0.06189694880031207</v>
+        <v>0</v>
       </c>
       <c r="D312">
         <v>0.5285495039888873</v>
@@ -9787,7 +9787,7 @@
         <v>2025</v>
       </c>
       <c r="C313">
-        <v>0.7472386375960139</v>
+        <v>0</v>
       </c>
       <c r="D313">
         <v>0.05600992984155081</v>
@@ -9816,7 +9816,7 @@
         <v>2026</v>
       </c>
       <c r="C314">
-        <v>0.01530064019369592</v>
+        <v>0</v>
       </c>
       <c r="D314">
         <v>0.4201197268078312</v>
@@ -9845,7 +9845,7 @@
         <v>2027</v>
       </c>
       <c r="C315">
-        <v>0.6990090467581542</v>
+        <v>0</v>
       </c>
       <c r="D315">
         <v>0.3047397760932014</v>
@@ -9874,7 +9874,7 @@
         <v>2028</v>
       </c>
       <c r="C316">
-        <v>0.2887866919958648</v>
+        <v>0</v>
       </c>
       <c r="D316">
         <v>0.3883235633501434</v>
@@ -9903,7 +9903,7 @@
         <v>2024</v>
       </c>
       <c r="C317">
-        <v>-0.06189766057947138</v>
+        <v>0</v>
       </c>
       <c r="E317">
         <v>0.2678419192886509</v>
@@ -9929,7 +9929,7 @@
         <v>2025</v>
       </c>
       <c r="C318">
-        <v>0.7472398702544869</v>
+        <v>0</v>
       </c>
       <c r="E318">
         <v>-0.7445046194769696</v>
@@ -9955,7 +9955,7 @@
         <v>2026</v>
       </c>
       <c r="C319">
-        <v>0.01530049990293979</v>
+        <v>0</v>
       </c>
       <c r="E319">
         <v>-0.4908362980454941</v>
@@ -9981,7 +9981,7 @@
         <v>2027</v>
       </c>
       <c r="C320">
-        <v>0.6990096904110152</v>
+        <v>0</v>
       </c>
       <c r="E320">
         <v>-0.6559162175902278</v>
@@ -10007,7 +10007,7 @@
         <v>2028</v>
       </c>
       <c r="C321">
-        <v>0.2887870765143793</v>
+        <v>0</v>
       </c>
       <c r="E321">
         <v>-0.6378981008328886</v>
@@ -10033,7 +10033,7 @@
         <v>2024</v>
       </c>
       <c r="C322">
-        <v>-0.06189349711831025</v>
+        <v>0</v>
       </c>
       <c r="D322">
         <v>-0.4000807513277897</v>
@@ -10062,7 +10062,7 @@
         <v>2025</v>
       </c>
       <c r="C323">
-        <v>0.7472326861011171</v>
+        <v>0</v>
       </c>
       <c r="D323">
         <v>-0.7641331701339897</v>
@@ -10091,7 +10091,7 @@
         <v>2026</v>
       </c>
       <c r="C324">
-        <v>0.01530133276317559</v>
+        <v>0</v>
       </c>
       <c r="D324">
         <v>-0.7995706504267749</v>
@@ -10120,7 +10120,7 @@
         <v>2027</v>
       </c>
       <c r="C325">
-        <v>0.6990059468261403</v>
+        <v>0</v>
       </c>
       <c r="D325">
         <v>-0.7947640017601144</v>
@@ -10149,7 +10149,7 @@
         <v>2028</v>
       </c>
       <c r="C326">
-        <v>0.2887848481767268</v>
+        <v>0</v>
       </c>
       <c r="D326">
         <v>-0.6673140833035137</v>
@@ -10178,7 +10178,7 @@
         <v>2024</v>
       </c>
       <c r="C327">
-        <v>0.1575175840586515</v>
+        <v>-0.1575175840586515</v>
       </c>
       <c r="D327">
         <v>-0.137163502918218</v>
@@ -10204,7 +10204,7 @@
         <v>2025</v>
       </c>
       <c r="C328">
-        <v>0.131903718104925</v>
+        <v>-0.131903718104925</v>
       </c>
       <c r="D328">
         <v>-0.4143210752229421</v>
@@ -10230,7 +10230,7 @@
         <v>2026</v>
       </c>
       <c r="C329">
-        <v>-0.2803652221286117</v>
+        <v>0.2803652221286117</v>
       </c>
       <c r="D329">
         <v>-0.3680493498712363</v>
@@ -10256,7 +10256,7 @@
         <v>2027</v>
       </c>
       <c r="C330">
-        <v>0.2252471902723071</v>
+        <v>-0.2252471902723071</v>
       </c>
       <c r="D330">
         <v>-0.3522246164229046</v>
@@ -10282,7 +10282,7 @@
         <v>2028</v>
       </c>
       <c r="C331">
-        <v>-0.192602925280849</v>
+        <v>0.192602925280849</v>
       </c>
       <c r="D331">
         <v>-0.2397652644069906</v>
@@ -10308,7 +10308,7 @@
         <v>2024</v>
       </c>
       <c r="C332">
-        <v>-0.07131978006391339</v>
+        <v>0</v>
       </c>
       <c r="D332">
         <v>0.4911023872868351</v>
@@ -10337,7 +10337,7 @@
         <v>2025</v>
       </c>
       <c r="C333">
-        <v>-0.4105288247385306</v>
+        <v>0</v>
       </c>
       <c r="D333">
         <v>-0.06368054659255021</v>
@@ -10366,7 +10366,7 @@
         <v>2026</v>
       </c>
       <c r="C334">
-        <v>-0.3060351001918819</v>
+        <v>0</v>
       </c>
       <c r="D334">
         <v>0.2335473618110336</v>
@@ -10395,7 +10395,7 @@
         <v>2027</v>
       </c>
       <c r="C335">
-        <v>-0.3120333261858307</v>
+        <v>0</v>
       </c>
       <c r="D335">
         <v>0.1761921353335705</v>
@@ -10424,7 +10424,7 @@
         <v>2028</v>
       </c>
       <c r="C336">
-        <v>-0.4512837994879994</v>
+        <v>0</v>
       </c>
       <c r="D336">
         <v>0.2547560565971209</v>
@@ -10648,7 +10648,7 @@
         <v>-1.897249508038879</v>
       </c>
       <c r="H343">
-        <v>-4.495630070394976</v>
+        <v>-4</v>
       </c>
       <c r="I343">
         <v>0.4869875306290807</v>
@@ -10674,7 +10674,7 @@
         <v>-0.4373282402110962</v>
       </c>
       <c r="H344">
-        <v>-6.168540918348144</v>
+        <v>-4</v>
       </c>
       <c r="I344">
         <v>0.449600725522978</v>
@@ -10700,7 +10700,7 @@
         <v>-1.249261330884603</v>
       </c>
       <c r="H345">
-        <v>-9.046301327895389</v>
+        <v>-4</v>
       </c>
       <c r="I345">
         <v>0.4172965691500139</v>
@@ -10726,7 +10726,7 @@
         <v>-0.5153360670344571</v>
       </c>
       <c r="H346">
-        <v>-7.771770140335611</v>
+        <v>-4</v>
       </c>
       <c r="I346">
         <v>0.3992333864136749</v>
@@ -10743,7 +10743,7 @@
         <v>2024</v>
       </c>
       <c r="C347">
-        <v>-0.05754660453722318</v>
+        <v>0</v>
       </c>
       <c r="D347">
         <v>0.9684226188619766</v>
@@ -10772,7 +10772,7 @@
         <v>2025</v>
       </c>
       <c r="C348">
-        <v>0.3789930899291798</v>
+        <v>0</v>
       </c>
       <c r="D348">
         <v>2.463879320854912</v>
@@ -10801,7 +10801,7 @@
         <v>2026</v>
       </c>
       <c r="C349">
-        <v>-0.1340403331269377</v>
+        <v>0</v>
       </c>
       <c r="D349">
         <v>1.856305353354203</v>
@@ -10830,7 +10830,7 @@
         <v>2027</v>
       </c>
       <c r="C350">
-        <v>0.3950765231277864</v>
+        <v>0</v>
       </c>
       <c r="D350">
         <v>1.812016159042284</v>
@@ -10859,7 +10859,7 @@
         <v>2028</v>
       </c>
       <c r="C351">
-        <v>0.01258486855136728</v>
+        <v>0</v>
       </c>
       <c r="D351">
         <v>1.48192394800774</v>
@@ -10978,7 +10978,7 @@
         <v>0.6990081999829137</v>
       </c>
       <c r="D355">
-        <v>-4.077099585299362</v>
+        <v>-4</v>
       </c>
       <c r="E355">
         <v>-0.3942627855646049</v>
@@ -11007,7 +11007,7 @@
         <v>0.2887861872202474</v>
       </c>
       <c r="D356">
-        <v>-4.79218469308576</v>
+        <v>-4</v>
       </c>
       <c r="E356">
         <v>-0.3811268345346925</v>
@@ -11033,7 +11033,7 @@
         <v>2024</v>
       </c>
       <c r="C357">
-        <v>-0.06171493944594082</v>
+        <v>0</v>
       </c>
       <c r="D357">
         <v>-0.7481629067490807</v>
@@ -11065,7 +11065,7 @@
         <v>2025</v>
       </c>
       <c r="C358">
-        <v>0.7250522394878656</v>
+        <v>0</v>
       </c>
       <c r="D358">
         <v>-1.377610838402408</v>
@@ -11097,7 +11097,7 @@
         <v>2026</v>
       </c>
       <c r="C359">
-        <v>0.00466382779623142</v>
+        <v>0</v>
       </c>
       <c r="D359">
         <v>-1.45601763214355</v>
@@ -11129,7 +11129,7 @@
         <v>2027</v>
       </c>
       <c r="C360">
-        <v>0.6807663929411063</v>
+        <v>0</v>
       </c>
       <c r="D360">
         <v>-1.526893846396458</v>
@@ -11161,7 +11161,7 @@
         <v>2028</v>
       </c>
       <c r="C361">
-        <v>0.2709083016046843</v>
+        <v>0</v>
       </c>
       <c r="D361">
         <v>-1.425289497286911</v>
@@ -11818,7 +11818,7 @@
         <v>2024</v>
       </c>
       <c r="C382">
-        <v>0.4997490561677623</v>
+        <v>0</v>
       </c>
       <c r="D382">
         <v>-0.4862903142958571</v>
@@ -11847,7 +11847,7 @@
         <v>2025</v>
       </c>
       <c r="C383">
-        <v>1.254385803989091</v>
+        <v>0</v>
       </c>
       <c r="D383">
         <v>-0.784127340582465</v>
@@ -11876,7 +11876,7 @@
         <v>2026</v>
       </c>
       <c r="C384">
-        <v>0.9716871447649108</v>
+        <v>0</v>
       </c>
       <c r="D384">
         <v>-0.8718649082345524</v>
@@ -11905,7 +11905,7 @@
         <v>2027</v>
       </c>
       <c r="C385">
-        <v>1.443350324337433</v>
+        <v>0</v>
       </c>
       <c r="D385">
         <v>-0.8592166649287979</v>
@@ -11934,7 +11934,7 @@
         <v>2028</v>
       </c>
       <c r="C386">
-        <v>1.281652235660809</v>
+        <v>0</v>
       </c>
       <c r="D386">
         <v>-0.7345741848661189</v>
@@ -12223,7 +12223,7 @@
         <v>2024</v>
       </c>
       <c r="C397">
-        <v>-0.2104791659730084</v>
+        <v>0</v>
       </c>
       <c r="D397">
         <v>-0.3298100244717888</v>
@@ -12252,7 +12252,7 @@
         <v>2025</v>
       </c>
       <c r="C398">
-        <v>1.28176206537711</v>
+        <v>0</v>
       </c>
       <c r="D398">
         <v>-0.6998213804552422</v>
@@ -12281,7 +12281,7 @@
         <v>2026</v>
       </c>
       <c r="C399">
-        <v>0.2756570865699149</v>
+        <v>0</v>
       </c>
       <c r="D399">
         <v>-0.7118792920353226</v>
@@ -12310,7 +12310,7 @@
         <v>2027</v>
       </c>
       <c r="C400">
-        <v>1.10126157690241</v>
+        <v>0</v>
       </c>
       <c r="D400">
         <v>-0.7035009583545001</v>
@@ -12339,7 +12339,7 @@
         <v>2028</v>
       </c>
       <c r="C401">
-        <v>0.7085974595858965</v>
+        <v>0</v>
       </c>
       <c r="D401">
         <v>-0.5771980769422332</v>
@@ -12368,7 +12368,7 @@
         <v>2024</v>
       </c>
       <c r="C402">
-        <v>-0.2447444600108794</v>
+        <v>0</v>
       </c>
       <c r="D402">
         <v>-0.1413531294406964</v>
@@ -12397,7 +12397,7 @@
         <v>2025</v>
       </c>
       <c r="C403">
-        <v>1.255074716135825</v>
+        <v>0</v>
       </c>
       <c r="D403">
         <v>-0.4463008478369702</v>
@@ -12426,7 +12426,7 @@
         <v>2026</v>
       </c>
       <c r="C404">
-        <v>0.2288038436131748</v>
+        <v>0</v>
       </c>
       <c r="D404">
         <v>-0.4041033144774787</v>
@@ -12455,7 +12455,7 @@
         <v>2027</v>
       </c>
       <c r="C405">
-        <v>1.061184340618879</v>
+        <v>0</v>
       </c>
       <c r="D405">
         <v>-0.3893729634050528</v>
@@ -12484,7 +12484,7 @@
         <v>2028</v>
       </c>
       <c r="C406">
-        <v>0.6584038432886126</v>
+        <v>0</v>
       </c>
       <c r="D406">
         <v>-0.2746940266108021</v>
@@ -12513,7 +12513,7 @@
         <v>2024</v>
       </c>
       <c r="C407">
-        <v>0.3907049501702132</v>
+        <v>-0.3907049501702132</v>
       </c>
       <c r="D407">
         <v>-0.5200254859195369</v>
@@ -12542,7 +12542,7 @@
         <v>2025</v>
       </c>
       <c r="C408">
-        <v>1.53595716048429</v>
+        <v>-1.53595716048429</v>
       </c>
       <c r="D408">
         <v>-3.576748623930492</v>
@@ -12571,7 +12571,7 @@
         <v>2026</v>
       </c>
       <c r="C409">
-        <v>0.9985024861317284</v>
+        <v>-0.9985024861317284</v>
       </c>
       <c r="D409">
         <v>-3.148513178645466</v>
@@ -12600,10 +12600,10 @@
         <v>2027</v>
       </c>
       <c r="C410">
-        <v>1.628844043620007</v>
+        <v>-1.628844043620007</v>
       </c>
       <c r="D410">
-        <v>-4.759849296850883</v>
+        <v>-4</v>
       </c>
       <c r="E410">
         <v>0.1146704843351792</v>
@@ -12629,10 +12629,10 @@
         <v>2028</v>
       </c>
       <c r="C411">
-        <v>1.418326227528234</v>
+        <v>-1.418326227528234</v>
       </c>
       <c r="D411">
-        <v>-5.261664714365435</v>
+        <v>-4</v>
       </c>
       <c r="E411">
         <v>0.17558962866608</v>
@@ -12658,7 +12658,7 @@
         <v>2024</v>
       </c>
       <c r="C412">
-        <v>0.418902834756269</v>
+        <v>-0.418902834756269</v>
       </c>
       <c r="D412">
         <v>0.1640120421538298</v>
@@ -12687,7 +12687,7 @@
         <v>2025</v>
       </c>
       <c r="C413">
-        <v>1.542554414356124</v>
+        <v>-1.542554414356124</v>
       </c>
       <c r="D413">
         <v>0.129867913995527</v>
@@ -12716,7 +12716,7 @@
         <v>2026</v>
       </c>
       <c r="C414">
-        <v>1.031867485712269</v>
+        <v>-1.031867485712269</v>
       </c>
       <c r="D414">
         <v>0.2140960873353699</v>
@@ -12745,7 +12745,7 @@
         <v>2027</v>
       </c>
       <c r="C415">
-        <v>1.649251120546072</v>
+        <v>-1.649251120546072</v>
       </c>
       <c r="D415">
         <v>0.2172120350764753</v>
@@ -12774,7 +12774,7 @@
         <v>2028</v>
       </c>
       <c r="C416">
-        <v>1.448734708636029</v>
+        <v>-1.448734708636029</v>
       </c>
       <c r="D416">
         <v>0.275935501956751</v>
@@ -12803,7 +12803,7 @@
         <v>2024</v>
       </c>
       <c r="C417">
-        <v>-0.2789019318022481</v>
+        <v>0</v>
       </c>
       <c r="E417">
         <v>0.697687783662388</v>
@@ -12826,7 +12826,7 @@
         <v>2025</v>
       </c>
       <c r="C418">
-        <v>1.225986167287583</v>
+        <v>0</v>
       </c>
       <c r="E418">
         <v>-0.04836166902281348</v>
@@ -12849,7 +12849,7 @@
         <v>2026</v>
       </c>
       <c r="C419">
-        <v>0.1804278351426863</v>
+        <v>0</v>
       </c>
       <c r="E419">
         <v>-0.9288038615291568</v>
@@ -12872,7 +12872,7 @@
         <v>2027</v>
       </c>
       <c r="C420">
-        <v>1.019123284386551</v>
+        <v>0</v>
       </c>
       <c r="E420">
         <v>-0.283512388864946</v>
@@ -12895,7 +12895,7 @@
         <v>2028</v>
       </c>
       <c r="C421">
-        <v>0.6060216641066364</v>
+        <v>0</v>
       </c>
       <c r="E421">
         <v>-0.9234740989426484</v>
@@ -13063,7 +13063,7 @@
         <v>2024</v>
       </c>
       <c r="C427">
-        <v>-1.041374039963504</v>
+        <v>0</v>
       </c>
       <c r="D427">
         <v>0.1985533881515423</v>
@@ -13092,7 +13092,7 @@
         <v>2025</v>
       </c>
       <c r="C428">
-        <v>-0.3471524700690548</v>
+        <v>0</v>
       </c>
       <c r="D428">
         <v>0.1726306237701127</v>
@@ -13121,7 +13121,7 @@
         <v>2026</v>
       </c>
       <c r="C429">
-        <v>-1.546686625261616</v>
+        <v>0</v>
       </c>
       <c r="D429">
         <v>0.2557384755809512</v>
@@ -13150,7 +13150,7 @@
         <v>2027</v>
       </c>
       <c r="C430">
-        <v>-0.7202539161405412</v>
+        <v>0</v>
       </c>
       <c r="D430">
         <v>0.256140121298071</v>
@@ -13179,7 +13179,7 @@
         <v>2028</v>
       </c>
       <c r="C431">
-        <v>-1.455912130681274</v>
+        <v>0</v>
       </c>
       <c r="D431">
         <v>0.309878624724262</v>
@@ -14078,7 +14078,7 @@
         <v>2024</v>
       </c>
       <c r="C462">
-        <v>-1.041354968101999</v>
+        <v>0</v>
       </c>
       <c r="D462">
         <v>0.4631642208885794</v>
@@ -14107,7 +14107,7 @@
         <v>2025</v>
       </c>
       <c r="C463">
-        <v>-0.3471522281689525</v>
+        <v>0</v>
       </c>
       <c r="D463">
         <v>-0.07203378191716737</v>
@@ -14136,7 +14136,7 @@
         <v>2026</v>
       </c>
       <c r="C464">
-        <v>-1.546666967684892</v>
+        <v>0</v>
       </c>
       <c r="D464">
         <v>0.2638210986004554</v>
@@ -14165,7 +14165,7 @@
         <v>2027</v>
       </c>
       <c r="C465">
-        <v>-0.7202438051794277</v>
+        <v>0</v>
       </c>
       <c r="D465">
         <v>0.1776889904425938</v>
@@ -14194,7 +14194,7 @@
         <v>2028</v>
       </c>
       <c r="C466">
-        <v>-1.455895613064264</v>
+        <v>0</v>
       </c>
       <c r="D466">
         <v>0.2679254051266858</v>
@@ -14223,7 +14223,7 @@
         <v>2024</v>
       </c>
       <c r="C467">
-        <v>-0.2788991676936826</v>
+        <v>0</v>
       </c>
       <c r="E467">
         <v>-1.376679986269924</v>
@@ -14249,7 +14249,7 @@
         <v>2025</v>
       </c>
       <c r="C468">
-        <v>1.225983007888353</v>
+        <v>0</v>
       </c>
       <c r="E468">
         <v>0.1766974447190646</v>
@@ -14275,7 +14275,7 @@
         <v>2026</v>
       </c>
       <c r="C469">
-        <v>0.1804277743713768</v>
+        <v>0</v>
       </c>
       <c r="E469">
         <v>0.6593106708924349</v>
@@ -14301,7 +14301,7 @@
         <v>2027</v>
       </c>
       <c r="C470">
-        <v>1.019121953599269</v>
+        <v>0</v>
       </c>
       <c r="E470">
         <v>0.5499068386479253</v>
@@ -14327,7 +14327,7 @@
         <v>2028</v>
       </c>
       <c r="C471">
-        <v>0.6060205147665808</v>
+        <v>0</v>
       </c>
       <c r="E471">
         <v>0.7411991398545243</v>
@@ -14468,7 +14468,7 @@
         <v>2024</v>
       </c>
       <c r="C477">
-        <v>-1.041373544409566</v>
+        <v>0</v>
       </c>
       <c r="D477">
         <v>-0.1430482539134869</v>
@@ -14497,7 +14497,7 @@
         <v>2025</v>
       </c>
       <c r="C478">
-        <v>-0.3471531963128006</v>
+        <v>0</v>
       </c>
       <c r="D478">
         <v>-0.4244266280178697</v>
@@ -14526,7 +14526,7 @@
         <v>2026</v>
       </c>
       <c r="C479">
-        <v>-1.546686450963884</v>
+        <v>0</v>
       </c>
       <c r="D479">
         <v>-0.3781375084923565</v>
@@ -14555,7 +14555,7 @@
         <v>2027</v>
       </c>
       <c r="C480">
-        <v>-0.7202542506990343</v>
+        <v>0</v>
       </c>
       <c r="D480">
         <v>-0.362623313177424</v>
@@ -14584,7 +14584,7 @@
         <v>2028</v>
       </c>
       <c r="C481">
-        <v>-1.455912280040237</v>
+        <v>0</v>
       </c>
       <c r="D481">
         <v>-0.2494983674114094</v>
@@ -14613,7 +14613,7 @@
         <v>2024</v>
       </c>
       <c r="C482">
-        <v>-1.001718609113401</v>
+        <v>1.001718609113401</v>
       </c>
       <c r="D482">
         <v>0.08974667631447619</v>
@@ -14642,7 +14642,7 @@
         <v>2025</v>
       </c>
       <c r="C483">
-        <v>-0.3638261443821199</v>
+        <v>0.3638261443821199</v>
       </c>
       <c r="D483">
         <v>0.03084154888341087</v>
@@ -14671,7 +14671,7 @@
         <v>2026</v>
       </c>
       <c r="C484">
-        <v>-1.507248823090964</v>
+        <v>1.507248823090964</v>
       </c>
       <c r="D484">
         <v>0.1163917094393282</v>
@@ -14700,7 +14700,7 @@
         <v>2027</v>
       </c>
       <c r="C485">
-        <v>-0.7115811950404036</v>
+        <v>0.7115811950404036</v>
       </c>
       <c r="D485">
         <v>0.1249742440615689</v>
@@ -14729,7 +14729,7 @@
         <v>2028</v>
       </c>
       <c r="C486">
-        <v>-1.430267320304949</v>
+        <v>1.430267320304949</v>
       </c>
       <c r="D486">
         <v>0.1948499039537607</v>
@@ -14933,7 +14933,7 @@
         <v>0.03061826176176649</v>
       </c>
       <c r="H492">
-        <v>-5.949175731768699</v>
+        <v>-4</v>
       </c>
       <c r="I492">
         <v>1.734938921487315</v>
@@ -15273,7 +15273,7 @@
         <v>-1.990046356074535</v>
       </c>
       <c r="F503">
-        <v>4.2872660518325</v>
+        <v>4</v>
       </c>
       <c r="G503">
         <v>0.2955115183361229</v>
@@ -15331,7 +15331,7 @@
         <v>-2.406722736948001</v>
       </c>
       <c r="F505">
-        <v>4.669875444613253</v>
+        <v>4</v>
       </c>
       <c r="G505">
         <v>-0.2058767139220488</v>
@@ -15383,7 +15383,7 @@
         <v>2024</v>
       </c>
       <c r="C507">
-        <v>-0.6582725800831793</v>
+        <v>0</v>
       </c>
       <c r="D507">
         <v>-1.281689653021671</v>
@@ -15409,7 +15409,7 @@
         <v>2025</v>
       </c>
       <c r="C508">
-        <v>-0.6035261959870231</v>
+        <v>0</v>
       </c>
       <c r="D508">
         <v>-1.868410818888078</v>
@@ -15424,7 +15424,7 @@
         <v>1.184060107504061</v>
       </c>
       <c r="J508">
-        <v>4.183917555134073</v>
+        <v>4</v>
       </c>
     </row>
     <row r="509">
@@ -15435,7 +15435,7 @@
         <v>2026</v>
       </c>
       <c r="C509">
-        <v>-1.081649873085979</v>
+        <v>0</v>
       </c>
       <c r="D509">
         <v>-3.217832970363197</v>
@@ -15461,7 +15461,7 @@
         <v>2027</v>
       </c>
       <c r="C510">
-        <v>-0.739033786337035</v>
+        <v>0</v>
       </c>
       <c r="D510">
         <v>-2.820552669190653</v>
@@ -15487,7 +15487,7 @@
         <v>2028</v>
       </c>
       <c r="C511">
-        <v>-1.178787703689231</v>
+        <v>0</v>
       </c>
       <c r="D511">
         <v>-3.866627945399038</v>
@@ -15513,7 +15513,7 @@
         <v>2024</v>
       </c>
       <c r="C512">
-        <v>-0.1960889200224818</v>
+        <v>0</v>
       </c>
       <c r="D512">
         <v>0.05718872710814161</v>
@@ -15539,7 +15539,7 @@
         <v>2025</v>
       </c>
       <c r="C513">
-        <v>0.4621644484145809</v>
+        <v>0</v>
       </c>
       <c r="D513">
         <v>-1.37498389783332</v>
@@ -15565,7 +15565,7 @@
         <v>2026</v>
       </c>
       <c r="C514">
-        <v>-0.120983824943146</v>
+        <v>0</v>
       </c>
       <c r="D514">
         <v>-0.6729871075477422</v>
@@ -15591,7 +15591,7 @@
         <v>2027</v>
       </c>
       <c r="C515">
-        <v>0.425626746180805</v>
+        <v>0</v>
       </c>
       <c r="D515">
         <v>-1.126113169551672</v>
@@ -15617,7 +15617,7 @@
         <v>2028</v>
       </c>
       <c r="C516">
-        <v>0.04931624901211098</v>
+        <v>0</v>
       </c>
       <c r="D516">
         <v>-0.7595804671775358</v>
@@ -15788,7 +15788,7 @@
         <v>2024</v>
       </c>
       <c r="C522">
-        <v>-1.04135554914165</v>
+        <v>0</v>
       </c>
       <c r="D522">
         <v>0.4956667910731403</v>
@@ -15817,7 +15817,7 @@
         <v>2025</v>
       </c>
       <c r="C523">
-        <v>-0.3471513854828882</v>
+        <v>0</v>
       </c>
       <c r="D523">
         <v>-0.00437174650542883</v>
@@ -15826,7 +15826,7 @@
         <v>-0.2394850435259981</v>
       </c>
       <c r="F523">
-        <v>4.614377439091541</v>
+        <v>4</v>
       </c>
       <c r="G523">
         <v>-0.9543691492734184</v>
@@ -15846,7 +15846,7 @@
         <v>2026</v>
       </c>
       <c r="C524">
-        <v>-1.546667176123355</v>
+        <v>0</v>
       </c>
       <c r="D524">
         <v>0.2584923204892083</v>
@@ -15875,7 +15875,7 @@
         <v>2027</v>
       </c>
       <c r="C525">
-        <v>-0.7202434201141755</v>
+        <v>0</v>
       </c>
       <c r="D525">
         <v>0.2148807702511127</v>
@@ -15904,7 +15904,7 @@
         <v>2028</v>
       </c>
       <c r="C526">
-        <v>-1.455895444930595</v>
+        <v>0</v>
       </c>
       <c r="D526">
         <v>0.2837411911412661</v>
@@ -15933,7 +15933,7 @@
         <v>2024</v>
       </c>
       <c r="C527">
-        <v>0.989403347350434</v>
+        <v>0</v>
       </c>
       <c r="D527">
         <v>-0.9731106511540482</v>
@@ -15962,7 +15962,7 @@
         <v>2025</v>
       </c>
       <c r="C528">
-        <v>-1.280130150380554</v>
+        <v>0</v>
       </c>
       <c r="D528">
         <v>-2.492816361925119</v>
@@ -15991,7 +15991,7 @@
         <v>2026</v>
       </c>
       <c r="C529">
-        <v>0.7350624791353679</v>
+        <v>0</v>
       </c>
       <c r="D529">
         <v>-3.017783419312421</v>
@@ -16020,7 +16020,7 @@
         <v>2027</v>
       </c>
       <c r="C530">
-        <v>-0.7904805203893323</v>
+        <v>0</v>
       </c>
       <c r="D530">
         <v>-3.56283532116078</v>
@@ -16049,7 +16049,7 @@
         <v>2028</v>
       </c>
       <c r="C531">
-        <v>0.118518025816767</v>
+        <v>0</v>
       </c>
       <c r="D531">
         <v>-3.987681617073627</v>
@@ -16078,7 +16078,7 @@
         <v>2024</v>
       </c>
       <c r="C532">
-        <v>-0.3620895859474955</v>
+        <v>0</v>
       </c>
       <c r="D532">
         <v>0.000488803286097361</v>
@@ -16104,7 +16104,7 @@
         <v>2025</v>
       </c>
       <c r="C533">
-        <v>-0.5549518765755149</v>
+        <v>0</v>
       </c>
       <c r="D533">
         <v>0.3185669847567315</v>
@@ -16130,7 +16130,7 @@
         <v>2026</v>
       </c>
       <c r="C534">
-        <v>-0.4638375354041045</v>
+        <v>0</v>
       </c>
       <c r="D534">
         <v>0.2870684411856502</v>
@@ -16156,7 +16156,7 @@
         <v>2027</v>
       </c>
       <c r="C535">
-        <v>-0.5846733424175397</v>
+        <v>0</v>
       </c>
       <c r="D535">
         <v>0.3126415125411612</v>
@@ -16182,7 +16182,7 @@
         <v>2028</v>
       </c>
       <c r="C536">
-        <v>-0.6282516591560869</v>
+        <v>0</v>
       </c>
       <c r="D536">
         <v>0.3533824167690783</v>
@@ -16208,7 +16208,7 @@
         <v>2024</v>
       </c>
       <c r="C537">
-        <v>-0.36819190031104</v>
+        <v>0</v>
       </c>
       <c r="D537">
         <v>0.1771673699927687</v>
@@ -16237,7 +16237,7 @@
         <v>2025</v>
       </c>
       <c r="C538">
-        <v>-0.5516106209459776</v>
+        <v>0</v>
       </c>
       <c r="D538">
         <v>0.5358080364979637</v>
@@ -16266,7 +16266,7 @@
         <v>2026</v>
       </c>
       <c r="C539">
-        <v>-0.4690229714022357</v>
+        <v>0</v>
       </c>
       <c r="D539">
         <v>0.741812660977202</v>
@@ -16295,7 +16295,7 @@
         <v>2027</v>
       </c>
       <c r="C540">
-        <v>-0.583950125211556</v>
+        <v>0</v>
       </c>
       <c r="D540">
         <v>0.7349690219512723</v>
@@ -16324,7 +16324,7 @@
         <v>2028</v>
       </c>
       <c r="C541">
-        <v>-0.6314268187311362</v>
+        <v>0</v>
       </c>
       <c r="D541">
         <v>0.724560238994996</v>
@@ -16353,7 +16353,7 @@
         <v>2024</v>
       </c>
       <c r="C542">
-        <v>-0.3681922423607815</v>
+        <v>0</v>
       </c>
       <c r="D542">
         <v>0.8732121434664762</v>
@@ -16382,7 +16382,7 @@
         <v>2025</v>
       </c>
       <c r="C543">
-        <v>-0.5516091700878436</v>
+        <v>0</v>
       </c>
       <c r="D543">
         <v>0.2681867944223036</v>
@@ -16411,7 +16411,7 @@
         <v>2026</v>
       </c>
       <c r="C544">
-        <v>-0.4690237859068595</v>
+        <v>0</v>
       </c>
       <c r="D544">
         <v>0.6175399858127244</v>
@@ -16440,7 +16440,7 @@
         <v>2027</v>
       </c>
       <c r="C545">
-        <v>-0.5839487313304292</v>
+        <v>0</v>
       </c>
       <c r="D545">
         <v>0.527858325681363</v>
@@ -16469,7 +16469,7 @@
         <v>2028</v>
       </c>
       <c r="C546">
-        <v>-0.6314270775142414</v>
+        <v>0</v>
       </c>
       <c r="D546">
         <v>0.5562633715300359</v>
@@ -16498,7 +16498,7 @@
         <v>2024</v>
       </c>
       <c r="C547">
-        <v>-0.3699027956149816</v>
+        <v>0</v>
       </c>
       <c r="D547">
         <v>-0.2178816085836021</v>
@@ -16527,7 +16527,7 @@
         <v>2025</v>
       </c>
       <c r="C548">
-        <v>-0.5377961551474587</v>
+        <v>0</v>
       </c>
       <c r="D548">
         <v>-0.3488947907330301</v>
@@ -16556,7 +16556,7 @@
         <v>2026</v>
       </c>
       <c r="C549">
-        <v>-0.463009176607561</v>
+        <v>0</v>
       </c>
       <c r="D549">
         <v>-0.2291468153609736</v>
@@ -16585,7 +16585,7 @@
         <v>2027</v>
       </c>
       <c r="C550">
-        <v>-0.5716219781029995</v>
+        <v>0</v>
       </c>
       <c r="D550">
         <v>-0.1960646902661316</v>
@@ -16614,7 +16614,7 @@
         <v>2028</v>
       </c>
       <c r="C551">
-        <v>-0.6211134169968058</v>
+        <v>0</v>
       </c>
       <c r="D551">
         <v>-0.09080522027441672</v>
@@ -16643,7 +16643,7 @@
         <v>2024</v>
       </c>
       <c r="C552">
-        <v>-0.3681917634798716</v>
+        <v>0</v>
       </c>
       <c r="D552">
         <v>-0.6843945258156162</v>
@@ -16672,7 +16672,7 @@
         <v>2025</v>
       </c>
       <c r="C553">
-        <v>-0.5516111325904768</v>
+        <v>0</v>
       </c>
       <c r="D553">
         <v>0.07269356577834429</v>
@@ -16701,7 +16701,7 @@
         <v>2026</v>
       </c>
       <c r="C554">
-        <v>-0.4690226594166957</v>
+        <v>0</v>
       </c>
       <c r="D554">
         <v>-0.2803455414282117</v>
@@ -16730,7 +16730,7 @@
         <v>2027</v>
       </c>
       <c r="C555">
-        <v>-0.5839506110822821</v>
+        <v>0</v>
       </c>
       <c r="D555">
         <v>-0.1537618853327898</v>
@@ -16759,7 +16759,7 @@
         <v>2028</v>
       </c>
       <c r="C556">
-        <v>-0.6314267058388676</v>
+        <v>0</v>
       </c>
       <c r="D556">
         <v>-0.08160997410194896</v>
@@ -16788,7 +16788,7 @@
         <v>2024</v>
       </c>
       <c r="C557">
-        <v>-0.5628674906069036</v>
+        <v>0</v>
       </c>
       <c r="E557">
         <v>-0.0009395205695678016</v>
@@ -16817,7 +16817,7 @@
         <v>2025</v>
       </c>
       <c r="C558">
-        <v>0.02365507827541835</v>
+        <v>0</v>
       </c>
       <c r="E558">
         <v>-0.4960857777948954</v>
@@ -16846,7 +16846,7 @@
         <v>2026</v>
       </c>
       <c r="C559">
-        <v>-0.4834316613108425</v>
+        <v>0</v>
       </c>
       <c r="E559">
         <v>-0.5050285223888903</v>
@@ -16875,7 +16875,7 @@
         <v>2027</v>
       </c>
       <c r="C560">
-        <v>-0.1165326002637551</v>
+        <v>0</v>
       </c>
       <c r="E560">
         <v>-0.5777574163873337</v>
@@ -16904,7 +16904,7 @@
         <v>2028</v>
       </c>
       <c r="C561">
-        <v>-0.4343913809643237</v>
+        <v>0</v>
       </c>
       <c r="E561">
         <v>-0.5815259619969051</v>
@@ -17253,7 +17253,7 @@
         <v>2024</v>
       </c>
       <c r="C572">
-        <v>-1.152164465063907</v>
+        <v>0</v>
       </c>
       <c r="D572">
         <v>-0.07002030511411801</v>
@@ -17285,7 +17285,7 @@
         <v>2025</v>
       </c>
       <c r="C573">
-        <v>0.1585791534404257</v>
+        <v>0</v>
       </c>
       <c r="D573">
         <v>-0.03344438660264489</v>
@@ -17317,7 +17317,7 @@
         <v>2026</v>
       </c>
       <c r="C574">
-        <v>-1.271593073526328</v>
+        <v>0</v>
       </c>
       <c r="D574">
         <v>-0.04736711593011866</v>
@@ -17349,7 +17349,7 @@
         <v>2027</v>
       </c>
       <c r="C575">
-        <v>-0.3255342025091247</v>
+        <v>0</v>
       </c>
       <c r="D575">
         <v>-0.00463005494541339</v>
@@ -17381,7 +17381,7 @@
         <v>2028</v>
       </c>
       <c r="C576">
-        <v>-1.03530886954197</v>
+        <v>0</v>
       </c>
       <c r="D576">
         <v>0.07072684570737625</v>
@@ -18010,7 +18010,7 @@
         <v>1.576191440820264</v>
       </c>
       <c r="J595">
-        <v>4.531784698050975</v>
+        <v>4</v>
       </c>
     </row>
     <row r="596">
@@ -18042,7 +18042,7 @@
         <v>1.546126687848851</v>
       </c>
       <c r="J596">
-        <v>4.879027770561974</v>
+        <v>4</v>
       </c>
     </row>
     <row r="597">
@@ -18053,7 +18053,7 @@
         <v>2024</v>
       </c>
       <c r="C597">
-        <v>-1.152163164406262</v>
+        <v>0</v>
       </c>
       <c r="D597">
         <v>0.6720475611938234</v>
@@ -18085,7 +18085,7 @@
         <v>2025</v>
       </c>
       <c r="C598">
-        <v>0.1585771628470405</v>
+        <v>0</v>
       </c>
       <c r="D598">
         <v>0.8700743698094147</v>
@@ -18117,7 +18117,7 @@
         <v>2026</v>
       </c>
       <c r="C599">
-        <v>-1.271593486534953</v>
+        <v>0</v>
       </c>
       <c r="D599">
         <v>0.9611788415316788</v>
@@ -18149,7 +18149,7 @@
         <v>2027</v>
       </c>
       <c r="C600">
-        <v>-0.3255352593969005</v>
+        <v>0</v>
       </c>
       <c r="D600">
         <v>0.8891971715591016</v>
@@ -18181,7 +18181,7 @@
         <v>2028</v>
       </c>
       <c r="C601">
-        <v>-1.035309913457315</v>
+        <v>0</v>
       </c>
       <c r="D601">
         <v>0.8420247434685489</v>
@@ -18213,7 +18213,7 @@
         <v>2024</v>
       </c>
       <c r="C602">
-        <v>-1.33361284172183</v>
+        <v>0</v>
       </c>
       <c r="D602">
         <v>0.6437572587853061</v>
@@ -18242,7 +18242,7 @@
         <v>2025</v>
       </c>
       <c r="C603">
-        <v>0.4277255645885279</v>
+        <v>0</v>
       </c>
       <c r="D603">
         <v>0.1889529505292654</v>
@@ -18274,7 +18274,7 @@
         <v>2026</v>
       </c>
       <c r="C604">
-        <v>-1.057380959385729</v>
+        <v>0</v>
       </c>
       <c r="D604">
         <v>0.7672072818822328</v>
@@ -18306,7 +18306,7 @@
         <v>2027</v>
       </c>
       <c r="C605">
-        <v>-0.1038258162888166</v>
+        <v>0</v>
       </c>
       <c r="D605">
         <v>0.4299949894501391</v>
@@ -18338,7 +18338,7 @@
         <v>2028</v>
       </c>
       <c r="C606">
-        <v>-0.7685423478326922</v>
+        <v>0</v>
       </c>
       <c r="D606">
         <v>0.6244151484415815</v>
@@ -18530,7 +18530,7 @@
         <v>2024</v>
       </c>
       <c r="C612">
-        <v>-1.356548512393128</v>
+        <v>0</v>
       </c>
       <c r="D612">
         <v>0.4646171765421338</v>
@@ -18562,7 +18562,7 @@
         <v>2025</v>
       </c>
       <c r="C613">
-        <v>0.4519170932656402</v>
+        <v>0</v>
       </c>
       <c r="D613">
         <v>0.6295482669703352</v>
@@ -18594,7 +18594,7 @@
         <v>2026</v>
       </c>
       <c r="C614">
-        <v>-1.047457097412042</v>
+        <v>0</v>
       </c>
       <c r="D614">
         <v>0.711936475327444</v>
@@ -18626,7 +18626,7 @@
         <v>2027</v>
       </c>
       <c r="C615">
-        <v>-0.08909169678015297</v>
+        <v>0</v>
       </c>
       <c r="D615">
         <v>0.6739730156170379</v>
@@ -18658,7 +18658,7 @@
         <v>2028</v>
       </c>
       <c r="C616">
-        <v>-0.7523875534346195</v>
+        <v>0</v>
       </c>
       <c r="D616">
         <v>0.6650592912469457</v>
@@ -18690,7 +18690,7 @@
         <v>2024</v>
       </c>
       <c r="C617">
-        <v>-1.06995200736398</v>
+        <v>1.06995200736398</v>
       </c>
       <c r="D617">
         <v>0.3504219507761429</v>
@@ -18719,7 +18719,7 @@
         <v>2025</v>
       </c>
       <c r="C618">
-        <v>0.4247456412911867</v>
+        <v>-0.4247456412911867</v>
       </c>
       <c r="D618">
         <v>0.5107170710999239</v>
@@ -18748,7 +18748,7 @@
         <v>2026</v>
       </c>
       <c r="C619">
-        <v>-0.9249359951392226</v>
+        <v>0.9249359951392226</v>
       </c>
       <c r="D619">
         <v>0.5903515241570457</v>
@@ -18777,7 +18777,7 @@
         <v>2027</v>
       </c>
       <c r="C620">
-        <v>-0.01283453112562967</v>
+        <v>0.01283453112562967</v>
       </c>
       <c r="D620">
         <v>-0.1639429428857138</v>
@@ -18806,7 +18806,7 @@
         <v>2028</v>
       </c>
       <c r="C621">
-        <v>-0.6474137888626591</v>
+        <v>0.6474137888626591</v>
       </c>
       <c r="D621">
         <v>-0.1553120351872262</v>
@@ -18835,7 +18835,7 @@
         <v>2024</v>
       </c>
       <c r="C622">
-        <v>-1.00826114219765</v>
+        <v>0</v>
       </c>
       <c r="D622">
         <v>0.3246890561420118</v>
@@ -18867,7 +18867,7 @@
         <v>2025</v>
       </c>
       <c r="C623">
-        <v>0.08486922375134477</v>
+        <v>0</v>
       </c>
       <c r="D623">
         <v>0.7818607169459937</v>
@@ -18899,7 +18899,7 @@
         <v>2026</v>
       </c>
       <c r="C624">
-        <v>-1.172854348793526</v>
+        <v>0</v>
       </c>
       <c r="D624">
         <v>0.7225743550577451</v>
@@ -18931,7 +18931,7 @@
         <v>2027</v>
       </c>
       <c r="C625">
-        <v>-0.3056351439424328</v>
+        <v>0</v>
       </c>
       <c r="D625">
         <v>0.7284213158376157</v>
@@ -18963,7 +18963,7 @@
         <v>2028</v>
       </c>
       <c r="C626">
-        <v>-0.9794573619233558</v>
+        <v>0</v>
       </c>
       <c r="D626">
         <v>0.6962403136397677</v>
@@ -19605,7 +19605,7 @@
         <v>2024</v>
       </c>
       <c r="C647">
-        <v>-0.3622307790313815</v>
+        <v>0</v>
       </c>
       <c r="D647">
         <v>-0.01271435000873231</v>
@@ -19634,7 +19634,7 @@
         <v>2025</v>
       </c>
       <c r="C648">
-        <v>-1.02260254878739</v>
+        <v>0</v>
       </c>
       <c r="D648">
         <v>-0.1360359753151544</v>
@@ -19663,7 +19663,7 @@
         <v>2026</v>
       </c>
       <c r="C649">
-        <v>-0.13937774464816</v>
+        <v>0</v>
       </c>
       <c r="D649">
         <v>-0.07433821969918605</v>
@@ -19692,7 +19692,7 @@
         <v>2027</v>
       </c>
       <c r="C650">
-        <v>-1.178624732057674</v>
+        <v>0</v>
       </c>
       <c r="D650">
         <v>-0.0584146455750037</v>
@@ -19721,7 +19721,7 @@
         <v>2028</v>
       </c>
       <c r="C651">
-        <v>-0.3948946652418361</v>
+        <v>0</v>
       </c>
       <c r="D651">
         <v>0.03051615153222278</v>
@@ -19910,7 +19910,7 @@
         <v>2024</v>
       </c>
       <c r="C657">
-        <v>-0.5374118826879765</v>
+        <v>0</v>
       </c>
       <c r="D657">
         <v>-1.895181894598542</v>
@@ -19942,7 +19942,7 @@
         <v>2025</v>
       </c>
       <c r="C658">
-        <v>-0.9846483324665596</v>
+        <v>0</v>
       </c>
       <c r="D658">
         <v>1.291624317034461</v>
@@ -19974,7 +19974,7 @@
         <v>2026</v>
       </c>
       <c r="C659">
-        <v>-0.3802763881353404</v>
+        <v>0</v>
       </c>
       <c r="D659">
         <v>0.1928895264830324</v>
@@ -20006,7 +20006,7 @@
         <v>2027</v>
       </c>
       <c r="C660">
-        <v>-1.192606403381157</v>
+        <v>0</v>
       </c>
       <c r="D660">
         <v>1.089336015525461</v>
@@ -20038,7 +20038,7 @@
         <v>2028</v>
       </c>
       <c r="C661">
-        <v>-0.6030325386337307</v>
+        <v>0</v>
       </c>
       <c r="D661">
         <v>0.3840170485012198</v>
@@ -20215,7 +20215,7 @@
         <v>2024</v>
       </c>
       <c r="C667">
-        <v>-0.3382234579999564</v>
+        <v>0</v>
       </c>
       <c r="D667">
         <v>0.2852749718430951</v>
@@ -20247,7 +20247,7 @@
         <v>2025</v>
       </c>
       <c r="C668">
-        <v>0.8151839850512947</v>
+        <v>0</v>
       </c>
       <c r="D668">
         <v>0.2842293443659424</v>
@@ -20279,7 +20279,7 @@
         <v>2026</v>
       </c>
       <c r="C669">
-        <v>-0.09888448133824006</v>
+        <v>0</v>
       </c>
       <c r="D669">
         <v>0.3734685281304291</v>
@@ -20311,7 +20311,7 @@
         <v>2027</v>
       </c>
       <c r="C670">
-        <v>0.6559099018985536</v>
+        <v>0</v>
       </c>
       <c r="D670">
         <v>0.3662697300500383</v>
@@ -20343,7 +20343,7 @@
         <v>2028</v>
       </c>
       <c r="C671">
-        <v>0.2104760898261182</v>
+        <v>0</v>
       </c>
       <c r="D671">
         <v>0.4052211850970251</v>
@@ -20375,7 +20375,7 @@
         <v>2024</v>
       </c>
       <c r="C672">
-        <v>-0.3382220386232825</v>
+        <v>0</v>
       </c>
       <c r="D672">
         <v>1.142084403524846</v>
@@ -20407,7 +20407,7 @@
         <v>2025</v>
       </c>
       <c r="C673">
-        <v>0.8151815437485415</v>
+        <v>0</v>
       </c>
       <c r="D673">
         <v>-0.3817768225164294</v>
@@ -20439,7 +20439,7 @@
         <v>2026</v>
       </c>
       <c r="C674">
-        <v>-0.09888420208030715</v>
+        <v>0</v>
       </c>
       <c r="D674">
         <v>1.067388610996314</v>
@@ -20471,7 +20471,7 @@
         <v>2027</v>
       </c>
       <c r="C675">
-        <v>0.6559086554584822</v>
+        <v>0</v>
       </c>
       <c r="D675">
         <v>0.1805262774238788</v>
@@ -20503,7 +20503,7 @@
         <v>2028</v>
       </c>
       <c r="C676">
-        <v>0.2104753399454597</v>
+        <v>0</v>
       </c>
       <c r="D676">
         <v>0.6942017847349896</v>
@@ -20680,7 +20680,7 @@
         <v>2024</v>
       </c>
       <c r="C682">
-        <v>0.4121260522366527</v>
+        <v>-0.4121260522366527</v>
       </c>
       <c r="D682">
         <v>0.8001808098224457</v>
@@ -20706,7 +20706,7 @@
         <v>2025</v>
       </c>
       <c r="C683">
-        <v>3.387472382362234</v>
+        <v>-3.387472382362234</v>
       </c>
       <c r="D683">
         <v>-0.3985731441700485</v>
@@ -20732,7 +20732,7 @@
         <v>2026</v>
       </c>
       <c r="C684">
-        <v>2.627861452254357</v>
+        <v>-2.627861452254357</v>
       </c>
       <c r="D684">
         <v>1.23611788628907</v>
@@ -20758,7 +20758,7 @@
         <v>2027</v>
       </c>
       <c r="C685">
-        <v>3.38819517491711</v>
+        <v>-3.38819517491711</v>
       </c>
       <c r="D685">
         <v>-0.2109703853498379</v>
@@ -20784,7 +20784,7 @@
         <v>2028</v>
       </c>
       <c r="C686">
-        <v>3.468136578258522</v>
+        <v>-3.468136578258522</v>
       </c>
       <c r="D686">
         <v>1.029649800679613</v>
@@ -20810,7 +20810,7 @@
         <v>2024</v>
       </c>
       <c r="C687">
-        <v>-0.347057868665024</v>
+        <v>0.347057868665024</v>
       </c>
       <c r="D687">
         <v>-0.2284226216094657</v>
@@ -20836,7 +20836,7 @@
         <v>2025</v>
       </c>
       <c r="C688">
-        <v>1.968033270848902</v>
+        <v>-1.968033270848902</v>
       </c>
       <c r="D688">
         <v>-0.6086030748413923</v>
@@ -20851,7 +20851,7 @@
         <v>-2.330763705450568</v>
       </c>
       <c r="J688">
-        <v>4.298913204236212</v>
+        <v>4</v>
       </c>
     </row>
     <row r="689">
@@ -20862,7 +20862,7 @@
         <v>2026</v>
       </c>
       <c r="C689">
-        <v>0.8557279599209737</v>
+        <v>-0.8557279599209737</v>
       </c>
       <c r="D689">
         <v>-0.5791296992890131</v>
@@ -20877,7 +20877,7 @@
         <v>-2.061869796811964</v>
       </c>
       <c r="J689">
-        <v>4.103964699647329</v>
+        <v>4</v>
       </c>
     </row>
     <row r="690">
@@ -20888,7 +20888,7 @@
         <v>2027</v>
       </c>
       <c r="C690">
-        <v>1.717113287839908</v>
+        <v>-1.717113287839908</v>
       </c>
       <c r="D690">
         <v>-0.5727439099084412</v>
@@ -20903,7 +20903,7 @@
         <v>-1.926858038345835</v>
       </c>
       <c r="J690">
-        <v>4.055135874743813</v>
+        <v>4</v>
       </c>
     </row>
     <row r="691">
@@ -20914,7 +20914,7 @@
         <v>2028</v>
       </c>
       <c r="C691">
-        <v>1.436624006885249</v>
+        <v>-1.436624006885249</v>
       </c>
       <c r="D691">
         <v>-0.4469379247106491</v>
@@ -20940,7 +20940,7 @@
         <v>2024</v>
       </c>
       <c r="C692">
-        <v>-0.3299627406986785</v>
+        <v>0.3299627406986785</v>
       </c>
       <c r="D692">
         <v>0.2254271944504804</v>
@@ -20969,7 +20969,7 @@
         <v>2025</v>
       </c>
       <c r="C693">
-        <v>-0.02933864868505775</v>
+        <v>0.02933864868505775</v>
       </c>
       <c r="D693">
         <v>0.02596739540234322</v>
@@ -20998,7 +20998,7 @@
         <v>2026</v>
       </c>
       <c r="C694">
-        <v>-0.3111685247603228</v>
+        <v>0.3111685247603228</v>
       </c>
       <c r="D694">
         <v>0.1439928061425713</v>
@@ -21027,7 +21027,7 @@
         <v>2027</v>
       </c>
       <c r="C695">
-        <v>-0.06498381476918261</v>
+        <v>0.06498381476918261</v>
       </c>
       <c r="D695">
         <v>0.1444951308903914</v>
@@ -21056,7 +21056,7 @@
         <v>2028</v>
       </c>
       <c r="C696">
-        <v>-0.3090367263357074</v>
+        <v>0.3090367263357074</v>
       </c>
       <c r="D696">
         <v>0.2129839792195105</v>
@@ -21085,7 +21085,7 @@
         <v>2024</v>
       </c>
       <c r="C697">
-        <v>-0.3788459488833759</v>
+        <v>0</v>
       </c>
       <c r="D697">
         <v>0.1975672214366006</v>
@@ -21117,7 +21117,7 @@
         <v>2025</v>
       </c>
       <c r="C698">
-        <v>-1.017224941383038</v>
+        <v>0</v>
       </c>
       <c r="D698">
         <v>0.1901113833037341</v>
@@ -21149,7 +21149,7 @@
         <v>2026</v>
       </c>
       <c r="C699">
-        <v>-0.151615004300486</v>
+        <v>0</v>
       </c>
       <c r="D699">
         <v>0.2754324880024407</v>
@@ -21181,7 +21181,7 @@
         <v>2027</v>
       </c>
       <c r="C700">
-        <v>-1.181827992994192</v>
+        <v>0</v>
       </c>
       <c r="D700">
         <v>0.2749689947374164</v>
@@ -21213,7 +21213,7 @@
         <v>2028</v>
       </c>
       <c r="C701">
-        <v>-0.4011866669647477</v>
+        <v>0</v>
       </c>
       <c r="D701">
         <v>0.3262987551015681</v>
@@ -21254,7 +21254,7 @@
         <v>0.2802659472644727</v>
       </c>
       <c r="F702">
-        <v>7.300977632006709</v>
+        <v>4</v>
       </c>
       <c r="G702">
         <v>0.1785370071400792</v>
@@ -21405,7 +21405,7 @@
         <v>2024</v>
       </c>
       <c r="C707">
-        <v>-0.3788451419396353</v>
+        <v>0</v>
       </c>
       <c r="D707">
         <v>0.4315847077263112</v>
@@ -21437,7 +21437,7 @@
         <v>2025</v>
       </c>
       <c r="C708">
-        <v>-1.017227799532578</v>
+        <v>0</v>
       </c>
       <c r="D708">
         <v>0.5750638251912186</v>
@@ -21469,7 +21469,7 @@
         <v>2026</v>
       </c>
       <c r="C709">
-        <v>-0.1516117939273956</v>
+        <v>0</v>
       </c>
       <c r="D709">
         <v>0.6592169738129195</v>
@@ -21501,7 +21501,7 @@
         <v>2027</v>
       </c>
       <c r="C710">
-        <v>-1.181831793139811</v>
+        <v>0</v>
       </c>
       <c r="D710">
         <v>0.6268517956118982</v>
@@ -21533,7 +21533,7 @@
         <v>2028</v>
       </c>
       <c r="C711">
-        <v>-0.4011835966671153</v>
+        <v>0</v>
       </c>
       <c r="D711">
         <v>0.6258682640412494</v>
@@ -22045,7 +22045,7 @@
         <v>2024</v>
       </c>
       <c r="C727">
-        <v>-0.354165105571962</v>
+        <v>0</v>
       </c>
       <c r="D727">
         <v>0.3517636641103462</v>
@@ -22077,7 +22077,7 @@
         <v>2025</v>
       </c>
       <c r="C728">
-        <v>-1.025128516040177</v>
+        <v>0</v>
       </c>
       <c r="D728">
         <v>0.44687882348116</v>
@@ -22109,7 +22109,7 @@
         <v>2026</v>
       </c>
       <c r="C729">
-        <v>-0.1335496738373407</v>
+        <v>0</v>
       </c>
       <c r="D729">
         <v>0.5334120032568507</v>
@@ -22141,7 +22141,7 @@
         <v>2027</v>
       </c>
       <c r="C730">
-        <v>-1.176947055903114</v>
+        <v>0</v>
       </c>
       <c r="D730">
         <v>0.5132061558925811</v>
@@ -22173,7 +22173,7 @@
         <v>2028</v>
       </c>
       <c r="C731">
-        <v>-0.3919473163199906</v>
+        <v>0</v>
       </c>
       <c r="D731">
         <v>0.5304604366035425</v>
@@ -22365,7 +22365,7 @@
         <v>2024</v>
       </c>
       <c r="C737">
-        <v>-0.3047745124445042</v>
+        <v>0</v>
       </c>
       <c r="D737">
         <v>-1.849029803654717</v>
@@ -22397,7 +22397,7 @@
         <v>2025</v>
       </c>
       <c r="C738">
-        <v>-1.249350501399174</v>
+        <v>0</v>
       </c>
       <c r="D738">
         <v>0.9118390316293928</v>
@@ -22429,7 +22429,7 @@
         <v>2026</v>
       </c>
       <c r="C739">
-        <v>-0.02268682711353311</v>
+        <v>0</v>
       </c>
       <c r="D739">
         <v>0.9871094034335096</v>
@@ -22461,7 +22461,7 @@
         <v>2027</v>
       </c>
       <c r="C740">
-        <v>-1.436834088394827</v>
+        <v>0</v>
       </c>
       <c r="D740">
         <v>0.9172125429935052</v>
@@ -22493,7 +22493,7 @@
         <v>2028</v>
       </c>
       <c r="C741">
-        <v>-0.3154801614280317</v>
+        <v>0</v>
       </c>
       <c r="D741">
         <v>0.8644619138608542</v>
@@ -22685,10 +22685,10 @@
         <v>2024</v>
       </c>
       <c r="C747">
-        <v>-0.3330312647024693</v>
+        <v>0</v>
       </c>
       <c r="D747">
-        <v>-4.107345255145684</v>
+        <v>-4</v>
       </c>
       <c r="E747">
         <v>-0.1981239436463172</v>
@@ -22717,7 +22717,7 @@
         <v>2025</v>
       </c>
       <c r="C748">
-        <v>-0.9879754674737607</v>
+        <v>0</v>
       </c>
       <c r="D748">
         <v>-0.6786629072890695</v>
@@ -22749,7 +22749,7 @@
         <v>2026</v>
       </c>
       <c r="C749">
-        <v>-0.1290999907615816</v>
+        <v>0</v>
       </c>
       <c r="D749">
         <v>-0.1558592436145527</v>
@@ -22781,7 +22781,7 @@
         <v>2027</v>
       </c>
       <c r="C750">
-        <v>-1.11878678921031</v>
+        <v>0</v>
       </c>
       <c r="D750">
         <v>-0.3998129222828589</v>
@@ -22813,7 +22813,7 @@
         <v>2028</v>
       </c>
       <c r="C751">
-        <v>-0.3889013293406502</v>
+        <v>0</v>
       </c>
       <c r="D751">
         <v>-0.159819147462879</v>
@@ -22845,7 +22845,7 @@
         <v>2024</v>
       </c>
       <c r="C752">
-        <v>-0.2622771821965347</v>
+        <v>0.2622771821965347</v>
       </c>
       <c r="D752">
         <v>0.3944721291659696</v>
@@ -22877,7 +22877,7 @@
         <v>2025</v>
       </c>
       <c r="C753">
-        <v>-1.515525255722404</v>
+        <v>1.515525255722404</v>
       </c>
       <c r="D753">
         <v>0.6060338669244043</v>
@@ -22909,7 +22909,7 @@
         <v>2026</v>
       </c>
       <c r="C754">
-        <v>0.0547678687222509</v>
+        <v>-0.0547678687222509</v>
       </c>
       <c r="D754">
         <v>0.6946307464484961</v>
@@ -22941,7 +22941,7 @@
         <v>2027</v>
       </c>
       <c r="C755">
-        <v>-1.743552315215315</v>
+        <v>1.743552315215315</v>
       </c>
       <c r="D755">
         <v>0.658839517958782</v>
@@ -22973,7 +22973,7 @@
         <v>2028</v>
       </c>
       <c r="C756">
-        <v>-0.2775739586677808</v>
+        <v>0.2775739586677808</v>
       </c>
       <c r="D756">
         <v>0.6525119071062461</v>
@@ -23005,7 +23005,7 @@
         <v>2024</v>
       </c>
       <c r="C757">
-        <v>-0.6942982465934583</v>
+        <v>0.6942982465934583</v>
       </c>
       <c r="D757">
         <v>0.2180594646223645</v>
@@ -23037,7 +23037,7 @@
         <v>2025</v>
       </c>
       <c r="C758">
-        <v>0.6964906698284729</v>
+        <v>-0.6964906698284729</v>
       </c>
       <c r="D758">
         <v>-0.1758873044557763</v>
@@ -23058,7 +23058,7 @@
         <v>-2.117950121664887</v>
       </c>
       <c r="J758">
-        <v>5.027612908630108</v>
+        <v>4</v>
       </c>
     </row>
     <row r="759">
@@ -23069,7 +23069,7 @@
         <v>2026</v>
       </c>
       <c r="C759">
-        <v>-0.3148779575224618</v>
+        <v>0.3148779575224618</v>
       </c>
       <c r="D759">
         <v>0.01616847550222871</v>
@@ -23090,7 +23090,7 @@
         <v>-1.879074027122614</v>
       </c>
       <c r="J759">
-        <v>5.310520627669931</v>
+        <v>4</v>
       </c>
     </row>
     <row r="760">
@@ -23101,7 +23101,7 @@
         <v>2027</v>
       </c>
       <c r="C760">
-        <v>0.4325493439648408</v>
+        <v>-0.4325493439648408</v>
       </c>
       <c r="D760">
         <v>-0.00673863526728768</v>
@@ -23122,7 +23122,7 @@
         <v>-1.764237506489365</v>
       </c>
       <c r="J760">
-        <v>5.096111155589836</v>
+        <v>4</v>
       </c>
     </row>
     <row r="761">
@@ -23133,7 +23133,7 @@
         <v>2028</v>
       </c>
       <c r="C761">
-        <v>-0.03374464804491255</v>
+        <v>0.03374464804491255</v>
       </c>
       <c r="D761">
         <v>0.0864305704127093</v>
@@ -23154,7 +23154,7 @@
         <v>-1.713994562226517</v>
       </c>
       <c r="J761">
-        <v>5.062576722609473</v>
+        <v>4</v>
       </c>
     </row>
     <row r="762">
@@ -23325,7 +23325,7 @@
         <v>2024</v>
       </c>
       <c r="C767">
-        <v>0.08780095460038594</v>
+        <v>0</v>
       </c>
       <c r="D767">
         <v>0.648741379652697</v>
@@ -23354,7 +23354,7 @@
         <v>2025</v>
       </c>
       <c r="C768">
-        <v>-0.8405564372959122</v>
+        <v>0</v>
       </c>
       <c r="D768">
         <v>1.087360569084824</v>
@@ -23383,7 +23383,7 @@
         <v>2026</v>
       </c>
       <c r="C769">
-        <v>0.3923801569956742</v>
+        <v>0</v>
       </c>
       <c r="D769">
         <v>1.165905341928787</v>
@@ -23412,7 +23412,7 @@
         <v>2027</v>
       </c>
       <c r="C770">
-        <v>-0.798036109416148</v>
+        <v>0</v>
       </c>
       <c r="D770">
         <v>1.071712018489022</v>
@@ -23441,7 +23441,7 @@
         <v>2028</v>
       </c>
       <c r="C771">
-        <v>0.09050216289329764</v>
+        <v>0</v>
       </c>
       <c r="D771">
         <v>0.9880294006219148</v>
@@ -23470,7 +23470,7 @@
         <v>2024</v>
       </c>
       <c r="C772">
-        <v>-0.221438663079151</v>
+        <v>0</v>
       </c>
       <c r="D772">
         <v>0.7624635292836698</v>
@@ -23499,7 +23499,7 @@
         <v>2025</v>
       </c>
       <c r="C773">
-        <v>-1.494441564863032</v>
+        <v>0</v>
       </c>
       <c r="D773">
         <v>1.060469740273088</v>
@@ -23528,7 +23528,7 @@
         <v>2026</v>
       </c>
       <c r="C774">
-        <v>0.1170994552325998</v>
+        <v>0</v>
       </c>
       <c r="D774">
         <v>1.11258566012325</v>
@@ -23557,7 +23557,7 @@
         <v>2027</v>
       </c>
       <c r="C775">
-        <v>-1.708556596591821</v>
+        <v>0</v>
       </c>
       <c r="D775">
         <v>1.022554338331476</v>
@@ -23586,7 +23586,7 @@
         <v>2028</v>
       </c>
       <c r="C776">
-        <v>-0.2163940821076785</v>
+        <v>0</v>
       </c>
       <c r="D776">
         <v>0.9484514621391034</v>
@@ -23615,7 +23615,7 @@
         <v>2024</v>
       </c>
       <c r="C777">
-        <v>-0.260072520303936</v>
+        <v>0</v>
       </c>
       <c r="D777">
         <v>0.6441368152315062</v>
@@ -23647,7 +23647,7 @@
         <v>2025</v>
       </c>
       <c r="C778">
-        <v>-1.534390696195638</v>
+        <v>0</v>
       </c>
       <c r="D778">
         <v>0.8388058653803029</v>
@@ -23679,7 +23679,7 @@
         <v>2026</v>
       </c>
       <c r="C779">
-        <v>0.05871463043720922</v>
+        <v>0</v>
       </c>
       <c r="D779">
         <v>0.918133397736556</v>
@@ -23711,7 +23711,7 @@
         <v>2027</v>
       </c>
       <c r="C780">
-        <v>-1.765525855033359</v>
+        <v>0</v>
       </c>
       <c r="D780">
         <v>0.8551152407864646</v>
@@ -23743,7 +23743,7 @@
         <v>2028</v>
       </c>
       <c r="C781">
-        <v>-0.276230607661173</v>
+        <v>0</v>
       </c>
       <c r="D781">
         <v>0.8137796097335546</v>
@@ -23775,7 +23775,7 @@
         <v>2024</v>
       </c>
       <c r="C782">
-        <v>-0.2600729666589128</v>
+        <v>0</v>
       </c>
       <c r="D782">
         <v>1.103393459418113</v>
@@ -23807,7 +23807,7 @@
         <v>2025</v>
       </c>
       <c r="C783">
-        <v>-1.53438928806312</v>
+        <v>0</v>
       </c>
       <c r="D783">
         <v>1.370098508515914</v>
@@ -23839,7 +23839,7 @@
         <v>2026</v>
       </c>
       <c r="C784">
-        <v>0.05871269343959162</v>
+        <v>0</v>
       </c>
       <c r="D784">
         <v>1.254207140666927</v>
@@ -23871,7 +23871,7 @@
         <v>2027</v>
       </c>
       <c r="C785">
-        <v>-1.76552374294691</v>
+        <v>0</v>
       </c>
       <c r="D785">
         <v>1.066677762552094</v>
@@ -23903,7 +23903,7 @@
         <v>2028</v>
       </c>
       <c r="C786">
-        <v>-0.2762327748556042</v>
+        <v>0</v>
       </c>
       <c r="D786">
         <v>0.9453914801957892</v>
@@ -23935,10 +23935,10 @@
         <v>2024</v>
       </c>
       <c r="C787">
-        <v>-0.2600727704584581</v>
+        <v>0</v>
       </c>
       <c r="D787">
-        <v>4.996624594588067</v>
+        <v>4</v>
       </c>
       <c r="E787">
         <v>0.6977133841495359</v>
@@ -23967,7 +23967,7 @@
         <v>2025</v>
       </c>
       <c r="C788">
-        <v>-1.534389912899794</v>
+        <v>0</v>
       </c>
       <c r="D788">
         <v>-2.640955923754468</v>
@@ -23999,10 +23999,10 @@
         <v>2026</v>
       </c>
       <c r="C789">
-        <v>0.05871354961384351</v>
+        <v>0</v>
       </c>
       <c r="D789">
-        <v>4.230125224940762</v>
+        <v>4</v>
       </c>
       <c r="E789">
         <v>-0.01789352768627229</v>
@@ -24031,7 +24031,7 @@
         <v>2027</v>
       </c>
       <c r="C790">
-        <v>-1.76552468039251</v>
+        <v>0</v>
       </c>
       <c r="D790">
         <v>-0.909775763058886</v>
@@ -24063,7 +24063,7 @@
         <v>2028</v>
       </c>
       <c r="C791">
-        <v>-0.2762318165342103</v>
+        <v>0</v>
       </c>
       <c r="D791">
         <v>2.097040570764827</v>
@@ -24255,7 +24255,7 @@
         <v>2024</v>
       </c>
       <c r="C797">
-        <v>-0.260068472792546</v>
+        <v>0</v>
       </c>
       <c r="D797">
         <v>0.2562783038751387</v>
@@ -24284,7 +24284,7 @@
         <v>2025</v>
       </c>
       <c r="C798">
-        <v>-1.53440369476259</v>
+        <v>0</v>
       </c>
       <c r="D798">
         <v>0.00892012569067919</v>
@@ -24313,7 +24313,7 @@
         <v>2026</v>
       </c>
       <c r="C799">
-        <v>0.058732380578028</v>
+        <v>0</v>
       </c>
       <c r="D799">
         <v>0.147372215355867</v>
@@ -24342,7 +24342,7 @@
         <v>2027</v>
       </c>
       <c r="C800">
-        <v>-1.765545361334039</v>
+        <v>0</v>
       </c>
       <c r="D800">
         <v>0.1425979142795927</v>
@@ -24371,7 +24371,7 @@
         <v>2028</v>
       </c>
       <c r="C801">
-        <v>-0.276210732398327</v>
+        <v>0</v>
       </c>
       <c r="D801">
         <v>0.2123808355123269</v>
@@ -24400,7 +24400,7 @@
         <v>2024</v>
       </c>
       <c r="C802">
-        <v>-0.2600736510470126</v>
+        <v>0</v>
       </c>
       <c r="E802">
         <v>0.1530180667197378</v>
@@ -24429,7 +24429,7 @@
         <v>2025</v>
       </c>
       <c r="C803">
-        <v>-1.534387088980411</v>
+        <v>0</v>
       </c>
       <c r="E803">
         <v>0.4313937898044328</v>
@@ -24458,7 +24458,7 @@
         <v>2026</v>
       </c>
       <c r="C804">
-        <v>0.05870969116335252</v>
+        <v>0</v>
       </c>
       <c r="E804">
         <v>0.1105341896457916</v>
@@ -24487,7 +24487,7 @@
         <v>2027</v>
       </c>
       <c r="C805">
-        <v>-1.765520442862669</v>
+        <v>0</v>
       </c>
       <c r="E805">
         <v>0.4985298465521047</v>
@@ -24516,7 +24516,7 @@
         <v>2028</v>
       </c>
       <c r="C806">
-        <v>-0.2762361366341807</v>
+        <v>0</v>
       </c>
       <c r="E806">
         <v>0.240834300969238</v>
@@ -24545,7 +24545,7 @@
         <v>2024</v>
       </c>
       <c r="C807">
-        <v>-0.2600686562646619</v>
+        <v>0</v>
       </c>
       <c r="E807">
         <v>0.6572712289760622</v>
@@ -24571,7 +24571,7 @@
         <v>2025</v>
       </c>
       <c r="C808">
-        <v>-1.534397043283047</v>
+        <v>0</v>
       </c>
       <c r="E808">
         <v>1.589996380290317</v>
@@ -24597,7 +24597,7 @@
         <v>2026</v>
       </c>
       <c r="C809">
-        <v>0.05872668046823071</v>
+        <v>0</v>
       </c>
       <c r="E809">
         <v>1.721975373424471</v>
@@ -24623,7 +24623,7 @@
         <v>2027</v>
       </c>
       <c r="C810">
-        <v>-1.76553513590138</v>
+        <v>0</v>
       </c>
       <c r="E810">
         <v>1.978714727959148</v>
@@ -24649,7 +24649,7 @@
         <v>2028</v>
       </c>
       <c r="C811">
-        <v>-0.276217521214787</v>
+        <v>0</v>
       </c>
       <c r="E811">
         <v>2.213149312511286</v>
@@ -24995,7 +24995,7 @@
         <v>2024</v>
       </c>
       <c r="C822">
-        <v>0.0878021525068904</v>
+        <v>0</v>
       </c>
       <c r="D822">
         <v>0.5194339969851944</v>
@@ -25004,7 +25004,7 @@
         <v>-0.1956002686401006</v>
       </c>
       <c r="F822">
-        <v>-4.410161019733056</v>
+        <v>-4</v>
       </c>
       <c r="G822">
         <v>0.1344003170065575</v>
@@ -25024,7 +25024,7 @@
         <v>2025</v>
       </c>
       <c r="C823">
-        <v>-0.8405609738410427</v>
+        <v>0</v>
       </c>
       <c r="D823">
         <v>0.8979191063113635</v>
@@ -25053,7 +25053,7 @@
         <v>2026</v>
       </c>
       <c r="C824">
-        <v>0.3923846379830029</v>
+        <v>0</v>
       </c>
       <c r="D824">
         <v>0.9404457034611836</v>
@@ -25082,7 +25082,7 @@
         <v>2027</v>
       </c>
       <c r="C825">
-        <v>-0.7980417572382765</v>
+        <v>0</v>
       </c>
       <c r="D825">
         <v>0.8787728058201698</v>
@@ -25111,7 +25111,7 @@
         <v>2028</v>
       </c>
       <c r="C826">
-        <v>0.09050590402960126</v>
+        <v>0</v>
       </c>
       <c r="D826">
         <v>0.8324335921119016</v>
@@ -25140,7 +25140,7 @@
         <v>2024</v>
       </c>
       <c r="C827">
-        <v>-0.4323900578472654</v>
+        <v>0</v>
       </c>
       <c r="D827">
         <v>0.1187877694171946</v>
@@ -25172,7 +25172,7 @@
         <v>2025</v>
       </c>
       <c r="C828">
-        <v>0.5979713387765365</v>
+        <v>0</v>
       </c>
       <c r="D828">
         <v>0.1698150573483478</v>
@@ -25204,7 +25204,7 @@
         <v>2026</v>
       </c>
       <c r="C829">
-        <v>0.0515802790472561</v>
+        <v>0</v>
       </c>
       <c r="D829">
         <v>0.2210687905958432</v>
@@ -25236,7 +25236,7 @@
         <v>2027</v>
       </c>
       <c r="C830">
-        <v>0.468075400725924</v>
+        <v>0</v>
       </c>
       <c r="D830">
         <v>0.2323624115191775</v>
@@ -25268,7 +25268,7 @@
         <v>2028</v>
       </c>
       <c r="C831">
-        <v>0.2370716147555187</v>
+        <v>0</v>
       </c>
       <c r="D831">
         <v>0.2871830102750134</v>
@@ -25783,7 +25783,7 @@
         <v>-0.07131619706632239</v>
       </c>
       <c r="D847">
-        <v>-4.015051441731517</v>
+        <v>-4</v>
       </c>
       <c r="E847">
         <v>-1.26997503332349</v>
@@ -25841,7 +25841,7 @@
         <v>-0.3060298225211835</v>
       </c>
       <c r="D849">
-        <v>-4.232666376361263</v>
+        <v>-4</v>
       </c>
       <c r="E849">
         <v>-1.02616747116956</v>
@@ -25870,7 +25870,7 @@
         <v>-0.3120392734138511</v>
       </c>
       <c r="D850">
-        <v>-5.199430711828786</v>
+        <v>-4</v>
       </c>
       <c r="E850">
         <v>-1.020496024295621</v>
@@ -25899,7 +25899,7 @@
         <v>-0.4512822779454024</v>
       </c>
       <c r="D851">
-        <v>-6.866442079384955</v>
+        <v>-4</v>
       </c>
       <c r="E851">
         <v>-1.008891215035058</v>
@@ -26053,7 +26053,7 @@
         <v>-0.3913092008205759</v>
       </c>
       <c r="H856">
-        <v>-4.261322248941346</v>
+        <v>-4</v>
       </c>
       <c r="I856">
         <v>0.4100373650315882</v>
@@ -26230,7 +26230,7 @@
         <v>2024</v>
       </c>
       <c r="C862">
-        <v>0.03609448508716435</v>
+        <v>0</v>
       </c>
       <c r="D862">
         <v>0.4647914949378319</v>
@@ -26262,7 +26262,7 @@
         <v>2025</v>
       </c>
       <c r="C863">
-        <v>0.4617998226586815</v>
+        <v>0</v>
       </c>
       <c r="D863">
         <v>0.4991290027962433</v>
@@ -26294,7 +26294,7 @@
         <v>2026</v>
       </c>
       <c r="C864">
-        <v>0.3478122323530157</v>
+        <v>0</v>
       </c>
       <c r="D864">
         <v>0.6065416871887341</v>
@@ -26326,7 +26326,7 @@
         <v>2027</v>
       </c>
       <c r="C865">
-        <v>0.5474200285382386</v>
+        <v>0</v>
       </c>
       <c r="D865">
         <v>0.5764827738012587</v>
@@ -26341,7 +26341,7 @@
         <v>0.5181497843447571</v>
       </c>
       <c r="H865">
-        <v>-4.58585257011403</v>
+        <v>-4</v>
       </c>
       <c r="I865">
         <v>-0.2037200464180826</v>
@@ -26358,7 +26358,7 @@
         <v>2028</v>
       </c>
       <c r="C866">
-        <v>0.4351578484371927</v>
+        <v>0</v>
       </c>
       <c r="D866">
         <v>0.5841292113977997</v>
@@ -26373,7 +26373,7 @@
         <v>0.3846473863416709</v>
       </c>
       <c r="H866">
-        <v>-6.26088189365114</v>
+        <v>-4</v>
       </c>
       <c r="I866">
         <v>-0.2173543969571269</v>
@@ -26399,7 +26399,7 @@
         <v>0.3145089426007828</v>
       </c>
       <c r="F867">
-        <v>8.066775268092901</v>
+        <v>4</v>
       </c>
       <c r="I867">
         <v>0.6100133006561477</v>
@@ -26520,7 +26520,7 @@
         <v>2024</v>
       </c>
       <c r="C872">
-        <v>0.03463893521566059</v>
+        <v>0</v>
       </c>
       <c r="D872">
         <v>0.314179723151896</v>
@@ -26549,7 +26549,7 @@
         <v>2025</v>
       </c>
       <c r="C873">
-        <v>0.470244697876341</v>
+        <v>0</v>
       </c>
       <c r="D873">
         <v>0.1958514428882023</v>
@@ -26578,7 +26578,7 @@
         <v>2026</v>
       </c>
       <c r="C874">
-        <v>0.3515731426414871</v>
+        <v>0</v>
       </c>
       <c r="D874">
         <v>0.3117423504433649</v>
@@ -26607,7 +26607,7 @@
         <v>2027</v>
       </c>
       <c r="C875">
-        <v>0.5546373170806547</v>
+        <v>0</v>
       </c>
       <c r="D875">
         <v>0.3045814701453239</v>
@@ -26636,7 +26636,7 @@
         <v>2028</v>
       </c>
       <c r="C876">
-        <v>0.4415596181337888</v>
+        <v>0</v>
       </c>
       <c r="D876">
         <v>0.3525695791883636</v>
@@ -26765,7 +26765,7 @@
         <v>2024</v>
       </c>
       <c r="C882">
-        <v>-0.04966579039921107</v>
+        <v>0</v>
       </c>
       <c r="D882">
         <v>1.006721032473284</v>
@@ -26794,7 +26794,7 @@
         <v>2025</v>
       </c>
       <c r="C883">
-        <v>0.728202196924484</v>
+        <v>0</v>
       </c>
       <c r="D883">
         <v>1.491767228351459</v>
@@ -26823,7 +26823,7 @@
         <v>2026</v>
       </c>
       <c r="C884">
-        <v>0.02306378687753979</v>
+        <v>0</v>
       </c>
       <c r="D884">
         <v>1.490600051475268</v>
@@ -26852,7 +26852,7 @@
         <v>2027</v>
       </c>
       <c r="C885">
-        <v>0.6910186604881823</v>
+        <v>0</v>
       </c>
       <c r="D885">
         <v>1.345384761756818</v>
@@ -26881,7 +26881,7 @@
         <v>2028</v>
       </c>
       <c r="C886">
-        <v>0.287174802013569</v>
+        <v>0</v>
       </c>
       <c r="D886">
         <v>1.196646815456774</v>
@@ -26910,7 +26910,7 @@
         <v>2024</v>
       </c>
       <c r="C887">
-        <v>0.03463881131248621</v>
+        <v>0</v>
       </c>
       <c r="D887">
         <v>1.266989682994863</v>
@@ -26942,7 +26942,7 @@
         <v>2025</v>
       </c>
       <c r="C888">
-        <v>0.4702452415443117</v>
+        <v>0</v>
       </c>
       <c r="D888">
         <v>-0.5935540149848861</v>
@@ -26974,7 +26974,7 @@
         <v>2026</v>
       </c>
       <c r="C889">
-        <v>0.3515729669250564</v>
+        <v>0</v>
       </c>
       <c r="D889">
         <v>0.4614838608921564</v>
@@ -27006,7 +27006,7 @@
         <v>2027</v>
       </c>
       <c r="C890">
-        <v>0.5546377694315748</v>
+        <v>0</v>
       </c>
       <c r="D890">
         <v>0.07355653746377887</v>
@@ -27038,7 +27038,7 @@
         <v>2028</v>
       </c>
       <c r="C891">
-        <v>0.4415596768483774</v>
+        <v>0</v>
       </c>
       <c r="D891">
         <v>0.2779256574553489</v>
@@ -27070,7 +27070,7 @@
         <v>2024</v>
       </c>
       <c r="C892">
-        <v>0.04097561232564815</v>
+        <v>0</v>
       </c>
       <c r="D892">
         <v>0.4981132258330423</v>
@@ -27102,7 +27102,7 @@
         <v>2025</v>
       </c>
       <c r="C893">
-        <v>0.4341001469438594</v>
+        <v>0</v>
       </c>
       <c r="D893">
         <v>0.6419088773863356</v>
@@ -27134,7 +27134,7 @@
         <v>2026</v>
       </c>
       <c r="C894">
-        <v>0.335617974409859</v>
+        <v>0</v>
       </c>
       <c r="D894">
         <v>0.7313538517872651</v>
@@ -27166,7 +27166,7 @@
         <v>2027</v>
       </c>
       <c r="C895">
-        <v>0.5237812879708799</v>
+        <v>0</v>
       </c>
       <c r="D895">
         <v>0.6903109191378026</v>
@@ -27198,7 +27198,7 @@
         <v>2028</v>
       </c>
       <c r="C896">
-        <v>0.414276919954683</v>
+        <v>0</v>
       </c>
       <c r="D896">
         <v>0.6787130207869445</v>
@@ -27230,7 +27230,7 @@
         <v>2024</v>
       </c>
       <c r="C897">
-        <v>0.4209201005495178</v>
+        <v>0</v>
       </c>
       <c r="D897">
         <v>0.1119096804643022</v>
@@ -27262,7 +27262,7 @@
         <v>2025</v>
       </c>
       <c r="C898">
-        <v>-0.8116255059167791</v>
+        <v>0</v>
       </c>
       <c r="D898">
         <v>0.08974727480187807</v>
@@ -27294,7 +27294,7 @@
         <v>2026</v>
       </c>
       <c r="C899">
-        <v>0.008836226825697119</v>
+        <v>0</v>
       </c>
       <c r="D899">
         <v>0.1668221334893414</v>
@@ -27326,7 +27326,7 @@
         <v>2027</v>
       </c>
       <c r="C900">
-        <v>-0.4971802904727481</v>
+        <v>0</v>
       </c>
       <c r="D900">
         <v>0.1729850487535128</v>
@@ -27358,7 +27358,7 @@
         <v>2028</v>
       </c>
       <c r="C901">
-        <v>-0.3417163286231776</v>
+        <v>0</v>
       </c>
       <c r="D901">
         <v>0.2370858575840241</v>
@@ -27550,7 +27550,7 @@
         <v>2024</v>
       </c>
       <c r="C907">
-        <v>0.4209235552221122</v>
+        <v>0</v>
       </c>
       <c r="D907">
         <v>-0.00349062076093236</v>
@@ -27582,7 +27582,7 @@
         <v>2025</v>
       </c>
       <c r="C908">
-        <v>-0.8116318072209766</v>
+        <v>0</v>
       </c>
       <c r="D908">
         <v>-0.1620632422461514</v>
@@ -27614,7 +27614,7 @@
         <v>2026</v>
       </c>
       <c r="C909">
-        <v>0.00884176430955296</v>
+        <v>0</v>
       </c>
       <c r="D909">
         <v>-0.0931631175212846</v>
@@ -27646,7 +27646,7 @@
         <v>2027</v>
       </c>
       <c r="C910">
-        <v>-0.4971853466356659</v>
+        <v>0</v>
       </c>
       <c r="D910">
         <v>-0.07837112398875337</v>
@@ -27678,7 +27678,7 @@
         <v>2028</v>
       </c>
       <c r="C911">
-        <v>-0.3417139285987971</v>
+        <v>0</v>
       </c>
       <c r="D911">
         <v>0.01267865118773405</v>
@@ -27914,7 +27914,7 @@
         <v>-1.096597237165619</v>
       </c>
       <c r="G918">
-        <v>5.703526679568335</v>
+        <v>4</v>
       </c>
       <c r="H918">
         <v>0.6566012235086919</v>
@@ -27946,7 +27946,7 @@
         <v>-1.103820878211852</v>
       </c>
       <c r="G919">
-        <v>5.85515416311088</v>
+        <v>4</v>
       </c>
       <c r="H919">
         <v>0.1054911030988691</v>
@@ -28024,7 +28024,7 @@
         <v>2024</v>
       </c>
       <c r="C922">
-        <v>0.4209232633670696</v>
+        <v>0</v>
       </c>
       <c r="D922">
         <v>0.1874823351090073</v>
@@ -28053,7 +28053,7 @@
         <v>2025</v>
       </c>
       <c r="C923">
-        <v>-0.8116312801722668</v>
+        <v>0</v>
       </c>
       <c r="D923">
         <v>-0.1715069383159224</v>
@@ -28082,7 +28082,7 @@
         <v>2026</v>
       </c>
       <c r="C924">
-        <v>0.008841297052153869</v>
+        <v>0</v>
       </c>
       <c r="D924">
         <v>0.06613601400846389</v>
@@ -28111,7 +28111,7 @@
         <v>2027</v>
       </c>
       <c r="C925">
-        <v>-0.4971849247921743</v>
+        <v>0</v>
       </c>
       <c r="D925">
         <v>0.0003024576747388322</v>
@@ -28140,7 +28140,7 @@
         <v>2028</v>
       </c>
       <c r="C926">
-        <v>-0.3417141328138142</v>
+        <v>0</v>
       </c>
       <c r="D926">
         <v>0.115449972516587</v>
@@ -28169,7 +28169,7 @@
         <v>2024</v>
       </c>
       <c r="C927">
-        <v>0.4194173143052343</v>
+        <v>0</v>
       </c>
       <c r="D927">
         <v>-0.03436750065618765</v>
@@ -28198,7 +28198,7 @@
         <v>2025</v>
       </c>
       <c r="C928">
-        <v>-0.8129652257828752</v>
+        <v>0</v>
       </c>
       <c r="D928">
         <v>-0.1070153125044264</v>
@@ -28227,7 +28227,7 @@
         <v>2026</v>
       </c>
       <c r="C929">
-        <v>0.00904543335317684</v>
+        <v>0</v>
       </c>
       <c r="D929">
         <v>-0.00240760130105165</v>
@@ -28256,7 +28256,7 @@
         <v>2027</v>
       </c>
       <c r="C930">
-        <v>-0.4992156332976</v>
+        <v>0</v>
       </c>
       <c r="D930">
         <v>0.01707137648062733</v>
@@ -28285,7 +28285,7 @@
         <v>2028</v>
       </c>
       <c r="C931">
-        <v>-0.3419610880782458</v>
+        <v>0</v>
       </c>
       <c r="D931">
         <v>0.1001794318566049</v>
@@ -28314,7 +28314,7 @@
         <v>2024</v>
       </c>
       <c r="C932">
-        <v>0.4139072731902053</v>
+        <v>0</v>
       </c>
       <c r="D932">
         <v>0.4676854440999878</v>
@@ -28343,7 +28343,7 @@
         <v>2025</v>
       </c>
       <c r="C933">
-        <v>-0.8357770472824354</v>
+        <v>0</v>
       </c>
       <c r="D933">
         <v>0.3867568417549703</v>
@@ -28372,7 +28372,7 @@
         <v>2026</v>
       </c>
       <c r="C934">
-        <v>0.01408628305198504</v>
+        <v>0</v>
       </c>
       <c r="D934">
         <v>0.5333471528407878</v>
@@ -28401,7 +28401,7 @@
         <v>2027</v>
       </c>
       <c r="C935">
-        <v>-0.5249055211480892</v>
+        <v>0</v>
       </c>
       <c r="D935">
         <v>0.5006603447406487</v>
@@ -28430,7 +28430,7 @@
         <v>2028</v>
       </c>
       <c r="C936">
-        <v>-0.3455974120574232</v>
+        <v>0</v>
       </c>
       <c r="D936">
         <v>0.5223033226606875</v>
@@ -28459,7 +28459,7 @@
         <v>2024</v>
       </c>
       <c r="C937">
-        <v>0.4209222071110646</v>
+        <v>0</v>
       </c>
       <c r="D937">
         <v>-0.04654255801903285</v>
@@ -28491,7 +28491,7 @@
         <v>2025</v>
       </c>
       <c r="C938">
-        <v>-0.8116293482607573</v>
+        <v>0</v>
       </c>
       <c r="D938">
         <v>0.3794969733463215</v>
@@ -28523,7 +28523,7 @@
         <v>2026</v>
       </c>
       <c r="C939">
-        <v>0.00883960342186834</v>
+        <v>0</v>
       </c>
       <c r="D939">
         <v>0.2500251945274473</v>
@@ -28555,7 +28555,7 @@
         <v>2027</v>
       </c>
       <c r="C940">
-        <v>-0.4971833735628242</v>
+        <v>0</v>
       </c>
       <c r="D940">
         <v>0.3199287203894957</v>
@@ -28587,7 +28587,7 @@
         <v>2028</v>
       </c>
       <c r="C941">
-        <v>-0.3417148651566914</v>
+        <v>0</v>
       </c>
       <c r="D941">
         <v>0.3451163339510503</v>
@@ -28619,7 +28619,7 @@
         <v>2024</v>
       </c>
       <c r="C942">
-        <v>1.125150532382845</v>
+        <v>0</v>
       </c>
       <c r="D942">
         <v>0.4001245654421672</v>
@@ -28645,7 +28645,7 @@
         <v>2025</v>
       </c>
       <c r="C943">
-        <v>1.560933605463124</v>
+        <v>0</v>
       </c>
       <c r="D943">
         <v>-1.219772176815059</v>
@@ -28671,7 +28671,7 @@
         <v>2026</v>
       </c>
       <c r="C944">
-        <v>1.451027087306407</v>
+        <v>0</v>
       </c>
       <c r="D944">
         <v>-0.5579984217917601</v>
@@ -28697,7 +28697,7 @@
         <v>2027</v>
       </c>
       <c r="C945">
-        <v>1.92526560676326</v>
+        <v>0</v>
       </c>
       <c r="D945">
         <v>-0.8291291394191966</v>
@@ -28723,7 +28723,7 @@
         <v>2028</v>
       </c>
       <c r="C946">
-        <v>1.828323902305427</v>
+        <v>0</v>
       </c>
       <c r="D946">
         <v>-0.6004900600492735</v>
@@ -28749,7 +28749,7 @@
         <v>2024</v>
       </c>
       <c r="C947">
-        <v>0.09213871075840564</v>
+        <v>0</v>
       </c>
       <c r="D947">
         <v>-0.7115645927571702</v>
@@ -28781,7 +28781,7 @@
         <v>2025</v>
       </c>
       <c r="C948">
-        <v>-1.396489926108058</v>
+        <v>0</v>
       </c>
       <c r="D948">
         <v>2.177264371136334</v>
@@ -28813,7 +28813,7 @@
         <v>2026</v>
       </c>
       <c r="C949">
-        <v>0.3647164168817649</v>
+        <v>0</v>
       </c>
       <c r="D949">
         <v>-1.433099703977799</v>
@@ -28845,7 +28845,7 @@
         <v>2027</v>
       </c>
       <c r="C950">
-        <v>-1.422504774246717</v>
+        <v>0</v>
       </c>
       <c r="D950">
         <v>2.236727673581659</v>
@@ -28877,7 +28877,7 @@
         <v>2028</v>
       </c>
       <c r="C951">
-        <v>-0.05602990077157659</v>
+        <v>0</v>
       </c>
       <c r="D951">
         <v>-1.126731846542834</v>
@@ -28909,7 +28909,7 @@
         <v>2024</v>
       </c>
       <c r="C952">
-        <v>0.9706376478795424</v>
+        <v>-0.9706376478795424</v>
       </c>
       <c r="D952">
         <v>-0.1676152677516826</v>
@@ -28938,13 +28938,13 @@
         <v>2025</v>
       </c>
       <c r="C953">
-        <v>0.8541472046524439</v>
+        <v>-0.8541472046524439</v>
       </c>
       <c r="D953">
         <v>-0.3143350709030779</v>
       </c>
       <c r="E953">
-        <v>8.109224925327458</v>
+        <v>4</v>
       </c>
       <c r="F953">
         <v>-0.6619548683256548</v>
@@ -28967,13 +28967,13 @@
         <v>2026</v>
       </c>
       <c r="C954">
-        <v>1.19723389236405</v>
+        <v>-1.19723389236405</v>
       </c>
       <c r="D954">
         <v>-0.2872182885765032</v>
       </c>
       <c r="E954">
-        <v>8.727206975454914</v>
+        <v>4</v>
       </c>
       <c r="F954">
         <v>0.09322415699650329</v>
@@ -28996,13 +28996,13 @@
         <v>2027</v>
       </c>
       <c r="C955">
-        <v>1.28950575299043</v>
+        <v>-1.28950575299043</v>
       </c>
       <c r="D955">
         <v>-0.2658510639422426</v>
       </c>
       <c r="E955">
-        <v>5.738853077288637</v>
+        <v>4</v>
       </c>
       <c r="F955">
         <v>-0.6818509601673547</v>
@@ -29025,7 +29025,7 @@
         <v>2028</v>
       </c>
       <c r="C956">
-        <v>1.311043780539446</v>
+        <v>-1.311043780539446</v>
       </c>
       <c r="D956">
         <v>-0.1599852793234095</v>
@@ -29054,7 +29054,7 @@
         <v>2024</v>
       </c>
       <c r="C957">
-        <v>1.124336980840754</v>
+        <v>-1.124336980840754</v>
       </c>
       <c r="D957">
         <v>-1.340794781698993</v>
@@ -29077,7 +29077,7 @@
         <v>2025</v>
       </c>
       <c r="C958">
-        <v>1.576540146099428</v>
+        <v>-1.576540146099428</v>
       </c>
       <c r="D958">
         <v>3.223585629051335</v>
@@ -29100,13 +29100,13 @@
         <v>2026</v>
       </c>
       <c r="C959">
-        <v>1.45789587179664</v>
+        <v>-1.45789587179664</v>
       </c>
       <c r="D959">
         <v>-2.619757761369901</v>
       </c>
       <c r="F959">
-        <v>-6.896194776928313</v>
+        <v>-4</v>
       </c>
       <c r="I959">
         <v>-0.7049306427961547</v>
@@ -29123,7 +29123,7 @@
         <v>2027</v>
       </c>
       <c r="C960">
-        <v>1.937832125611594</v>
+        <v>-1.937832125611594</v>
       </c>
       <c r="D960">
         <v>3.268776042283505</v>
@@ -29146,13 +29146,13 @@
         <v>2028</v>
       </c>
       <c r="C961">
-        <v>1.840440160203817</v>
+        <v>-1.840440160203817</v>
       </c>
       <c r="D961">
         <v>-2.134831310259527</v>
       </c>
       <c r="F961">
-        <v>-7.298090305342003</v>
+        <v>-4</v>
       </c>
       <c r="I961">
         <v>-0.739209463872513</v>
@@ -29169,7 +29169,7 @@
         <v>2024</v>
       </c>
       <c r="C962">
-        <v>-0.4324336199356265</v>
+        <v>0</v>
       </c>
       <c r="D962">
         <v>-1.380149525598535</v>
@@ -29201,7 +29201,7 @@
         <v>2025</v>
       </c>
       <c r="C963">
-        <v>0.5938989600056699</v>
+        <v>0</v>
       </c>
       <c r="D963">
         <v>-1.081465180107411</v>
@@ -29233,7 +29233,7 @@
         <v>2026</v>
       </c>
       <c r="C964">
-        <v>0.04962123845830073</v>
+        <v>0</v>
       </c>
       <c r="D964">
         <v>-1.942920094310894</v>
@@ -29265,7 +29265,7 @@
         <v>2027</v>
       </c>
       <c r="C965">
-        <v>0.4642754893184929</v>
+        <v>0</v>
       </c>
       <c r="D965">
         <v>-1.829143630183808</v>
@@ -29297,7 +29297,7 @@
         <v>2028</v>
       </c>
       <c r="C966">
-        <v>0.2339026628493215</v>
+        <v>0</v>
       </c>
       <c r="D966">
         <v>-1.858642550041312</v>
@@ -29329,7 +29329,7 @@
         <v>2024</v>
       </c>
       <c r="C967">
-        <v>-0.3684007265854155</v>
+        <v>0</v>
       </c>
       <c r="D967">
         <v>1.209321116792944</v>
@@ -29352,7 +29352,7 @@
         <v>2025</v>
       </c>
       <c r="C968">
-        <v>-0.549933559162006</v>
+        <v>0</v>
       </c>
       <c r="D968">
         <v>0.0290133480213728</v>
@@ -29375,7 +29375,7 @@
         <v>2026</v>
       </c>
       <c r="C969">
-        <v>-0.4682919211026454</v>
+        <v>0</v>
       </c>
       <c r="D969">
         <v>1.892396555959924</v>
@@ -29398,7 +29398,7 @@
         <v>2027</v>
       </c>
       <c r="C970">
-        <v>-0.5824540289106981</v>
+        <v>0</v>
       </c>
       <c r="D970">
         <v>0.1410467104009566</v>
@@ -29421,7 +29421,7 @@
         <v>2028</v>
       </c>
       <c r="C971">
-        <v>-0.6301736975005141</v>
+        <v>0</v>
       </c>
       <c r="D971">
         <v>1.530095447728454</v>
@@ -29444,7 +29444,7 @@
         <v>2024</v>
       </c>
       <c r="C972">
-        <v>-0.4323904581230684</v>
+        <v>0.4323904581230684</v>
       </c>
       <c r="D972">
         <v>-1.675615212179295</v>
@@ -29470,10 +29470,10 @@
         <v>2025</v>
       </c>
       <c r="C973">
-        <v>0.5979733183731576</v>
+        <v>-0.5979733183731576</v>
       </c>
       <c r="D973">
-        <v>4.696830150682251</v>
+        <v>4</v>
       </c>
       <c r="E973">
         <v>-1.579252416028762</v>
@@ -29496,7 +29496,7 @@
         <v>2026</v>
       </c>
       <c r="C974">
-        <v>0.05157951567692734</v>
+        <v>-0.05157951567692734</v>
       </c>
       <c r="D974">
         <v>-2.586613363061087</v>
@@ -29522,7 +29522,7 @@
         <v>2027</v>
       </c>
       <c r="C975">
-        <v>0.4680771364170232</v>
+        <v>-0.4680771364170232</v>
       </c>
       <c r="D975">
         <v>3.765418330462562</v>
@@ -29548,7 +29548,7 @@
         <v>2028</v>
       </c>
       <c r="C976">
-        <v>0.2370716487825792</v>
+        <v>-0.2370716487825792</v>
       </c>
       <c r="D976">
         <v>-1.641003220868453</v>
@@ -29574,7 +29574,7 @@
         <v>2024</v>
       </c>
       <c r="C977">
-        <v>-0.377100244782866</v>
+        <v>0</v>
       </c>
       <c r="D977">
         <v>-0.9441533073645272</v>
@@ -29600,7 +29600,7 @@
         <v>2025</v>
       </c>
       <c r="C978">
-        <v>-0.4284549268863622</v>
+        <v>0</v>
       </c>
       <c r="D978">
         <v>-0.05978446984897976</v>
@@ -29626,7 +29626,7 @@
         <v>2026</v>
       </c>
       <c r="C979">
-        <v>-0.4086676057036289</v>
+        <v>0</v>
       </c>
       <c r="D979">
         <v>-0.7882212037178066</v>
@@ -29635,7 +29635,7 @@
         <v>-0.6201381162426335</v>
       </c>
       <c r="F979">
-        <v>4.807136392291197</v>
+        <v>4</v>
       </c>
       <c r="H979">
         <v>-0.9006924284330377</v>
@@ -29652,7 +29652,7 @@
         <v>2027</v>
       </c>
       <c r="C980">
-        <v>-0.4715632180770602</v>
+        <v>0</v>
       </c>
       <c r="D980">
         <v>-0.489458920775896</v>
@@ -29678,7 +29678,7 @@
         <v>2028</v>
       </c>
       <c r="C981">
-        <v>-0.5338111744539139</v>
+        <v>0</v>
       </c>
       <c r="D981">
         <v>-0.4711488635609637</v>
@@ -29687,7 +29687,7 @@
         <v>-0.39126562332552</v>
       </c>
       <c r="F981">
-        <v>4.431829132301172</v>
+        <v>4</v>
       </c>
       <c r="H981">
         <v>-0.4649842423696736</v>
@@ -29704,7 +29704,7 @@
         <v>2024</v>
       </c>
       <c r="C982">
-        <v>-0.432389644823384</v>
+        <v>0.432389644823384</v>
       </c>
       <c r="D982">
         <v>1.579711585043077</v>
@@ -29733,7 +29733,7 @@
         <v>2025</v>
       </c>
       <c r="C983">
-        <v>0.5979689729968758</v>
+        <v>-0.5979689729968758</v>
       </c>
       <c r="D983">
         <v>-3.971974873035379</v>
@@ -29762,7 +29762,7 @@
         <v>2026</v>
       </c>
       <c r="C984">
-        <v>0.05158109357658336</v>
+        <v>-0.05158109357658336</v>
       </c>
       <c r="D984">
         <v>2.688931977625789</v>
@@ -29791,10 +29791,10 @@
         <v>2027</v>
       </c>
       <c r="C985">
-        <v>0.4680732995132381</v>
+        <v>-0.4680732995132381</v>
       </c>
       <c r="D985">
-        <v>-4.119425376742541</v>
+        <v>-4</v>
       </c>
       <c r="E985">
         <v>1.130983923930292</v>
@@ -29820,7 +29820,7 @@
         <v>2028</v>
       </c>
       <c r="C986">
-        <v>0.2370714898326303</v>
+        <v>-0.2370714898326303</v>
       </c>
       <c r="D986">
         <v>2.225085326390164</v>
@@ -29849,7 +29849,7 @@
         <v>2024</v>
       </c>
       <c r="C987">
-        <v>-0.4323900827791532</v>
+        <v>0</v>
       </c>
       <c r="E987">
         <v>0.7709491944882099</v>
@@ -29869,7 +29869,7 @@
         <v>2025</v>
       </c>
       <c r="C988">
-        <v>0.597971473823018</v>
+        <v>0</v>
       </c>
       <c r="E988">
         <v>0.3047249462758613</v>
@@ -29889,7 +29889,7 @@
         <v>2026</v>
       </c>
       <c r="C989">
-        <v>0.05158023052378373</v>
+        <v>0</v>
       </c>
       <c r="E989">
         <v>0.255784333487485</v>
@@ -29909,7 +29909,7 @@
         <v>2027</v>
       </c>
       <c r="C990">
-        <v>0.4680755201116855</v>
+        <v>0</v>
       </c>
       <c r="E990">
         <v>0.3601024622128981</v>
@@ -29929,7 +29929,7 @@
         <v>2028</v>
       </c>
       <c r="C991">
-        <v>0.2370716201390845</v>
+        <v>0</v>
       </c>
       <c r="E991">
         <v>0.3987699774886644</v>
@@ -29949,7 +29949,7 @@
         <v>2024</v>
       </c>
       <c r="C992">
-        <v>-0.4323905884717975</v>
+        <v>0.4323905884717975</v>
       </c>
       <c r="D992">
         <v>0.7592992203364207</v>
@@ -29975,7 +29975,7 @@
         <v>2025</v>
       </c>
       <c r="C993">
-        <v>0.5979743168663326</v>
+        <v>-0.5979743168663326</v>
       </c>
       <c r="D993">
         <v>0.8292079272692324</v>
@@ -30001,7 +30001,7 @@
         <v>2026</v>
       </c>
       <c r="C994">
-        <v>0.05157923769820531</v>
+        <v>-0.05157923769820531</v>
       </c>
       <c r="D994">
         <v>1.147247420816964</v>
@@ -30027,7 +30027,7 @@
         <v>2027</v>
       </c>
       <c r="C995">
-        <v>0.4680780413593828</v>
+        <v>-0.4680780413593828</v>
       </c>
       <c r="D995">
         <v>0.8562456607507868</v>
@@ -30053,7 +30053,7 @@
         <v>2028</v>
       </c>
       <c r="C996">
-        <v>0.237071758220949</v>
+        <v>-0.237071758220949</v>
       </c>
       <c r="D996">
         <v>0.9626213247741724</v>
@@ -30079,7 +30079,7 @@
         <v>2024</v>
       </c>
       <c r="C997">
-        <v>0.1886791748199544</v>
+        <v>-0.1886791748199544</v>
       </c>
       <c r="D997">
         <v>-0.2351819326848492</v>
@@ -30105,7 +30105,7 @@
         <v>2025</v>
       </c>
       <c r="C998">
-        <v>1.677081561161972</v>
+        <v>-1.677081561161972</v>
       </c>
       <c r="D998">
         <v>-0.1842370870578067</v>
@@ -30131,7 +30131,7 @@
         <v>2026</v>
       </c>
       <c r="C999">
-        <v>0.988596807264713</v>
+        <v>-0.988596807264713</v>
       </c>
       <c r="D999">
         <v>-0.3405915168360164</v>
@@ -30157,7 +30157,7 @@
         <v>2027</v>
       </c>
       <c r="C1000">
-        <v>1.681927306950797</v>
+        <v>-1.681927306950797</v>
       </c>
       <c r="D1000">
         <v>-0.2158186258670557</v>
@@ -30183,7 +30183,7 @@
         <v>2028</v>
       </c>
       <c r="C1001">
-        <v>1.457080971074863</v>
+        <v>-1.457080971074863</v>
       </c>
       <c r="D1001">
         <v>-0.1613662101596771</v>
@@ -30209,7 +30209,7 @@
         <v>2024</v>
       </c>
       <c r="C1002">
-        <v>0.188680915501997</v>
+        <v>-0.188680915501997</v>
       </c>
       <c r="E1002">
         <v>-0.7184400512692987</v>
@@ -30229,7 +30229,7 @@
         <v>2025</v>
       </c>
       <c r="C1003">
-        <v>1.677077721299226</v>
+        <v>-1.677077721299226</v>
       </c>
       <c r="E1003">
         <v>-1.028326589697411</v>
@@ -30249,7 +30249,7 @@
         <v>2026</v>
       </c>
       <c r="C1004">
-        <v>0.9885967725089592</v>
+        <v>-0.9885967725089592</v>
       </c>
       <c r="E1004">
         <v>-1.094021468986063</v>
@@ -30269,7 +30269,7 @@
         <v>2027</v>
       </c>
       <c r="C1005">
-        <v>1.681925097049692</v>
+        <v>-1.681925097049692</v>
       </c>
       <c r="E1005">
         <v>-1.251939228166389</v>
@@ -30289,7 +30289,7 @@
         <v>2028</v>
       </c>
       <c r="C1006">
-        <v>1.457079395108803</v>
+        <v>-1.457079395108803</v>
       </c>
       <c r="E1006">
         <v>-1.318710208688874</v>
@@ -30309,7 +30309,7 @@
         <v>2024</v>
       </c>
       <c r="C1007">
-        <v>0.1879808132058753</v>
+        <v>-0.1879808132058753</v>
       </c>
       <c r="D1007">
         <v>-0.840038026342011</v>
@@ -30335,7 +30335,7 @@
         <v>2025</v>
       </c>
       <c r="C1008">
-        <v>1.667508651665799</v>
+        <v>-1.667508651665799</v>
       </c>
       <c r="D1008">
         <v>-0.1923434952140047</v>
@@ -30361,7 +30361,7 @@
         <v>2026</v>
       </c>
       <c r="C1009">
-        <v>0.9826676838180892</v>
+        <v>-0.9826676838180892</v>
       </c>
       <c r="D1009">
         <v>-1.036052577891663</v>
@@ -30387,7 +30387,7 @@
         <v>2027</v>
       </c>
       <c r="C1010">
-        <v>1.673531981002842</v>
+        <v>-1.673531981002842</v>
       </c>
       <c r="D1010">
         <v>-0.5853647524994078</v>
@@ -30413,7 +30413,7 @@
         <v>2028</v>
       </c>
       <c r="C1011">
-        <v>1.448314330818428</v>
+        <v>-1.448314330818428</v>
       </c>
       <c r="D1011">
         <v>-0.6823650430360098</v>
@@ -30439,7 +30439,7 @@
         <v>2024</v>
       </c>
       <c r="C1012">
-        <v>0.9066868943940368</v>
+        <v>0</v>
       </c>
       <c r="D1012">
         <v>0.3944724724550327</v>
@@ -30468,7 +30468,7 @@
         <v>2025</v>
       </c>
       <c r="C1013">
-        <v>-0.6033193184386195</v>
+        <v>0</v>
       </c>
       <c r="D1013">
         <v>0.6755022385631052</v>
@@ -30497,7 +30497,7 @@
         <v>2026</v>
       </c>
       <c r="C1014">
-        <v>0.6784730262183893</v>
+        <v>0</v>
       </c>
       <c r="D1014">
         <v>0.6705960976892906</v>
@@ -30526,7 +30526,7 @@
         <v>2027</v>
       </c>
       <c r="C1015">
-        <v>-0.1128676681087529</v>
+        <v>0</v>
       </c>
       <c r="D1015">
         <v>0.6814194500619296</v>
@@ -30555,7 +30555,7 @@
         <v>2028</v>
       </c>
       <c r="C1016">
-        <v>0.3023194512859692</v>
+        <v>0</v>
       </c>
       <c r="D1016">
         <v>0.6500022057878281</v>
@@ -30584,7 +30584,7 @@
         <v>2024</v>
       </c>
       <c r="C1017">
-        <v>2.633641620369048</v>
+        <v>0</v>
       </c>
       <c r="E1017">
         <v>-0.7305982087955576</v>
@@ -30607,7 +30607,7 @@
         <v>2025</v>
       </c>
       <c r="C1018">
-        <v>-1.128108366834973</v>
+        <v>0</v>
       </c>
       <c r="E1018">
         <v>-0.6448349124358781</v>
@@ -30630,7 +30630,7 @@
         <v>2026</v>
       </c>
       <c r="C1019">
-        <v>2.760973001697449</v>
+        <v>0</v>
       </c>
       <c r="E1019">
         <v>-0.07391824305923989</v>
@@ -30653,7 +30653,7 @@
         <v>2027</v>
       </c>
       <c r="C1020">
-        <v>-0.1087192993865466</v>
+        <v>0</v>
       </c>
       <c r="E1020">
         <v>-0.5741943443518239</v>
@@ -30676,7 +30676,7 @@
         <v>2028</v>
       </c>
       <c r="C1021">
-        <v>1.889485124238244</v>
+        <v>0</v>
       </c>
       <c r="E1021">
         <v>-0.2025072462666623</v>
@@ -30699,7 +30699,7 @@
         <v>2024</v>
       </c>
       <c r="C1022">
-        <v>1.374047983115379</v>
+        <v>0</v>
       </c>
       <c r="E1022">
         <v>0.9298641804693012</v>
@@ -30725,7 +30725,7 @@
         <v>2025</v>
       </c>
       <c r="C1023">
-        <v>-0.9961193712801836</v>
+        <v>0</v>
       </c>
       <c r="E1023">
         <v>-1.52629304764322</v>
@@ -30751,7 +30751,7 @@
         <v>2026</v>
       </c>
       <c r="C1024">
-        <v>0.699094774493185</v>
+        <v>0</v>
       </c>
       <c r="E1024">
         <v>1.58011298310334</v>
@@ -30777,7 +30777,7 @@
         <v>2027</v>
       </c>
       <c r="C1025">
-        <v>-0.3049348162331055</v>
+        <v>0</v>
       </c>
       <c r="E1025">
         <v>-1.658665522862516</v>
@@ -30803,7 +30803,7 @@
         <v>2028</v>
       </c>
       <c r="C1026">
-        <v>0.1541308736511116</v>
+        <v>0</v>
       </c>
       <c r="E1026">
         <v>1.739656539314334</v>
@@ -30829,7 +30829,7 @@
         <v>2024</v>
       </c>
       <c r="C1027">
-        <v>2.909095161486063</v>
+        <v>0</v>
       </c>
       <c r="D1027">
         <v>0.1233333440689704</v>
@@ -30858,7 +30858,7 @@
         <v>2025</v>
       </c>
       <c r="C1028">
-        <v>-0.973301499792802</v>
+        <v>0</v>
       </c>
       <c r="D1028">
         <v>0.9101007029888618</v>
@@ -30887,7 +30887,7 @@
         <v>2026</v>
       </c>
       <c r="C1029">
-        <v>2.972538885812198</v>
+        <v>0</v>
       </c>
       <c r="D1029">
         <v>0.5858701031366071</v>
@@ -30916,7 +30916,7 @@
         <v>2027</v>
       </c>
       <c r="C1030">
-        <v>0.1706041736645615</v>
+        <v>0</v>
       </c>
       <c r="D1030">
         <v>0.7303928220651176</v>
@@ -30945,7 +30945,7 @@
         <v>2028</v>
       </c>
       <c r="C1031">
-        <v>2.100917743850338</v>
+        <v>0</v>
       </c>
       <c r="D1031">
         <v>0.6444347230225446</v>
@@ -30974,7 +30974,7 @@
         <v>2024</v>
       </c>
       <c r="C1032">
-        <v>-0.2600576788825699</v>
+        <v>0</v>
       </c>
       <c r="D1032">
         <v>0.1871791010058364</v>
@@ -31006,7 +31006,7 @@
         <v>2025</v>
       </c>
       <c r="C1033">
-        <v>-1.534438392310211</v>
+        <v>0</v>
       </c>
       <c r="D1033">
         <v>0.02768729218595046</v>
@@ -31038,7 +31038,7 @@
         <v>2026</v>
       </c>
       <c r="C1034">
-        <v>0.05877974403172656</v>
+        <v>0</v>
       </c>
       <c r="D1034">
         <v>0.1711159616926335</v>
@@ -31070,7 +31070,7 @@
         <v>2027</v>
       </c>
       <c r="C1035">
-        <v>-1.765597432231501</v>
+        <v>0</v>
       </c>
       <c r="D1035">
         <v>0.1505518291100304</v>
@@ -31102,7 +31102,7 @@
         <v>2028</v>
       </c>
       <c r="C1036">
-        <v>-0.2761576952867965</v>
+        <v>0</v>
       </c>
       <c r="D1036">
         <v>0.2272985660875717</v>
@@ -31134,7 +31134,7 @@
         <v>2024</v>
       </c>
       <c r="C1037">
-        <v>2.62297510696543</v>
+        <v>-2.62297510696543</v>
       </c>
       <c r="D1037">
         <v>0.05969041122804858</v>
@@ -31163,7 +31163,7 @@
         <v>2025</v>
       </c>
       <c r="C1038">
-        <v>-0.9757277341562328</v>
+        <v>0.9757277341562328</v>
       </c>
       <c r="D1038">
         <v>-0.1799636940411147</v>
@@ -31192,7 +31192,7 @@
         <v>2026</v>
       </c>
       <c r="C1039">
-        <v>2.536928180457669</v>
+        <v>-2.536928180457669</v>
       </c>
       <c r="D1039">
         <v>-0.07676633839475305</v>
@@ -31221,7 +31221,7 @@
         <v>2027</v>
       </c>
       <c r="C1040">
-        <v>0.09588621172646566</v>
+        <v>-0.09588621172646566</v>
       </c>
       <c r="D1040">
         <v>-0.07153597866128393</v>
@@ -31250,7 +31250,7 @@
         <v>2028</v>
       </c>
       <c r="C1041">
-        <v>1.722985930943912</v>
+        <v>-1.722985930943912</v>
       </c>
       <c r="D1041">
         <v>0.02111906084631589</v>
@@ -31279,7 +31279,7 @@
         <v>2024</v>
       </c>
       <c r="C1042">
-        <v>1.377931840084425</v>
+        <v>0</v>
       </c>
       <c r="D1042">
         <v>-1.063077130551025</v>
@@ -31308,7 +31308,7 @@
         <v>2025</v>
       </c>
       <c r="C1043">
-        <v>-0.9914575636330109</v>
+        <v>0</v>
       </c>
       <c r="D1043">
         <v>0.3058597185545134</v>
@@ -31337,7 +31337,7 @@
         <v>2026</v>
       </c>
       <c r="C1044">
-        <v>0.6988263381804536</v>
+        <v>0</v>
       </c>
       <c r="D1044">
         <v>-1.167308552102856</v>
@@ -31366,7 +31366,7 @@
         <v>2027</v>
       </c>
       <c r="C1045">
-        <v>-0.2986562809288325</v>
+        <v>0</v>
       </c>
       <c r="D1045">
         <v>-0.3028818071306529</v>
@@ -31395,7 +31395,7 @@
         <v>2028</v>
       </c>
       <c r="C1046">
-        <v>0.1556152162798971</v>
+        <v>0</v>
       </c>
       <c r="D1046">
         <v>-0.6501881719618335</v>
@@ -31424,7 +31424,7 @@
         <v>2024</v>
       </c>
       <c r="C1047">
-        <v>1.377929952246327</v>
+        <v>0</v>
       </c>
       <c r="D1047">
         <v>0.940180683941728</v>
@@ -31453,7 +31453,7 @@
         <v>2025</v>
       </c>
       <c r="C1048">
-        <v>-0.9914546879535958</v>
+        <v>0</v>
       </c>
       <c r="D1048">
         <v>-0.2538234526100686</v>
@@ -31482,7 +31482,7 @@
         <v>2026</v>
       </c>
       <c r="C1049">
-        <v>0.6988236079479966</v>
+        <v>0</v>
       </c>
       <c r="D1049">
         <v>0.6889887649277241</v>
@@ -31511,7 +31511,7 @@
         <v>2027</v>
       </c>
       <c r="C1050">
-        <v>-0.298654066115852</v>
+        <v>0</v>
       </c>
       <c r="D1050">
         <v>0.2410604010132278</v>
@@ -31540,7 +31540,7 @@
         <v>2028</v>
       </c>
       <c r="C1051">
-        <v>0.155614053655958</v>
+        <v>0</v>
       </c>
       <c r="D1051">
         <v>0.4804835772996502</v>
@@ -31569,7 +31569,7 @@
         <v>2024</v>
       </c>
       <c r="C1052">
-        <v>1.042824509615017</v>
+        <v>0</v>
       </c>
       <c r="D1052">
         <v>-0.4314451072411882</v>
@@ -31598,7 +31598,7 @@
         <v>2025</v>
       </c>
       <c r="C1053">
-        <v>-0.4356198515979554</v>
+        <v>0</v>
       </c>
       <c r="D1053">
         <v>-0.1080894360951527</v>
@@ -31627,7 +31627,7 @@
         <v>2026</v>
       </c>
       <c r="C1054">
-        <v>0.6081212077658518</v>
+        <v>0</v>
       </c>
       <c r="D1054">
         <v>-0.316121759211259</v>
@@ -31656,7 +31656,7 @@
         <v>2027</v>
       </c>
       <c r="C1055">
-        <v>0.1125440532548068</v>
+        <v>0</v>
       </c>
       <c r="D1055">
         <v>-0.2179047443243923</v>
@@ -31685,7 +31685,7 @@
         <v>2028</v>
       </c>
       <c r="C1056">
-        <v>0.3029526062453121</v>
+        <v>0</v>
       </c>
       <c r="D1056">
         <v>-0.1368852826310329</v>
@@ -31714,7 +31714,7 @@
         <v>2024</v>
       </c>
       <c r="C1057">
-        <v>0.7823777134064829</v>
+        <v>0</v>
       </c>
       <c r="D1057">
         <v>1.961021427809833</v>
@@ -31740,7 +31740,7 @@
         <v>2025</v>
       </c>
       <c r="C1058">
-        <v>0.04580746320218585</v>
+        <v>0</v>
       </c>
       <c r="D1058">
         <v>-0.735439115109366</v>
@@ -31766,7 +31766,7 @@
         <v>2026</v>
       </c>
       <c r="C1059">
-        <v>0.5756706942267591</v>
+        <v>0</v>
       </c>
       <c r="D1059">
         <v>1.653157215492967</v>
@@ -31792,7 +31792,7 @@
         <v>2027</v>
       </c>
       <c r="C1060">
-        <v>0.4623723170072383</v>
+        <v>0</v>
       </c>
       <c r="D1060">
         <v>0.1632065714933961</v>
@@ -31818,7 +31818,7 @@
         <v>2028</v>
       </c>
       <c r="C1061">
-        <v>0.4689852566466686</v>
+        <v>0</v>
       </c>
       <c r="D1061">
         <v>0.9503535531705634</v>
@@ -31844,7 +31844,7 @@
         <v>2024</v>
       </c>
       <c r="C1062">
-        <v>1.377931715662224</v>
+        <v>0</v>
       </c>
       <c r="E1062">
         <v>-0.4134083398371869</v>
@@ -31870,7 +31870,7 @@
         <v>2025</v>
       </c>
       <c r="C1063">
-        <v>-0.9914573697427284</v>
+        <v>0</v>
       </c>
       <c r="E1063">
         <v>0.4936632832487322</v>
@@ -31896,7 +31896,7 @@
         <v>2026</v>
       </c>
       <c r="C1064">
-        <v>0.6988261579230886</v>
+        <v>0</v>
       </c>
       <c r="E1064">
         <v>0.7706601089838807</v>
@@ -31922,7 +31922,7 @@
         <v>2027</v>
       </c>
       <c r="C1065">
-        <v>-0.2986561305793293</v>
+        <v>0</v>
       </c>
       <c r="E1065">
         <v>0.8188162468000281</v>
@@ -31948,7 +31948,7 @@
         <v>2028</v>
       </c>
       <c r="C1066">
-        <v>0.1556151410843959</v>
+        <v>0</v>
       </c>
       <c r="E1066">
         <v>0.9646541507299492</v>
@@ -31974,7 +31974,7 @@
         <v>2024</v>
       </c>
       <c r="C1067">
-        <v>1.952716193461725</v>
+        <v>-1.952716193461725</v>
       </c>
       <c r="D1067">
         <v>0.3461315864713097</v>
@@ -31997,7 +31997,7 @@
         <v>2025</v>
       </c>
       <c r="C1068">
-        <v>-0.9775846950420216</v>
+        <v>0.9775846950420216</v>
       </c>
       <c r="D1068">
         <v>0.1304396141020395</v>
@@ -32023,7 +32023,7 @@
         <v>2026</v>
       </c>
       <c r="C1069">
-        <v>1.533251915184754</v>
+        <v>-1.533251915184754</v>
       </c>
       <c r="D1069">
         <v>0.09671036602482662</v>
@@ -32049,7 +32049,7 @@
         <v>2027</v>
       </c>
       <c r="C1070">
-        <v>-0.0955455492182368</v>
+        <v>0.0955455492182368</v>
       </c>
       <c r="D1070">
         <v>0.06417652735356258</v>
@@ -32075,7 +32075,7 @@
         <v>2028</v>
       </c>
       <c r="C1071">
-        <v>0.863472091329905</v>
+        <v>-0.863472091329905</v>
       </c>
       <c r="D1071">
         <v>0.1273423642247783</v>
@@ -32101,7 +32101,7 @@
         <v>2024</v>
       </c>
       <c r="C1072">
-        <v>2.909089657644557</v>
+        <v>-2.909089657644557</v>
       </c>
       <c r="D1072">
         <v>-0.559903356026287</v>
@@ -32127,7 +32127,7 @@
         <v>2025</v>
       </c>
       <c r="C1073">
-        <v>-0.9732930008647962</v>
+        <v>0.9732930008647962</v>
       </c>
       <c r="D1073">
         <v>-0.8656956613509371</v>
@@ -32153,7 +32153,7 @@
         <v>2026</v>
       </c>
       <c r="C1074">
-        <v>2.9725279503569</v>
+        <v>-2.9725279503569</v>
       </c>
       <c r="D1074">
         <v>-0.6300863432807262</v>
@@ -32179,7 +32179,7 @@
         <v>2027</v>
       </c>
       <c r="C1075">
-        <v>0.1706127713557685</v>
+        <v>-0.1706127713557685</v>
       </c>
       <c r="D1075">
         <v>-0.483572341701671</v>
@@ -32205,7 +32205,7 @@
         <v>2028</v>
       </c>
       <c r="C1076">
-        <v>2.100910780213225</v>
+        <v>-2.100910780213225</v>
       </c>
       <c r="D1076">
         <v>-0.2935616908899935</v>
@@ -32231,7 +32231,7 @@
         <v>2024</v>
       </c>
       <c r="C1077">
-        <v>0.9361834111666016</v>
+        <v>-0.9361834111666016</v>
       </c>
       <c r="D1077">
         <v>0.2970251279712547</v>
@@ -32260,7 +32260,7 @@
         <v>2025</v>
       </c>
       <c r="C1078">
-        <v>-0.244987142888262</v>
+        <v>0.244987142888262</v>
       </c>
       <c r="D1078">
         <v>0.2630893832377871</v>
@@ -32289,7 +32289,7 @@
         <v>2026</v>
       </c>
       <c r="C1079">
-        <v>0.589321140433088</v>
+        <v>-0.589321140433088</v>
       </c>
       <c r="D1079">
         <v>0.3588315434065552</v>
@@ -32318,7 +32318,7 @@
         <v>2027</v>
       </c>
       <c r="C1080">
-        <v>0.2516183741593288</v>
+        <v>-0.2516183741593288</v>
       </c>
       <c r="D1080">
         <v>0.3520070413474847</v>
@@ -32347,7 +32347,7 @@
         <v>2028</v>
       </c>
       <c r="C1081">
-        <v>0.3637366328035526</v>
+        <v>-0.3637366328035526</v>
       </c>
       <c r="D1081">
         <v>0.393006725411895</v>
@@ -32376,7 +32376,7 @@
         <v>2024</v>
       </c>
       <c r="C1082">
-        <v>1.3779309042974</v>
+        <v>0</v>
       </c>
       <c r="D1082">
         <v>-1.32591984917643</v>
@@ -32405,7 +32405,7 @@
         <v>2025</v>
       </c>
       <c r="C1083">
-        <v>-0.9914561362430584</v>
+        <v>0</v>
       </c>
       <c r="D1083">
         <v>-0.997923974013465</v>
@@ -32434,7 +32434,7 @@
         <v>2026</v>
       </c>
       <c r="C1084">
-        <v>0.6988249846843702</v>
+        <v>0</v>
       </c>
       <c r="D1084">
         <v>-3.163474156805175</v>
@@ -32463,7 +32463,7 @@
         <v>2027</v>
       </c>
       <c r="C1085">
-        <v>-0.2986551811183562</v>
+        <v>0</v>
       </c>
       <c r="D1085">
         <v>-1.480180275186496</v>
@@ -32492,7 +32492,7 @@
         <v>2028</v>
       </c>
       <c r="C1086">
-        <v>0.1556146406105054</v>
+        <v>0</v>
       </c>
       <c r="D1086">
         <v>-3.413029214000975</v>
@@ -32550,7 +32550,7 @@
         <v>-0.9914554356714618</v>
       </c>
       <c r="D1088">
-        <v>4.343503123253436</v>
+        <v>4</v>
       </c>
       <c r="E1088">
         <v>-0.2434437128423272</v>
@@ -32651,7 +32651,7 @@
         <v>2024</v>
       </c>
       <c r="C1092">
-        <v>0.6703430282021067</v>
+        <v>-0.6703430282021067</v>
       </c>
       <c r="D1092">
         <v>-0.8190016691818893</v>
@@ -32680,7 +32680,7 @@
         <v>2025</v>
       </c>
       <c r="C1093">
-        <v>0.2726787509534497</v>
+        <v>-0.2726787509534497</v>
       </c>
       <c r="D1093">
         <v>-1.254903525500685</v>
@@ -32709,7 +32709,7 @@
         <v>2026</v>
       </c>
       <c r="C1094">
-        <v>0.579365449447599</v>
+        <v>-0.579365449447599</v>
       </c>
       <c r="D1094">
         <v>-0.9906801382115932</v>
@@ -32738,7 +32738,7 @@
         <v>2027</v>
       </c>
       <c r="C1095">
-        <v>0.6261240102927366</v>
+        <v>-0.6261240102927366</v>
       </c>
       <c r="D1095">
         <v>-0.8105171875008516</v>
@@ -32767,7 +32767,7 @@
         <v>2028</v>
       </c>
       <c r="C1096">
-        <v>0.5629877832553604</v>
+        <v>-0.5629877832553604</v>
       </c>
       <c r="D1096">
         <v>-0.5823270248046244</v>
@@ -32796,7 +32796,7 @@
         <v>2024</v>
       </c>
       <c r="C1097">
-        <v>0.3829442539224198</v>
+        <v>0</v>
       </c>
       <c r="D1097">
         <v>-0.4830989158932738</v>
@@ -32822,7 +32822,7 @@
         <v>2025</v>
       </c>
       <c r="C1098">
-        <v>0.9543289978743594</v>
+        <v>0</v>
       </c>
       <c r="D1098">
         <v>-0.9995524052160922</v>
@@ -32848,7 +32848,7 @@
         <v>2026</v>
       </c>
       <c r="C1099">
-        <v>0.68278477454477</v>
+        <v>0</v>
       </c>
       <c r="D1099">
         <v>-1.046896789230256</v>
@@ -32874,7 +32874,7 @@
         <v>2027</v>
       </c>
       <c r="C1100">
-        <v>1.121785098509264</v>
+        <v>0</v>
       </c>
       <c r="D1100">
         <v>-1.070096668805498</v>
@@ -32900,7 +32900,7 @@
         <v>2028</v>
       </c>
       <c r="C1101">
-        <v>0.920770802822872</v>
+        <v>0</v>
       </c>
       <c r="D1101">
         <v>-0.9436202322820262</v>
@@ -32926,7 +32926,7 @@
         <v>2024</v>
       </c>
       <c r="C1102">
-        <v>1.377932543807348</v>
+        <v>0</v>
       </c>
       <c r="D1102">
         <v>-0.2597417169873574</v>
@@ -32955,7 +32955,7 @@
         <v>2025</v>
       </c>
       <c r="C1103">
-        <v>-0.9914586290442056</v>
+        <v>0</v>
       </c>
       <c r="D1103">
         <v>-0.8310599763691381</v>
@@ -32984,7 +32984,7 @@
         <v>2026</v>
       </c>
       <c r="C1104">
-        <v>0.6988273554481234</v>
+        <v>0</v>
       </c>
       <c r="D1104">
         <v>-0.816787362385121</v>
@@ -33013,7 +33013,7 @@
         <v>2027</v>
       </c>
       <c r="C1105">
-        <v>-0.2986570999692432</v>
+        <v>0</v>
       </c>
       <c r="D1105">
         <v>-0.8232613504371623</v>
@@ -33042,7 +33042,7 @@
         <v>2028</v>
       </c>
       <c r="C1106">
-        <v>0.155615651814415</v>
+        <v>0</v>
       </c>
       <c r="D1106">
         <v>-0.6940007744937869</v>
@@ -33071,7 +33071,7 @@
         <v>2024</v>
       </c>
       <c r="C1107">
-        <v>1.377929872273159</v>
+        <v>0</v>
       </c>
       <c r="D1107">
         <v>1.263894825945268</v>
@@ -33100,7 +33100,7 @@
         <v>2025</v>
       </c>
       <c r="C1108">
-        <v>-0.9914545649208228</v>
+        <v>0</v>
       </c>
       <c r="D1108">
         <v>-2.899581067610357</v>
@@ -33129,7 +33129,7 @@
         <v>2026</v>
       </c>
       <c r="C1109">
-        <v>0.6988234922015532</v>
+        <v>0</v>
       </c>
       <c r="D1109">
         <v>0.3242947647673449</v>
@@ -33158,7 +33158,7 @@
         <v>2027</v>
       </c>
       <c r="C1110">
-        <v>-0.2986539710748182</v>
+        <v>0</v>
       </c>
       <c r="D1110">
         <v>-2.140043412299643</v>
@@ -33187,7 +33187,7 @@
         <v>2028</v>
       </c>
       <c r="C1111">
-        <v>0.1556140048020449</v>
+        <v>0</v>
       </c>
       <c r="D1111">
         <v>-0.4792308137784259</v>
@@ -33216,7 +33216,7 @@
         <v>2024</v>
       </c>
       <c r="C1112">
-        <v>1.92934249712328</v>
+        <v>0</v>
       </c>
       <c r="D1112">
         <v>1.089370737374574</v>
@@ -33242,7 +33242,7 @@
         <v>2025</v>
       </c>
       <c r="C1113">
-        <v>-0.9777877523877472</v>
+        <v>0</v>
       </c>
       <c r="D1113">
         <v>1.054140210467475</v>
@@ -33268,7 +33268,7 @@
         <v>2026</v>
       </c>
       <c r="C1114">
-        <v>1.49880235863338</v>
+        <v>0</v>
       </c>
       <c r="D1114">
         <v>0.7496122284633756</v>
@@ -33294,7 +33294,7 @@
         <v>2027</v>
       </c>
       <c r="C1115">
-        <v>-0.1029446580811283</v>
+        <v>0</v>
       </c>
       <c r="D1115">
         <v>0.479466602860069</v>
@@ -33320,7 +33320,7 @@
         <v>2028</v>
       </c>
       <c r="C1116">
-        <v>0.834184653259802</v>
+        <v>0</v>
       </c>
       <c r="D1116">
         <v>0.3667729678971421</v>
@@ -33346,7 +33346,7 @@
         <v>2024</v>
       </c>
       <c r="C1117">
-        <v>1.370889301015629</v>
+        <v>0</v>
       </c>
       <c r="D1117">
         <v>-0.1422801758919419</v>
@@ -33372,7 +33372,7 @@
         <v>2025</v>
       </c>
       <c r="C1118">
-        <v>-0.9803511283590161</v>
+        <v>0</v>
       </c>
       <c r="D1118">
         <v>-0.3285513291620629</v>
@@ -33398,7 +33398,7 @@
         <v>2026</v>
       </c>
       <c r="C1119">
-        <v>0.6965514974682782</v>
+        <v>0</v>
       </c>
       <c r="D1119">
         <v>-0.2842487466241019</v>
@@ -33424,7 +33424,7 @@
         <v>2027</v>
       </c>
       <c r="C1120">
-        <v>-0.2903514099591136</v>
+        <v>0</v>
       </c>
       <c r="D1120">
         <v>-0.2666681021192269</v>
@@ -33450,7 +33450,7 @@
         <v>2028</v>
       </c>
       <c r="C1121">
-        <v>0.1581771298996781</v>
+        <v>0</v>
       </c>
       <c r="D1121">
         <v>-0.1600934389119067</v>
@@ -33476,7 +33476,7 @@
         <v>2024</v>
       </c>
       <c r="C1122">
-        <v>0.1886810308293686</v>
+        <v>-0.1886810308293686</v>
       </c>
       <c r="D1122">
         <v>-0.2405742827920094</v>
@@ -33496,7 +33496,7 @@
         <v>2025</v>
       </c>
       <c r="C1123">
-        <v>1.677077481142358</v>
+        <v>-1.677077481142358</v>
       </c>
       <c r="D1123">
         <v>0.05240218953580805</v>
@@ -33516,7 +33516,7 @@
         <v>2026</v>
       </c>
       <c r="C1124">
-        <v>0.988596776923077</v>
+        <v>-0.988596776923077</v>
       </c>
       <c r="D1124">
         <v>-0.5158878705079017</v>
@@ -33536,7 +33536,7 @@
         <v>2027</v>
       </c>
       <c r="C1125">
-        <v>1.68192496222487</v>
+        <v>-1.68192496222487</v>
       </c>
       <c r="D1125">
         <v>0.09035368480753996</v>
@@ -33556,7 +33556,7 @@
         <v>2028</v>
       </c>
       <c r="C1126">
-        <v>1.457079302059414</v>
+        <v>-1.457079302059414</v>
       </c>
       <c r="D1126">
         <v>-0.320241825361385</v>
@@ -33576,7 +33576,7 @@
         <v>2024</v>
       </c>
       <c r="C1127">
-        <v>0.4738887321751755</v>
+        <v>0</v>
       </c>
       <c r="D1127">
         <v>-0.04405817805673528</v>
@@ -33605,7 +33605,7 @@
         <v>2025</v>
       </c>
       <c r="C1128">
-        <v>-1.62533172464547</v>
+        <v>0</v>
       </c>
       <c r="D1128">
         <v>-0.2905808015932249</v>
@@ -33634,7 +33634,7 @@
         <v>2026</v>
       </c>
       <c r="C1129">
-        <v>0.8684237390987275</v>
+        <v>0</v>
       </c>
       <c r="D1129">
         <v>-0.2247747629952742</v>
@@ -33663,7 +33663,7 @@
         <v>2027</v>
       </c>
       <c r="C1130">
-        <v>-1.569838660518622</v>
+        <v>0</v>
       </c>
       <c r="D1130">
         <v>-0.209299968561992</v>
@@ -33692,7 +33692,7 @@
         <v>2028</v>
       </c>
       <c r="C1131">
-        <v>0.3438686894929818</v>
+        <v>0</v>
       </c>
       <c r="D1131">
         <v>-0.106844968027513</v>
@@ -33721,7 +33721,7 @@
         <v>2024</v>
       </c>
       <c r="C1132">
-        <v>1.783763584423528</v>
+        <v>-1.783763584423528</v>
       </c>
       <c r="D1132">
         <v>-0.5703941322278272</v>
@@ -33750,7 +33750,7 @@
         <v>2025</v>
       </c>
       <c r="C1133">
-        <v>-1.334464075734527</v>
+        <v>1.334464075734527</v>
       </c>
       <c r="D1133">
         <v>0.8120955897232705</v>
@@ -33779,7 +33779,7 @@
         <v>2026</v>
       </c>
       <c r="C1134">
-        <v>2.057574334746446</v>
+        <v>-2.057574334746446</v>
       </c>
       <c r="D1134">
         <v>-0.5285888432132165</v>
@@ -33808,7 +33808,7 @@
         <v>2027</v>
       </c>
       <c r="C1135">
-        <v>-0.6771121427922305</v>
+        <v>0.6771121427922305</v>
       </c>
       <c r="D1135">
         <v>0.4334776563235682</v>
@@ -33837,7 +33837,7 @@
         <v>2028</v>
       </c>
       <c r="C1136">
-        <v>1.292971103416035</v>
+        <v>-1.292971103416035</v>
       </c>
       <c r="D1136">
         <v>-0.09459090248001034</v>
@@ -33866,7 +33866,7 @@
         <v>2024</v>
       </c>
       <c r="C1137">
-        <v>1.138973002937483</v>
+        <v>-1.138973002937483</v>
       </c>
       <c r="D1137">
         <v>0.7865990664288365</v>
@@ -33895,7 +33895,7 @@
         <v>2025</v>
       </c>
       <c r="C1138">
-        <v>1.43624827748586</v>
+        <v>-1.43624827748586</v>
       </c>
       <c r="D1138">
         <v>0.02411783537164664</v>
@@ -33924,7 +33924,7 @@
         <v>2026</v>
       </c>
       <c r="C1139">
-        <v>1.412155712361371</v>
+        <v>-1.412155712361371</v>
       </c>
       <c r="D1139">
         <v>1.099196962848126</v>
@@ -33953,7 +33953,7 @@
         <v>2027</v>
       </c>
       <c r="C1140">
-        <v>1.830151782565778</v>
+        <v>-1.830151782565778</v>
       </c>
       <c r="D1140">
         <v>0.2500023576763364</v>
@@ -33982,7 +33982,7 @@
         <v>2028</v>
       </c>
       <c r="C1141">
-        <v>1.744052249044894</v>
+        <v>-1.744052249044894</v>
       </c>
       <c r="D1141">
         <v>0.8714149063135599</v>
@@ -34011,7 +34011,7 @@
         <v>2024</v>
       </c>
       <c r="C1142">
-        <v>1.124320038311728</v>
+        <v>-1.124320038311728</v>
       </c>
       <c r="D1142">
         <v>-0.1696255691531769</v>
@@ -34043,7 +34043,7 @@
         <v>2025</v>
       </c>
       <c r="C1143">
-        <v>1.576532825468356</v>
+        <v>-1.576532825468356</v>
       </c>
       <c r="D1143">
         <v>-0.04512538462283337</v>
@@ -34075,7 +34075,7 @@
         <v>2026</v>
       </c>
       <c r="C1144">
-        <v>1.457875846918871</v>
+        <v>-1.457875846918871</v>
       </c>
       <c r="D1144">
         <v>-0.07668208642379584</v>
@@ -34107,7 +34107,7 @@
         <v>2027</v>
       </c>
       <c r="C1145">
-        <v>1.937817670267296</v>
+        <v>-1.937817670267296</v>
       </c>
       <c r="D1145">
         <v>-0.03775325655120682</v>
@@ -34139,7 +34139,7 @@
         <v>2028</v>
       </c>
       <c r="C1146">
-        <v>1.840420476690722</v>
+        <v>-1.840420476690722</v>
       </c>
       <c r="D1146">
         <v>0.04428955960012229</v>
@@ -34171,7 +34171,7 @@
         <v>2024</v>
       </c>
       <c r="C1147">
-        <v>1.124340621700677</v>
+        <v>-2.248681243401354</v>
       </c>
       <c r="D1147">
         <v>0.1224508562421063</v>
@@ -34203,7 +34203,7 @@
         <v>2025</v>
       </c>
       <c r="C1148">
-        <v>1.5765361797947</v>
+        <v>-3.153072359589399</v>
       </c>
       <c r="D1148">
         <v>0.1081891371054465</v>
@@ -34235,7 +34235,7 @@
         <v>2026</v>
       </c>
       <c r="C1149">
-        <v>1.45789752621821</v>
+        <v>-2.915795052436421</v>
       </c>
       <c r="D1149">
         <v>0.1881740366399763</v>
@@ -34267,7 +34267,7 @@
         <v>2027</v>
       </c>
       <c r="C1150">
-        <v>1.937830656341815</v>
+        <v>-3.87566131268363</v>
       </c>
       <c r="D1150">
         <v>0.1928928899302086</v>
@@ -34299,7 +34299,7 @@
         <v>2028</v>
       </c>
       <c r="C1151">
-        <v>1.840439908978253</v>
+        <v>-3.680879817956506</v>
       </c>
       <c r="D1151">
         <v>0.2546142878539916</v>
@@ -34331,7 +34331,7 @@
         <v>2024</v>
       </c>
       <c r="C1152">
-        <v>2.909090245917174</v>
+        <v>-2.909090245917174</v>
       </c>
       <c r="D1152">
         <v>1.448264582150171</v>
@@ -34357,7 +34357,7 @@
         <v>2025</v>
       </c>
       <c r="C1153">
-        <v>-0.9732939060182212</v>
+        <v>0.9732939060182212</v>
       </c>
       <c r="D1153">
         <v>-1.648170349964329</v>
@@ -34383,7 +34383,7 @@
         <v>2026</v>
       </c>
       <c r="C1154">
-        <v>2.972529118037513</v>
+        <v>-2.972529118037513</v>
       </c>
       <c r="D1154">
         <v>1.291927753866666</v>
@@ -34409,7 +34409,7 @@
         <v>2027</v>
       </c>
       <c r="C1155">
-        <v>0.1706118562283996</v>
+        <v>-0.1706118562283996</v>
       </c>
       <c r="D1155">
         <v>-0.8464757990483622</v>
@@ -34435,7 +34435,7 @@
         <v>2028</v>
       </c>
       <c r="C1156">
-        <v>2.100911524470266</v>
+        <v>-2.100911524470266</v>
       </c>
       <c r="D1156">
         <v>0.6462765635226433</v>
@@ -34461,7 +34461,7 @@
         <v>2024</v>
       </c>
       <c r="C1157">
-        <v>1.124337618031076</v>
+        <v>-1.124337618031076</v>
       </c>
       <c r="D1157">
         <v>0.2427502434147983</v>
@@ -34490,7 +34490,7 @@
         <v>2025</v>
       </c>
       <c r="C1158">
-        <v>1.576538427426816</v>
+        <v>-1.576538427426816</v>
       </c>
       <c r="D1158">
         <v>-0.218868370315253</v>
@@ -34519,7 +34519,7 @@
         <v>2026</v>
       </c>
       <c r="C1159">
-        <v>1.457895671436664</v>
+        <v>-1.457895671436664</v>
       </c>
       <c r="D1159">
         <v>0.06494469060156555</v>
@@ -34548,7 +34548,7 @@
         <v>2027</v>
       </c>
       <c r="C1160">
-        <v>1.937831022206772</v>
+        <v>-1.937831022206772</v>
       </c>
       <c r="D1160">
         <v>-0.01403922528766569</v>
@@ -34577,7 +34577,7 @@
         <v>2028</v>
       </c>
       <c r="C1161">
-        <v>1.840439287453094</v>
+        <v>-1.840439287453094</v>
       </c>
       <c r="D1161">
         <v>0.1046250502426192</v>
@@ -34606,7 +34606,7 @@
         <v>2024</v>
       </c>
       <c r="C1162">
-        <v>2.904679568053139</v>
+        <v>-2.904679568053139</v>
       </c>
       <c r="D1162">
         <v>-0.1339383363196509</v>
@@ -34629,7 +34629,7 @@
         <v>2025</v>
       </c>
       <c r="C1163">
-        <v>-0.9668138012810024</v>
+        <v>0.9668138012810024</v>
       </c>
       <c r="D1163">
         <v>-0.2732725677758948</v>
@@ -34652,7 +34652,7 @@
         <v>2026</v>
       </c>
       <c r="C1164">
-        <v>2.968229309318942</v>
+        <v>-2.968229309318942</v>
       </c>
       <c r="D1164">
         <v>-0.2376655351454124</v>
@@ -34675,7 +34675,7 @@
         <v>2027</v>
       </c>
       <c r="C1165">
-        <v>0.1763431811189579</v>
+        <v>-0.1763431811189579</v>
       </c>
       <c r="D1165">
         <v>-0.2171878890857002</v>
@@ -34698,7 +34698,7 @@
         <v>2028</v>
       </c>
       <c r="C1166">
-        <v>2.099532274961566</v>
+        <v>-2.099532274961566</v>
       </c>
       <c r="D1166">
         <v>-0.1148330732820445</v>
@@ -34721,7 +34721,7 @@
         <v>2024</v>
       </c>
       <c r="C1167">
-        <v>2.909089368318778</v>
+        <v>-2.909089368318778</v>
       </c>
       <c r="D1167">
         <v>-0.3072201738430257</v>
@@ -34744,7 +34744,7 @@
         <v>2025</v>
       </c>
       <c r="C1168">
-        <v>-0.9732925554681618</v>
+        <v>0.9732925554681618</v>
       </c>
       <c r="D1168">
         <v>-1.234624128243101</v>
@@ -34767,7 +34767,7 @@
         <v>2026</v>
       </c>
       <c r="C1169">
-        <v>2.972527375987252</v>
+        <v>-2.972527375987252</v>
       </c>
       <c r="D1169">
         <v>-0.8225429848073914</v>
@@ -34790,13 +34790,13 @@
         <v>2027</v>
       </c>
       <c r="C1170">
-        <v>0.170613221697414</v>
+        <v>-0.170613221697414</v>
       </c>
       <c r="D1170">
         <v>-1.300467056136964</v>
       </c>
       <c r="E1170">
-        <v>4.331409410723094</v>
+        <v>4</v>
       </c>
       <c r="F1170">
         <v>-1.731750294204816</v>
@@ -34813,13 +34813,13 @@
         <v>2028</v>
       </c>
       <c r="C1171">
-        <v>2.100910414168113</v>
+        <v>-2.100910414168113</v>
       </c>
       <c r="D1171">
         <v>-0.7578771918685832</v>
       </c>
       <c r="E1171">
-        <v>4.657459635365195</v>
+        <v>4</v>
       </c>
       <c r="F1171">
         <v>-1.636694087039588</v>
@@ -34836,7 +34836,7 @@
         <v>2024</v>
       </c>
       <c r="C1172">
-        <v>2.909095016318055</v>
+        <v>-2.909095016318055</v>
       </c>
       <c r="D1172">
         <v>-1.039774062080257</v>
@@ -34862,7 +34862,7 @@
         <v>2025</v>
       </c>
       <c r="C1173">
-        <v>-0.9733012742407442</v>
+        <v>0.9733012742407442</v>
       </c>
       <c r="D1173">
         <v>0.698251300759441</v>
@@ -34888,7 +34888,7 @@
         <v>2026</v>
       </c>
       <c r="C1174">
-        <v>2.972538596892675</v>
+        <v>-2.972538596892675</v>
       </c>
       <c r="D1174">
         <v>-2.324137757750326</v>
@@ -34914,7 +34914,7 @@
         <v>2027</v>
       </c>
       <c r="C1175">
-        <v>0.1706044020700759</v>
+        <v>-0.1706044020700759</v>
       </c>
       <c r="D1175">
         <v>0.9100196419683332</v>
@@ -34940,7 +34940,7 @@
         <v>2028</v>
       </c>
       <c r="C1176">
-        <v>2.100917560160533</v>
+        <v>-2.100917560160533</v>
       </c>
       <c r="D1176">
         <v>-2.150491160653396</v>
@@ -34966,7 +34966,7 @@
         <v>2024</v>
       </c>
       <c r="C1177">
-        <v>2.909091834936389</v>
+        <v>-2.909091834936389</v>
       </c>
       <c r="E1177">
         <v>-0.7833339770721962</v>
@@ -34989,7 +34989,7 @@
         <v>2025</v>
       </c>
       <c r="C1178">
-        <v>-0.97329636553605</v>
+        <v>0.97329636553605</v>
       </c>
       <c r="E1178">
         <v>-0.7390156937828236</v>
@@ -35012,7 +35012,7 @@
         <v>2026</v>
       </c>
       <c r="C1179">
-        <v>2.972532277256914</v>
+        <v>-2.972532277256914</v>
       </c>
       <c r="E1179">
         <v>-0.610322618670633</v>
@@ -35035,7 +35035,7 @@
         <v>2027</v>
       </c>
       <c r="C1180">
-        <v>0.1706093671628682</v>
+        <v>-0.1706093671628682</v>
       </c>
       <c r="E1180">
         <v>-0.8030860716829987</v>
@@ -35058,7 +35058,7 @@
         <v>2028</v>
       </c>
       <c r="C1181">
-        <v>2.100913535019571</v>
+        <v>-2.100913535019571</v>
       </c>
       <c r="E1181">
         <v>-0.7652935433351347</v>
@@ -35096,7 +35096,7 @@
         <v>0.1505163249475846</v>
       </c>
       <c r="H1182">
-        <v>-4.062459980427661</v>
+        <v>-4</v>
       </c>
       <c r="I1182">
         <v>-0.6882851704938278</v>
@@ -35241,7 +35241,7 @@
         <v>2024</v>
       </c>
       <c r="C1187">
-        <v>-0.07131475781495722</v>
+        <v>0</v>
       </c>
       <c r="D1187">
         <v>-0.29564006723602</v>
@@ -35270,7 +35270,7 @@
         <v>2025</v>
       </c>
       <c r="C1188">
-        <v>-0.4105398198548817</v>
+        <v>0</v>
       </c>
       <c r="D1188">
         <v>0.5540937420418273</v>
@@ -35299,7 +35299,7 @@
         <v>2026</v>
       </c>
       <c r="C1189">
-        <v>-0.3060276986581292</v>
+        <v>0</v>
       </c>
       <c r="D1189">
         <v>-0.5431213667756466</v>
@@ -35328,7 +35328,7 @@
         <v>2027</v>
       </c>
       <c r="C1190">
-        <v>-0.3120417734513997</v>
+        <v>0</v>
       </c>
       <c r="D1190">
         <v>0.5385002955681091</v>
@@ -35357,7 +35357,7 @@
         <v>2028</v>
       </c>
       <c r="C1191">
-        <v>-0.4512817075927677</v>
+        <v>0</v>
       </c>
       <c r="D1191">
         <v>-0.2886911603010563</v>
@@ -35386,7 +35386,7 @@
         <v>2024</v>
       </c>
       <c r="C1192">
-        <v>-0.07169813976287556</v>
+        <v>0</v>
       </c>
       <c r="D1192">
         <v>0.3187749654531639</v>
@@ -35412,7 +35412,7 @@
         <v>2025</v>
       </c>
       <c r="C1193">
-        <v>-0.4074456438949929</v>
+        <v>0</v>
       </c>
       <c r="D1193">
         <v>0.4113612531643978</v>
@@ -35438,7 +35438,7 @@
         <v>2026</v>
       </c>
       <c r="C1194">
-        <v>-0.3072638869268617</v>
+        <v>0</v>
       </c>
       <c r="D1194">
         <v>0.4983595522669817</v>
@@ -35464,7 +35464,7 @@
         <v>2027</v>
       </c>
       <c r="C1195">
-        <v>-0.309237287814197</v>
+        <v>0</v>
       </c>
       <c r="D1195">
         <v>0.4812785716516907</v>
@@ -35490,7 +35490,7 @@
         <v>2028</v>
       </c>
       <c r="C1196">
-        <v>-0.4511593483556566</v>
+        <v>0</v>
       </c>
       <c r="D1196">
         <v>0.5034311424629746</v>
@@ -35627,7 +35627,7 @@
         <v>0.2812677991552214</v>
       </c>
       <c r="H1200">
-        <v>-4.425595443069937</v>
+        <v>-4</v>
       </c>
       <c r="I1200">
         <v>1.974220204345855</v>
@@ -35659,7 +35659,7 @@
         <v>0.1426669219608456</v>
       </c>
       <c r="H1201">
-        <v>-5.804159935273246</v>
+        <v>-4</v>
       </c>
       <c r="I1201">
         <v>1.941141774921374</v>
@@ -35676,7 +35676,7 @@
         <v>2024</v>
       </c>
       <c r="C1202">
-        <v>-0.3681810889443231</v>
+        <v>0</v>
       </c>
       <c r="I1202">
         <v>1.302567803223032</v>
@@ -35690,7 +35690,7 @@
         <v>2025</v>
       </c>
       <c r="C1203">
-        <v>-0.5516497450536156</v>
+        <v>0</v>
       </c>
       <c r="I1203">
         <v>0.8572507363931099</v>
@@ -35704,7 +35704,7 @@
         <v>2026</v>
       </c>
       <c r="C1204">
-        <v>-0.4689985822311152</v>
+        <v>0</v>
       </c>
       <c r="I1204">
         <v>0.7758025680058569</v>
@@ -35718,7 +35718,7 @@
         <v>2027</v>
       </c>
       <c r="C1205">
-        <v>-0.5839871568227338</v>
+        <v>0</v>
       </c>
       <c r="I1205">
         <v>0.7283290079514979</v>
@@ -35732,7 +35732,7 @@
         <v>2028</v>
       </c>
       <c r="C1206">
-        <v>-0.6314177204743193</v>
+        <v>0</v>
       </c>
       <c r="I1206">
         <v>0.7062145007663094</v>
@@ -35746,7 +35746,7 @@
         <v>2024</v>
       </c>
       <c r="C1207">
-        <v>-0.4085988108242845</v>
+        <v>0</v>
       </c>
       <c r="D1207">
         <v>0.636509405646463</v>
@@ -35778,7 +35778,7 @@
         <v>2025</v>
       </c>
       <c r="C1208">
-        <v>-0.145691028567384</v>
+        <v>0</v>
       </c>
       <c r="D1208">
         <v>1.420568967291146</v>
@@ -35810,7 +35810,7 @@
         <v>2026</v>
       </c>
       <c r="C1209">
-        <v>-0.2901310797432791</v>
+        <v>0</v>
       </c>
       <c r="D1209">
         <v>1.356809023178542</v>
@@ -35842,7 +35842,7 @@
         <v>2027</v>
       </c>
       <c r="C1210">
-        <v>-0.218216157299203</v>
+        <v>0</v>
       </c>
       <c r="D1210">
         <v>1.240669862102529</v>
@@ -35874,7 +35874,7 @@
         <v>2028</v>
       </c>
       <c r="C1211">
-        <v>-0.3276545395431396</v>
+        <v>0</v>
       </c>
       <c r="D1211">
         <v>1.118406524106522</v>
@@ -35906,7 +35906,7 @@
         <v>2024</v>
       </c>
       <c r="C1212">
-        <v>-0.3382231316251376</v>
+        <v>0</v>
       </c>
       <c r="D1212">
         <v>0.2138079072319173</v>
@@ -35938,7 +35938,7 @@
         <v>2025</v>
       </c>
       <c r="C1213">
-        <v>0.815183432935123</v>
+        <v>0</v>
       </c>
       <c r="D1213">
         <v>0.08619800532490239</v>
@@ -35970,7 +35970,7 @@
         <v>2026</v>
       </c>
       <c r="C1214">
-        <v>-0.09888441273717584</v>
+        <v>0</v>
       </c>
       <c r="D1214">
         <v>0.1286476928668652</v>
@@ -36002,7 +36002,7 @@
         <v>2027</v>
       </c>
       <c r="C1215">
-        <v>0.6559096228158126</v>
+        <v>0</v>
       </c>
       <c r="D1215">
         <v>0.1243470795224386</v>
@@ -36034,7 +36034,7 @@
         <v>2028</v>
       </c>
       <c r="C1216">
-        <v>0.2104759247953625</v>
+        <v>0</v>
       </c>
       <c r="D1216">
         <v>0.1910668767283228</v>
@@ -36066,7 +36066,7 @@
         <v>2024</v>
       </c>
       <c r="C1217">
-        <v>-0.3086424111273073</v>
+        <v>0</v>
       </c>
       <c r="D1217">
         <v>-0.8306185336010069</v>
@@ -36095,7 +36095,7 @@
         <v>2025</v>
       </c>
       <c r="C1218">
-        <v>0.8360684946606429</v>
+        <v>0</v>
       </c>
       <c r="D1218">
         <v>-2.046223088666762</v>
@@ -36124,7 +36124,7 @@
         <v>2026</v>
       </c>
       <c r="C1219">
-        <v>0.05900734336567861</v>
+        <v>0</v>
       </c>
       <c r="D1219">
         <v>-2.378000093913234</v>
@@ -36153,7 +36153,7 @@
         <v>2027</v>
       </c>
       <c r="C1220">
-        <v>0.7207143357147866</v>
+        <v>0</v>
       </c>
       <c r="D1220">
         <v>-2.67854303446793</v>
@@ -36182,7 +36182,7 @@
         <v>2028</v>
       </c>
       <c r="C1221">
-        <v>0.3419946692118671</v>
+        <v>0</v>
       </c>
       <c r="D1221">
         <v>-2.783331627376841</v>
@@ -36211,7 +36211,7 @@
         <v>2024</v>
       </c>
       <c r="C1222">
-        <v>0.09382705210038587</v>
+        <v>-0.09382705210038587</v>
       </c>
       <c r="E1222">
         <v>1.863570830653072</v>
@@ -36234,7 +36234,7 @@
         <v>2025</v>
       </c>
       <c r="C1223">
-        <v>2.895145897845211</v>
+        <v>-2.895145897845211</v>
       </c>
       <c r="E1223">
         <v>0.7082906158873615</v>
@@ -36257,7 +36257,7 @@
         <v>2026</v>
       </c>
       <c r="C1224">
-        <v>1.998851548552438</v>
+        <v>-1.998851548552438</v>
       </c>
       <c r="E1224">
         <v>0.7481115090644466</v>
@@ -36280,7 +36280,7 @@
         <v>2027</v>
       </c>
       <c r="C1225">
-        <v>2.796931375357162</v>
+        <v>-2.796931375357162</v>
       </c>
       <c r="E1225">
         <v>0.867270410193324</v>
@@ -36303,7 +36303,7 @@
         <v>2028</v>
       </c>
       <c r="C1226">
-        <v>2.749039226790466</v>
+        <v>-2.749039226790466</v>
       </c>
       <c r="E1226">
         <v>0.9968749343613476</v>
@@ -36797,7 +36797,7 @@
         <v>-0.3979397519187997</v>
       </c>
       <c r="G1248">
-        <v>4.465731974444721</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1249">
@@ -37740,7 +37740,7 @@
         <v>0.1121115251287685</v>
       </c>
       <c r="H1292">
-        <v>-4.237320376939642</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1293">
@@ -37760,7 +37760,7 @@
         <v>0.08266863211456747</v>
       </c>
       <c r="H1293">
-        <v>-5.393265599358077</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="1294">
@@ -39794,7 +39794,7 @@
         <v>2024</v>
       </c>
       <c r="E1389">
-        <v>4.643253345856928</v>
+        <v>4</v>
       </c>
       <c r="F1389">
         <v>0.2939959999861965</v>
